--- a/SLOVAKIA_2026_FINAL_LINKS_FIXED.xlsx
+++ b/SLOVAKIA_2026_FINAL_LINKS_FIXED.xlsx
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="18" customWidth="1" style="6" min="1" max="1"/>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>כפר הררי ציורי, בתי עץ, קפה וצילומים.</t>
+          <t>ביקור אחד ממוקד: חניה ליד Ždiarsky Dom, הליכה בין בתי העץ הגוראליים, צילומים מול ההרים וקפה/עוגה אם רוצים.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>אין צורך במסלול ארוך בתוך הכפר.</t>
+          <t>לא חוזרים ל־Ždiar פעם נוספת. לא משוטטים סתם – ביקור קצר וממוקד בלבד.</t>
         </is>
       </c>
     </row>
@@ -1905,47 +1905,47 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Ždiar</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Bobová dráha Bachledka – מגלשת ההרים</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Obria lavička</t>
+          <t>Bachledka Ski &amp; Sun</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Obria lavička Ždiar</t>
+          <t>Bachledka Ski &amp; Sun, Ždiar 702, Slovakia</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>5–10 דק׳</t>
+          <t>🚶 באותו מתחם</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>20–30 דק׳</t>
+          <t>30–45 דק׳</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>€44 ל־4 לסיבוב רגיל; €36 ל־4 אם מספיקים למבצע עד 10:30</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>ספסל ענק מול הנוף ונקודת צילום מיוחדת.</t>
+          <t>מגלשת הרים חדשה באורך 1,520 מ׳, 20 פניות ועד 40 קמ״ש. שולטים במהירות לבד.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>עצירה קצרה ונוחה.</t>
+          <t>באותו מתחם – אין נסיעה נוספת. יש למלא טופס לפני הנסיעה.</t>
         </is>
       </c>
     </row>
@@ -1957,22 +1957,22 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>Ždiar</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>Obria lavička</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Strednica Viewpoint</t>
-        </is>
-      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Strednica Ždiar</t>
+          <t>Obria lavička Ždiar</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>30–45 דק׳</t>
+          <t>20–30 דק׳</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>תצפית פתוחה על רכס Belianske Tatras.</t>
+          <t>ספסל ענק מול הנוף ונקודת צילום מיוחדת.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>כמעט ללא הליכה.</t>
+          <t>עצירה קצרה ונוחה.</t>
         </is>
       </c>
     </row>
@@ -2009,22 +2009,22 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>Obria lavička</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>Strednica Viewpoint</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים באזור Ždiar</t>
-        </is>
-      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ždiar, Slovakia</t>
+          <t>Strednica Ždiar</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>60 דק׳</t>
+          <t>30–45 דק׳</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>ארוחה רגועה וקפה.</t>
+          <t>תצפית פתוחה על רכס Belianske Tatras.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>אפשר להזיז לפי עומס ומזג אוויר.</t>
+          <t>כמעט ללא הליכה.</t>
         </is>
       </c>
     </row>
@@ -2061,143 +2061,147 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Strednica Viewpoint</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים באזור Ždiar</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ždiar, Slovakia</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>5–10 דק׳</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>60 דק׳</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>חינם</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>קפה/מאפה/נשנוש קצר בלבד למי שרוצה.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>אין ארוחת צהריים מלאה; אוכלים בוקר וערב במלון.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1" s="6">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>24.9.2026 – יום ה׳</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>ארוחת צהריים באזור Ždiar</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Hotel International</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>30–35 דק׳</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>ערב</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>חזרה לספא ולארוחת ערב.</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Belianska Cave נשארת חלופת גשם בלבד.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1" s="6">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Google Maps ליום</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" s="6">
       <c r="A39" s="4" t="inlineStr">
         <is>
+          <t>Google Maps ליום</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1" s="6">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
           <t>לינה בסוף היום</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1" s="6">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>עלות משוערת ליום ל-4: Bachledka ל־4: €116 אונליין / €120 בקופה; שאר היום חינם.</t>
-        </is>
-      </c>
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="18" t="n"/>
-      <c r="D40" s="18" t="n"/>
-      <c r="E40" s="18" t="n"/>
-      <c r="F40" s="18" t="n"/>
-      <c r="G40" s="18" t="n"/>
-      <c r="H40" s="18" t="n"/>
-      <c r="I40" s="18" t="n"/>
-      <c r="J40" s="19" t="n"/>
-    </row>
-    <row r="41" ht="6" customHeight="1" s="6"/>
-    <row r="42" ht="32" customHeight="1" s="6">
-      <c r="A42" s="32" t="inlineStr">
+    <row r="41" ht="6" customHeight="1" s="6">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>עלות משוערת ליום ל-4: Bachledka €116 אונליין / €120 בקופה + מגלשת Bachledka €44 ל־4 לסיבוב (או €36 במבצע בוקר אם מספיקים).</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="n"/>
+      <c r="I41" s="18" t="n"/>
+      <c r="J41" s="19" t="n"/>
+    </row>
+    <row r="42" ht="32" customHeight="1" s="6"/>
+    <row r="43" ht="58" customHeight="1" s="6">
+      <c r="A43" s="32" t="inlineStr">
         <is>
           <t>חלופה | 24.9 חלופת גשם | חלופת גשם: Belianska Cave, Kežmarok ו־Poprad</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="58" customHeight="1" s="6">
-      <c r="A43" s="34" t="inlineStr">
-        <is>
-          <t>24.9.2026 – חלופה</t>
-        </is>
-      </c>
-      <c r="B43" s="35" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C43" s="34" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Hotel International – יציאה</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Hotel International, Veľká Lomnica</t>
-        </is>
-      </c>
-      <c r="F43" s="35" t="inlineStr">
-        <is>
-          <t>25–30 דק׳</t>
-        </is>
-      </c>
-      <c r="G43" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="35" t="inlineStr">
-        <is>
-          <t>כלול לפי חבילת המלון</t>
-        </is>
-      </c>
-      <c r="I43" s="34" t="inlineStr">
-        <is>
-          <t>יציאה לכיוון מערת Belianska.</t>
-        </is>
-      </c>
-      <c r="J43" s="34" t="inlineStr">
-        <is>
-          <t>להגיע מוקדם כדי לתפוס סיור.</t>
         </is>
       </c>
     </row>
@@ -2209,47 +2213,43 @@
       </c>
       <c r="B44" s="35" t="inlineStr">
         <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="C44" s="34" t="inlineStr">
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C44" s="34" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Hotel International – יציאה</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Belianska Cave</t>
-        </is>
-      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Belianska jaskyňa</t>
+          <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
       <c r="F44" s="35" t="inlineStr">
         <is>
+          <t>25–30 דק׳</t>
+        </is>
+      </c>
+      <c r="G44" s="35" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G44" s="35" t="inlineStr">
-        <is>
-          <t>1:30–2:00 ש׳</t>
-        </is>
-      </c>
       <c r="H44" s="35" t="inlineStr">
         <is>
-          <t>€60 ל־4 (15€ לאדם)</t>
+          <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
       <c r="I44" s="34" t="inlineStr">
         <is>
-          <t>מערת נטיפים מרשימה – חלופה מצוינת למזג אוויר גשום.</t>
+          <t>יציאה לכיוון מערת Belianska.</t>
         </is>
       </c>
       <c r="J44" s="34" t="inlineStr">
         <is>
-          <t>יש עלייה רגלית לכניסה; קר בפנים.</t>
+          <t>להגיע מוקדם כדי לתפוס סיור.</t>
         </is>
       </c>
     </row>
@@ -2261,47 +2261,47 @@
       </c>
       <c r="B45" s="35" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
+          <t>Hotel International – יציאה</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>Belianska Cave</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Kežmarok – מרכז עתיק</t>
-        </is>
-      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hradné námestie, Kežmarok</t>
+          <t>Belianska jaskyňa</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>20–25 דק׳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
         <is>
-          <t>1:15 ש׳</t>
+          <t>1:30–2:00 ש׳</t>
         </is>
       </c>
       <c r="H45" s="35" t="inlineStr">
         <is>
-          <t>המרכז חינם; כניסה לטירה רק אם בוחרים</t>
+          <t>€60 ל־4 (15€ לאדם)</t>
         </is>
       </c>
       <c r="I45" s="34" t="inlineStr">
         <is>
-          <t>טירה, כיכר עתיקה, קפה וארוחת צהריים.</t>
+          <t>מערת נטיפים מרשימה – חלופה מצוינת למזג אוויר גשום.</t>
         </is>
       </c>
       <c r="J45" s="34" t="inlineStr">
         <is>
-          <t>חניה בתשלום במרכז; לא נמצא חניון חינם ציבורי מאומת.</t>
+          <t>יש עלייה רגלית לכניסה; קר בפנים.</t>
         </is>
       </c>
     </row>
@@ -2313,22 +2313,22 @@
       </c>
       <c r="B46" s="35" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
+          <t>Belianska Cave</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>Kežmarok – מרכז עתיק</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Poprad – Forum / מרכז</t>
-        </is>
-      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Forum Poprad</t>
+          <t>Hradné námestie, Kežmarok</t>
         </is>
       </c>
       <c r="F46" s="35" t="inlineStr">
@@ -2338,22 +2338,22 @@
       </c>
       <c r="G46" s="35" t="inlineStr">
         <is>
-          <t>1:30–2:00 ש׳</t>
+          <t>1:15 ש׳</t>
         </is>
       </c>
       <c r="H46" s="35" t="inlineStr">
         <is>
-          <t>חינם; קניות/אוכל לפי בחירה</t>
+          <t>המרכז חינם; כניסה לטירה רק אם בוחרים</t>
         </is>
       </c>
       <c r="I46" s="34" t="inlineStr">
         <is>
-          <t>קניות קלות, קפה וגלידה במקום מקורה.</t>
+          <t>טירה, כיכר עתיקה, קפה וארוחת צהריים.</t>
         </is>
       </c>
       <c r="J46" s="34" t="inlineStr">
         <is>
-          <t>Forum: 2 שעות ראשונות חינם ביום חול.</t>
+          <t>חניה בתשלום במרכז; לא נמצא חניון חינם ציבורי מאומת.</t>
         </is>
       </c>
     </row>
@@ -2365,139 +2365,143 @@
       </c>
       <c r="B47" s="35" t="inlineStr">
         <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C47" s="34" t="inlineStr">
+        <is>
+          <t>Kežmarok – מרכז עתיק</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Poprad – Forum / מרכז</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Forum Poprad</t>
+        </is>
+      </c>
+      <c r="F47" s="35" t="inlineStr">
+        <is>
+          <t>20–25 דק׳</t>
+        </is>
+      </c>
+      <c r="G47" s="35" t="inlineStr">
+        <is>
+          <t>1:30–2:00 ש׳</t>
+        </is>
+      </c>
+      <c r="H47" s="35" t="inlineStr">
+        <is>
+          <t>חינם; קניות/אוכל לפי בחירה</t>
+        </is>
+      </c>
+      <c r="I47" s="34" t="inlineStr">
+        <is>
+          <t>קניות קלות, קפה וגלידה במקום מקורה.</t>
+        </is>
+      </c>
+      <c r="J47" s="34" t="inlineStr">
+        <is>
+          <t>Forum: 2 שעות ראשונות חינם ביום חול.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1" s="6">
+      <c r="A48" s="34" t="inlineStr">
+        <is>
+          <t>24.9.2026 – חלופה</t>
+        </is>
+      </c>
+      <c r="B48" s="35" t="inlineStr">
+        <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="C47" s="34" t="inlineStr">
+      <c r="C48" s="34" t="inlineStr">
         <is>
           <t>Poprad – Forum / מרכז</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Hotel International</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
-      <c r="F47" s="35" t="inlineStr">
+      <c r="F48" s="35" t="inlineStr">
         <is>
           <t>15–20 דק׳</t>
         </is>
       </c>
-      <c r="G47" s="35" t="inlineStr">
+      <c r="G48" s="35" t="inlineStr">
         <is>
           <t>ערב</t>
         </is>
       </c>
-      <c r="H47" s="35" t="inlineStr">
+      <c r="H48" s="35" t="inlineStr">
         <is>
           <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
-      <c r="I47" s="34" t="inlineStr">
+      <c r="I48" s="34" t="inlineStr">
         <is>
           <t>חזרה לספא וארוחת ערב.</t>
         </is>
       </c>
-      <c r="J47" s="34" t="inlineStr">
+      <c r="J48" s="34" t="inlineStr">
         <is>
           <t>אם מזג האוויר משתפר אפשר להוסיף עצירה קצרה בתצפית.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1" s="6">
-      <c r="A48" s="36" t="inlineStr">
+    <row r="49" ht="28" customHeight="1" s="6">
+      <c r="A49" s="36" t="inlineStr">
         <is>
           <t>Google Maps לחלופה</t>
         </is>
       </c>
-      <c r="B48" s="37" t="n"/>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="B49" s="37" t="n"/>
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
         </is>
       </c>
-      <c r="D48" s="37" t="n"/>
-      <c r="E48" s="37" t="n"/>
-      <c r="F48" s="37" t="n"/>
-      <c r="G48" s="37" t="n"/>
-      <c r="H48" s="37" t="n"/>
-      <c r="I48" s="37" t="n"/>
-      <c r="J48" s="37" t="n"/>
-    </row>
-    <row r="49" ht="28" customHeight="1" s="6">
-      <c r="A49" s="39" t="inlineStr">
+      <c r="D49" s="37" t="n"/>
+      <c r="E49" s="37" t="n"/>
+      <c r="F49" s="37" t="n"/>
+      <c r="G49" s="37" t="n"/>
+      <c r="H49" s="37" t="n"/>
+      <c r="I49" s="37" t="n"/>
+      <c r="J49" s="37" t="n"/>
+    </row>
+    <row r="50" ht="8" customHeight="1" s="6">
+      <c r="A50" s="39" t="inlineStr">
         <is>
           <t>עלות החלופה ל-4: Belianska Cave: €60 ל־4; Kežmarok/Poprad ללא כניסה חובה.</t>
         </is>
       </c>
-      <c r="B49" s="18" t="n"/>
-      <c r="C49" s="18" t="n"/>
-      <c r="D49" s="18" t="n"/>
-      <c r="E49" s="18" t="n"/>
-      <c r="F49" s="18" t="n"/>
-      <c r="G49" s="18" t="n"/>
-      <c r="H49" s="18" t="n"/>
-      <c r="I49" s="18" t="n"/>
-      <c r="J49" s="19" t="n"/>
-    </row>
-    <row r="50" ht="8" customHeight="1" s="6"/>
-    <row r="51" ht="28" customHeight="1" s="6">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="18" t="n"/>
+      <c r="D50" s="18" t="n"/>
+      <c r="E50" s="18" t="n"/>
+      <c r="F50" s="18" t="n"/>
+      <c r="G50" s="18" t="n"/>
+      <c r="H50" s="18" t="n"/>
+      <c r="I50" s="18" t="n"/>
+      <c r="J50" s="19" t="n"/>
+    </row>
+    <row r="51" ht="28" customHeight="1" s="6"/>
+    <row r="52" ht="58" customHeight="1" s="6">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>יום ו׳ | 25.9.2026 | Suchá Belá – נקיק הסולמות, ולאחריו Tatrabob</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="58" customHeight="1" s="6">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>25.9.2026 – יום ו׳</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Podlesok – Suchá Belá</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Podlesok, Slovenský raj</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>45–60 דק׳</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>20–30 דק׳</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>€16 ל־4 כניסת Suchá Belá + חניה בנפרד</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>נסיעה לנקודת ההתחלה וחניה.</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>להגיע מוקדם לפני העומס על הסולמות.</t>
         </is>
       </c>
     </row>
@@ -2509,47 +2513,43 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
         <is>
           <t>Podlesok – Suchá Belá</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Suchá Belá Gorge</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Suchá Belá, Podlesok</t>
+          <t>Podlesok, Slovenský raj</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45–60 דק׳</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>4:00–5:00 ש׳</t>
+          <t>20–30 דק׳</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>€16 ל־4 (4€ לאדם)</t>
+          <t>€16 ל־4 כניסת Suchá Belá + חניה בנפרד</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>נקיק צר עם מפלים, גשרי עץ וסולמות מתכת גבוהים.</t>
+          <t>Podlesok הוא החניון ונקודת היציאה ל־Suchá Belá. מחנים ומתארגנים ומכאן יוצאים ברגל לערוץ.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>מסלול חד־כיווני; נעלי הליכה חובה ולא בגשם חזק.</t>
+          <t>להגיע מוקדם לפני העומס על הסולמות.</t>
         </is>
       </c>
     </row>
@@ -2561,22 +2561,22 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>Podlesok – Suchá Belá</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>Suchá Belá Gorge</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים ב־Podlesok</t>
-        </is>
-      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Podlesok</t>
+          <t>Suchá Belá, Podlesok</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2586,22 +2586,22 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>45–60 דק׳</t>
+          <t>4:00–5:00 ש׳</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>€16 ל־4 כניסת Suchá Belá + חניה בנפרד</t>
+          <t>€16 ל־4 (4€ לאדם)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>ארוחה ומנוחה לאחר המסלול.</t>
+          <t>נקיק צר עם מפלים, גשרי עץ וסולמות מתכת גבוהים.</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>לא להתעכב כדי להספיק את המגלשה.</t>
+          <t>מסלול חד־כיווני; נעלי הליכה חובה ולא בגשם חזק.</t>
         </is>
       </c>
     </row>
@@ -2613,27 +2613,27 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>Suchá Belá Gorge</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>ארוחת צהריים ב־Podlesok</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Tatrabob – Tatranská Lomnica</t>
-        </is>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tatrabob Tatranská Lomnica</t>
+          <t>Podlesok</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>45–55 דק׳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -2643,17 +2643,17 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>€36 ל־4 לסיבוב אחד (9€ לאדם)</t>
+          <t>€16 ל־4 כניסת Suchá Belá + חניה בנפרד</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>מגלשת הרים על מסילה עם שליטה אישית במהירות.</t>
+          <t>מנוחה קצרה, שתייה, קפה/מאפה או נשנוש אחרי המסלול.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>לבדוק שעות פעילות ומזג אוויר סמוך ליום.</t>
+          <t>לא ארוחת צהריים מלאה – שומרים זמן ל־Tatrabob ולחזרה למלון סביב 17:00.</t>
         </is>
       </c>
     </row>
@@ -2665,143 +2665,147 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים ב־Podlesok</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Tatrabob – Tatranská Lomnica</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Tatrabob Tatranská Lomnica</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>45–55 דק׳</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>45–60 דק׳</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>€36 ל־4 לסיבוב אחד (9€ לאדם)</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>מגלשת הרים על מסילה עם שליטה אישית במהירות.</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>לבדוק שעות פעילות ומזג אוויר סמוך ליום.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1" s="6">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>25.9.2026 – יום ו׳</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Tatrabob – Tatranská Lomnica</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Hotel International</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Hotel International</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>10–15 דק׳</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>ערב</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>חזרה למלון, ספא וארוחת ערב.</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>המגלשה קרובה למלון ולכן משתלבת היטב.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1" s="6">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Google Maps ליום</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" s="6">
       <c r="A58" s="4" t="inlineStr">
         <is>
+          <t>Google Maps ליום</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1" s="6">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
           <t>לינה בסוף היום</t>
         </is>
       </c>
-      <c r="C58" s="15" t="inlineStr">
+      <c r="C59" s="15" t="inlineStr">
         <is>
           <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="28" customHeight="1" s="6">
-      <c r="A59" s="16" t="inlineStr">
+    <row r="60" ht="6" customHeight="1" s="6">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>עלות משוערת ליום ל-4: Suchá Belá €16 ל־4 + Tatrabob €36 ל־4 לסיבוב אחד = כ־€52 + חניה.</t>
         </is>
       </c>
-      <c r="B59" s="18" t="n"/>
-      <c r="C59" s="18" t="n"/>
-      <c r="D59" s="18" t="n"/>
-      <c r="E59" s="18" t="n"/>
-      <c r="F59" s="18" t="n"/>
-      <c r="G59" s="18" t="n"/>
-      <c r="H59" s="18" t="n"/>
-      <c r="I59" s="18" t="n"/>
-      <c r="J59" s="19" t="n"/>
-    </row>
-    <row r="60" ht="6" customHeight="1" s="6"/>
-    <row r="61" ht="32" customHeight="1" s="6">
-      <c r="A61" s="32" t="inlineStr">
+      <c r="B60" s="18" t="n"/>
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="18" t="n"/>
+      <c r="H60" s="18" t="n"/>
+      <c r="I60" s="18" t="n"/>
+      <c r="J60" s="19" t="n"/>
+    </row>
+    <row r="61" ht="32" customHeight="1" s="6"/>
+    <row r="62" ht="58" customHeight="1" s="6">
+      <c r="A62" s="32" t="inlineStr">
         <is>
           <t>חלופה | 25.9 חלופה – פסגות | חלופה ל־Suchá Belá: יום פסגות – Skalnaté Pleso, Lomnický štít / Lomnické sedlo, Veľká Svišťovka ו־Mountain Carts</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="58" customHeight="1" s="6">
-      <c r="A62" s="34" t="inlineStr">
-        <is>
-          <t>25.9.2026 – חלופה</t>
-        </is>
-      </c>
-      <c r="B62" s="35" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="C62" s="34" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Tatranská Lomnica – חניה ורכבל</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Tatranská Lomnica Cable Car</t>
-        </is>
-      </c>
-      <c r="F62" s="35" t="inlineStr">
-        <is>
-          <t>10–15 דק׳</t>
-        </is>
-      </c>
-      <c r="G62" s="35" t="inlineStr">
-        <is>
-          <t>20–30 דק׳</t>
-        </is>
-      </c>
-      <c r="H62" s="35" t="inlineStr">
-        <is>
-          <t>חניה חינם ב־Eurocamp או כ־€10 ליום ליד הרכבל</t>
-        </is>
-      </c>
-      <c r="I62" s="34" t="inlineStr">
-        <is>
-          <t>חניה והתארגנות לרכבלים.</t>
-        </is>
-      </c>
-      <c r="J62" s="34" t="inlineStr">
-        <is>
-          <t>אפשר חניה חינם ב־Eurocamp או חניה בתשלום ליד הרכבל.</t>
         </is>
       </c>
     </row>
@@ -2813,47 +2817,43 @@
       </c>
       <c r="B63" s="35" t="inlineStr">
         <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="C63" s="34" t="inlineStr">
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C63" s="34" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
         <is>
           <t>Tatranská Lomnica – חניה ורכבל</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Skalnaté Pleso</t>
-        </is>
-      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Skalnaté Pleso</t>
+          <t>Tatranská Lomnica Cable Car</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>רכבל</t>
+          <t>10–15 דק׳</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
         <is>
-          <t>45–60 דק׳</t>
+          <t>20–30 דק׳</t>
         </is>
       </c>
       <c r="H63" s="35" t="inlineStr">
         <is>
-          <t>מחיר Gopass דינמי</t>
+          <t>חניה חינם ב־Eurocamp או כ־€10 ליום ליד הרכבל</t>
         </is>
       </c>
       <c r="I63" s="34" t="inlineStr">
         <is>
-          <t>עלייה לאגם האלפיני בגובה כ־1,751 מ׳.</t>
+          <t>חניה והתארגנות לרכבלים.</t>
         </is>
       </c>
       <c r="J63" s="34" t="inlineStr">
         <is>
-          <t>להזמין Gopass מראש אם אפשר.</t>
+          <t>אפשר חניה חינם ב־Eurocamp או חניה בתשלום ליד הרכבל.</t>
         </is>
       </c>
     </row>
@@ -2865,47 +2865,47 @@
       </c>
       <c r="B64" s="35" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
+          <t>Tatranská Lomnica – חניה ורכבל</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>Skalnaté Pleso</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Lomnický štít – אם יש כרטיס</t>
-        </is>
-      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lomnický štít</t>
+          <t>Skalnaté Pleso</t>
         </is>
       </c>
       <c r="F64" s="35" t="inlineStr">
         <is>
-          <t>רכבל מיוחד</t>
+          <t>רכבל</t>
         </is>
       </c>
       <c r="G64" s="35" t="inlineStr">
         <is>
-          <t>60–90 דק׳</t>
+          <t>45–60 דק׳</t>
         </is>
       </c>
       <c r="H64" s="35" t="inlineStr">
         <is>
-          <t>מחיר Gopass דינמי – חובה לבדוק/להזמין מראש</t>
+          <t>מחיר Gopass דינמי</t>
         </is>
       </c>
       <c r="I64" s="34" t="inlineStr">
         <is>
-          <t>פסגת לומניצקי בגובה 2,634 מ׳ – תצפית ה־WOW של היום.</t>
+          <t>עלייה לאגם האלפיני בגובה כ־1,751 מ׳.</t>
         </is>
       </c>
       <c r="J64" s="34" t="inlineStr">
         <is>
-          <t>השעה בכרטיס היא היציאה מ־Skalnaté Pleso; קיבולת מוגבלת.</t>
+          <t>להזמין Gopass מראש אם אפשר.</t>
         </is>
       </c>
     </row>
@@ -2917,47 +2917,47 @@
       </c>
       <c r="B65" s="35" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C65" s="34" t="inlineStr">
         <is>
+          <t>Skalnaté Pleso</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>Lomnický štít – אם יש כרטיס</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Lomnické sedlo</t>
-        </is>
-      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lomnické sedlo</t>
+          <t>Lomnický štít</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>רכבל כיסאות</t>
+          <t>רכבל מיוחד</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
         <is>
-          <t>60–75 דק׳</t>
+          <t>60–90 דק׳</t>
         </is>
       </c>
       <c r="H65" s="35" t="inlineStr">
         <is>
-          <t>מחיר Gopass דינמי</t>
+          <t>מחיר Gopass דינמי – חובה לבדוק/להזמין מראש</t>
         </is>
       </c>
       <c r="I65" s="34" t="inlineStr">
         <is>
-          <t>אוכף הרים בגובה כ־2,190 מ׳ עם נוף חד לפסגות.</t>
+          <t>פסגת לומניצקי בגובה 2,634 מ׳ – תצפית ה־WOW של היום.</t>
         </is>
       </c>
       <c r="J65" s="34" t="inlineStr">
         <is>
-          <t>אם עלינו ל־Lomnický štít והזמן קצר – אפשר לקצר כאן.</t>
+          <t>השעה בכרטיס היא היציאה מ־Skalnaté Pleso; קיבולת מוגבלת.</t>
         </is>
       </c>
     </row>
@@ -2969,47 +2969,47 @@
       </c>
       <c r="B66" s="35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
+          <t>Lomnický štít – אם יש כרטיס</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>Lomnické sedlo</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Veľká Svišťovka – אופציונלי</t>
-        </is>
-      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Veľká Svišťovka</t>
+          <t>Lomnické sedlo</t>
         </is>
       </c>
       <c r="F66" s="35" t="inlineStr">
         <is>
-          <t>הליכה</t>
+          <t>רכבל כיסאות</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
         <is>
-          <t>2:30–3:00 ש׳</t>
+          <t>60–75 דק׳</t>
         </is>
       </c>
       <c r="H66" s="35" t="inlineStr">
         <is>
-          <t>חינם – מסלול הליכה</t>
+          <t>מחיר Gopass דינמי</t>
         </is>
       </c>
       <c r="I66" s="34" t="inlineStr">
         <is>
-          <t>מסלול הררי ותצפיות גבוהות; לבצע רק בתנאים יבשים.</t>
+          <t>אוכף הרים בגובה כ־2,190 מ׳ עם נוף חד לפסגות.</t>
         </is>
       </c>
       <c r="J66" s="34" t="inlineStr">
         <is>
-          <t>לא לבצע בערפל/גשם/סלע רטוב. אם יש פסגה + עומס, לוותר.</t>
+          <t>אם עלינו ל־Lomnický štít והזמן קצר – אפשר לקצר כאן.</t>
         </is>
       </c>
     </row>
@@ -3021,47 +3021,47 @@
       </c>
       <c r="B67" s="35" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C67" s="34" t="inlineStr">
         <is>
+          <t>Lomnické sedlo</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t>Veľká Svišťovka – אופציונלי</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Štart / Mountain Carts</t>
-        </is>
-      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mountain Carts Tatranská Lomnica</t>
+          <t>Veľká Svišťovka</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>רכבל</t>
+          <t>הליכה</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
         <is>
-          <t>30–45 דק׳</t>
+          <t>2:30–3:00 ש׳</t>
         </is>
       </c>
       <c r="H67" s="35" t="inlineStr">
         <is>
-          <t>מחיר משתנה – לבדוק ב־Gopass/באתר ביום הקנייה</t>
+          <t>חינם – מסלול הליכה</t>
         </is>
       </c>
       <c r="I67" s="34" t="inlineStr">
         <is>
-          <t>ירידה חווייתית במסלול אספלט של כ־3 ק״מ.</t>
+          <t>מסלול הררי ותצפיות גבוהות; לבצע רק בתנאים יבשים.</t>
         </is>
       </c>
       <c r="J67" s="34" t="inlineStr">
         <is>
-          <t>אופציונלי ובכפוף לפעילות ומזג אוויר.</t>
+          <t>לא לבצע בערפל/גשם/סלע רטוב. אם יש פסגה + עומס, לוותר.</t>
         </is>
       </c>
     </row>
@@ -3073,27 +3073,27 @@
       </c>
       <c r="B68" s="35" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C68" s="34" t="inlineStr">
         <is>
+          <t>Veľká Svišťovka – אופציונלי</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
           <t>Štart / Mountain Carts</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Starý Smokovec – רק אם נשאר זמן</t>
-        </is>
-      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Starý Smokovec</t>
+          <t>Mountain Carts Tatranská Lomnica</t>
         </is>
       </c>
       <c r="F68" s="35" t="inlineStr">
         <is>
-          <t>15–20 דק׳</t>
+          <t>רכבל</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="H68" s="35" t="inlineStr">
         <is>
-          <t>חינם לסיבוב בעיירה</t>
+          <t>מחיר משתנה – לבדוק ב־Gopass/באתר ביום הקנייה</t>
         </is>
       </c>
       <c r="I68" s="34" t="inlineStr">
         <is>
-          <t>קפה/גלידה וסיבוב קצר בעיירה.</t>
+          <t>ירידה חווייתית במסלול אספלט של כ־3 ק״מ.</t>
         </is>
       </c>
       <c r="J68" s="34" t="inlineStr">
         <is>
-          <t>אם היום בהר התארך – חוזרים ישר למלון.</t>
+          <t>אופציונלי ובכפוף לפעילות ומזג אוויר.</t>
         </is>
       </c>
     </row>
@@ -3125,139 +3125,143 @@
       </c>
       <c r="B69" s="35" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C69" s="34" t="inlineStr">
+        <is>
+          <t>Štart / Mountain Carts</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Starý Smokovec – רק אם נשאר זמן</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Starý Smokovec</t>
+        </is>
+      </c>
+      <c r="F69" s="35" t="inlineStr">
+        <is>
+          <t>15–20 דק׳</t>
+        </is>
+      </c>
+      <c r="G69" s="35" t="inlineStr">
+        <is>
+          <t>30–45 דק׳</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>חינם לסיבוב בעיירה</t>
+        </is>
+      </c>
+      <c r="I69" s="34" t="inlineStr">
+        <is>
+          <t>קפה/גלידה וסיבוב קצר בעיירה.</t>
+        </is>
+      </c>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>אם היום בהר התארך – חוזרים ישר למלון.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1" s="6">
+      <c r="A70" s="34" t="inlineStr">
+        <is>
+          <t>25.9.2026 – חלופה</t>
+        </is>
+      </c>
+      <c r="B70" s="35" t="inlineStr">
+        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="C69" s="34" t="inlineStr">
+      <c r="C70" s="34" t="inlineStr">
         <is>
           <t>Starý Smokovec – רק אם נשאר זמן</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Hotel International</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
-      <c r="F69" s="35" t="inlineStr">
+      <c r="F70" s="35" t="inlineStr">
         <is>
           <t>20–25 דק׳</t>
         </is>
       </c>
-      <c r="G69" s="35" t="inlineStr">
+      <c r="G70" s="35" t="inlineStr">
         <is>
           <t>ערב</t>
         </is>
       </c>
-      <c r="H69" s="35" t="inlineStr">
+      <c r="H70" s="35" t="inlineStr">
         <is>
           <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
-      <c r="I69" s="34" t="inlineStr">
+      <c r="I70" s="34" t="inlineStr">
         <is>
           <t>חזרה למלון, ספא וארוחת ערב.</t>
         </is>
       </c>
-      <c r="J69" s="34" t="inlineStr">
+      <c r="J70" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1" s="6">
-      <c r="A70" s="36" t="inlineStr">
+    <row r="71" ht="28" customHeight="1" s="6">
+      <c r="A71" s="36" t="inlineStr">
         <is>
           <t>Google Maps לחלופה</t>
         </is>
       </c>
-      <c r="B70" s="37" t="n"/>
-      <c r="C70" s="15" t="inlineStr">
+      <c r="B71" s="37" t="n"/>
+      <c r="C71" s="15" t="inlineStr">
         <is>
           <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
         </is>
       </c>
-      <c r="D70" s="37" t="n"/>
-      <c r="E70" s="37" t="n"/>
-      <c r="F70" s="37" t="n"/>
-      <c r="G70" s="37" t="n"/>
-      <c r="H70" s="37" t="n"/>
-      <c r="I70" s="37" t="n"/>
-      <c r="J70" s="37" t="n"/>
-    </row>
-    <row r="71" ht="28" customHeight="1" s="6">
-      <c r="A71" s="39" t="inlineStr">
+      <c r="D71" s="37" t="n"/>
+      <c r="E71" s="37" t="n"/>
+      <c r="F71" s="37" t="n"/>
+      <c r="G71" s="37" t="n"/>
+      <c r="H71" s="37" t="n"/>
+      <c r="I71" s="37" t="n"/>
+      <c r="J71" s="37" t="n"/>
+    </row>
+    <row r="72" ht="6" customHeight="1" s="6">
+      <c r="A72" s="39" t="inlineStr">
         <is>
           <t>עלות החלופה ל-4: כ־€220–360 ל־4 לפי כרטיסי הרכבל והאם עולים ל־Lomnický štít</t>
         </is>
       </c>
-      <c r="B71" s="18" t="n"/>
-      <c r="C71" s="18" t="n"/>
-      <c r="D71" s="18" t="n"/>
-      <c r="E71" s="18" t="n"/>
-      <c r="F71" s="18" t="n"/>
-      <c r="G71" s="18" t="n"/>
-      <c r="H71" s="18" t="n"/>
-      <c r="I71" s="18" t="n"/>
-      <c r="J71" s="19" t="n"/>
-    </row>
-    <row r="72" ht="6" customHeight="1" s="6"/>
-    <row r="73" ht="32" customHeight="1" s="6">
-      <c r="A73" s="32" t="inlineStr">
+      <c r="B72" s="18" t="n"/>
+      <c r="C72" s="18" t="n"/>
+      <c r="D72" s="18" t="n"/>
+      <c r="E72" s="18" t="n"/>
+      <c r="F72" s="18" t="n"/>
+      <c r="G72" s="18" t="n"/>
+      <c r="H72" s="18" t="n"/>
+      <c r="I72" s="18" t="n"/>
+      <c r="J72" s="19" t="n"/>
+    </row>
+    <row r="73" ht="32" customHeight="1" s="6"/>
+    <row r="74" ht="58" customHeight="1" s="6">
+      <c r="A74" s="32" t="inlineStr">
         <is>
           <t>חלופה | 25.9 חלופה רגועה – Štrbské Pleso | חלופה רגועה / ראות בינונית: Štrbské Pleso – אגם, הליכה וקפה</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="58" customHeight="1" s="6">
-      <c r="A74" s="34" t="inlineStr">
-        <is>
-          <t>25.9.2026 – חלופה</t>
-        </is>
-      </c>
-      <c r="B74" s="35" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C74" s="34" t="inlineStr"/>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Štrbské Pleso – חניה</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Central parking Štrbské Pleso</t>
-        </is>
-      </c>
-      <c r="F74" s="35" t="inlineStr">
-        <is>
-          <t>🚗 35–45 דק׳</t>
-        </is>
-      </c>
-      <c r="G74" s="35" t="inlineStr">
-        <is>
-          <t>10–15 דק׳</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>כ־€12 לרכב (חניה; לבדוק במקום)</t>
-        </is>
-      </c>
-      <c r="I74" s="34" t="inlineStr">
-        <is>
-          <t>מחנים ליד מרכז העיירה ויוצאים ברגל לאגם.</t>
-        </is>
-      </c>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>החניה שדווחה ע״י מטיילים הייתה כ־€12 ליום; לבדוק תעריף במקום.</t>
         </is>
       </c>
     </row>
@@ -3269,47 +3273,43 @@
       </c>
       <c r="B75" s="35" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C75" s="34" t="inlineStr">
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C75" s="34" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
         <is>
           <t>Štrbské Pleso – חניה</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Štrbské Pleso – סיבוב סביב האגם</t>
-        </is>
-      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Štrbské Pleso</t>
+          <t>Central parking Štrbské Pleso</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>🚶 5–10 דק׳</t>
+          <t>🚗 35–45 דק׳</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
         <is>
-          <t>1:15–1:45 ש׳</t>
+          <t>10–15 דק׳</t>
         </is>
       </c>
       <c r="H75" s="35" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>כ־€12 לרכב (חניה; לבדוק במקום)</t>
         </is>
       </c>
       <c r="I75" s="34" t="inlineStr">
         <is>
-          <t>הליכה קלה סביב האגם האלפיני, תצפיות לפסגות, צילום וקפה.</t>
+          <t>מחנים ליד מרכז העיירה ויוצאים ברגל לאגם.</t>
         </is>
       </c>
       <c r="J75" s="34" t="inlineStr">
         <is>
-          <t>מסלול נוח וגמיש; אפשר לקצר בכל שלב.</t>
+          <t>החניה שדווחה ע״י מטיילים הייתה כ־€12 ליום; לבדוק תעריף במקום.</t>
         </is>
       </c>
     </row>
@@ -3321,19 +3321,19 @@
       </c>
       <c r="B76" s="35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C76" s="34" t="inlineStr">
         <is>
+          <t>Štrbské Pleso – חניה</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
           <t>Štrbské Pleso – סיבוב סביב האגם</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>קפה / דוכנים ליד האגם</t>
-        </is>
-      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>Štrbské Pleso</t>
@@ -3341,27 +3341,27 @@
       </c>
       <c r="F76" s="35" t="inlineStr">
         <is>
-          <t>🚶 2–5 דק׳</t>
+          <t>🚶 5–10 דק׳</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
         <is>
-          <t>45–60 דק׳</t>
+          <t>1:15–1:45 ש׳</t>
         </is>
       </c>
       <c r="H76" s="35" t="inlineStr">
         <is>
-          <t>לפי הזמנה</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I76" s="34" t="inlineStr">
         <is>
-          <t>קפה, מאפה והפסקה מול הנוף.</t>
+          <t>הליכה קלה סביב האגם האלפיני, תצפיות לפסגות, צילום וקפה.</t>
         </is>
       </c>
       <c r="J76" s="34" t="inlineStr">
         <is>
-          <t>ללא התחייבות לאטרקציה נוספת.</t>
+          <t>מסלול נוח וגמיש; אפשר לקצר בכל שלב.</t>
         </is>
       </c>
     </row>
@@ -3373,47 +3373,47 @@
       </c>
       <c r="B77" s="35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C77" s="34" t="inlineStr">
         <is>
+          <t>Štrbské Pleso – סיבוב סביב האגם</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>קפה / דוכנים ליד האגם</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Solisko – אופציונלי רק אם הראות טובה</t>
-        </is>
-      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Solisko Express Štrbské Pleso</t>
+          <t>Štrbské Pleso</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>🚶 10–15 דק׳</t>
+          <t>🚶 2–5 דק׳</t>
         </is>
       </c>
       <c r="G77" s="35" t="inlineStr">
         <is>
-          <t>1:30–2:00 ש׳</t>
+          <t>45–60 דק׳</t>
         </is>
       </c>
       <c r="H77" s="35" t="inlineStr">
         <is>
-          <t>מחיר Gopass דינמי – לבדוק ביום הקנייה</t>
+          <t>לפי הזמנה</t>
         </is>
       </c>
       <c r="I77" s="34" t="inlineStr">
         <is>
-          <t>רכבל כיסאות לתצפיות גבוהות מעל Štrbské Pleso, רק אם העננות נפתחת.</t>
+          <t>קפה, מאפה והפסקה מול הנוף.</t>
         </is>
       </c>
       <c r="J77" s="34" t="inlineStr">
         <is>
-          <t>לא חובה; מחיר הכרטיס דינמי ב־Gopass ולכן מחליטים במקום/יום קודם.</t>
+          <t>ללא התחייבות לאטרקציה נוספת.</t>
         </is>
       </c>
     </row>
@@ -3425,139 +3425,143 @@
       </c>
       <c r="B78" s="35" t="inlineStr">
         <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C78" s="34" t="inlineStr">
+        <is>
+          <t>קפה / דוכנים ליד האגם</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Solisko – אופציונלי רק אם הראות טובה</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Solisko Express Štrbské Pleso</t>
+        </is>
+      </c>
+      <c r="F78" s="35" t="inlineStr">
+        <is>
+          <t>🚶 10–15 דק׳</t>
+        </is>
+      </c>
+      <c r="G78" s="35" t="inlineStr">
+        <is>
+          <t>1:30–2:00 ש׳</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>מחיר Gopass דינמי – לבדוק ביום הקנייה</t>
+        </is>
+      </c>
+      <c r="I78" s="34" t="inlineStr">
+        <is>
+          <t>רכבל כיסאות לתצפיות גבוהות מעל Štrbské Pleso, רק אם העננות נפתחת.</t>
+        </is>
+      </c>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>לא חובה; מחיר הכרטיס דינמי ב־Gopass ולכן מחליטים במקום/יום קודם.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1" s="6">
+      <c r="A79" s="34" t="inlineStr">
+        <is>
+          <t>25.9.2026 – חלופה</t>
+        </is>
+      </c>
+      <c r="B79" s="35" t="inlineStr">
+        <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="C78" s="34" t="inlineStr">
+      <c r="C79" s="34" t="inlineStr">
         <is>
           <t>Solisko – אופציונלי רק אם הראות טובה</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Hotel International</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
-      <c r="F78" s="35" t="inlineStr">
+      <c r="F79" s="35" t="inlineStr">
         <is>
           <t>🚗 35–45 דק׳</t>
         </is>
       </c>
-      <c r="G78" s="35" t="inlineStr">
+      <c r="G79" s="35" t="inlineStr">
         <is>
           <t>אחה״צ/ערב</t>
         </is>
       </c>
-      <c r="H78" s="35" t="inlineStr">
+      <c r="H79" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I78" s="34" t="inlineStr">
+      <c r="I79" s="34" t="inlineStr">
         <is>
           <t>חזרה מוקדמת יחסית לספא, מנוחה וארוחת ערב.</t>
         </is>
       </c>
-      <c r="J78" s="34" t="inlineStr">
+      <c r="J79" s="34" t="inlineStr">
         <is>
           <t>חלופה רגועה בכוונה.</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="20" customHeight="1" s="6">
-      <c r="A79" s="36" t="inlineStr">
+    <row r="80" ht="28" customHeight="1" s="6">
+      <c r="A80" s="36" t="inlineStr">
         <is>
           <t>Google Maps לחלופה</t>
         </is>
       </c>
-      <c r="B79" s="37" t="n"/>
-      <c r="C79" s="15" t="inlineStr">
+      <c r="B80" s="37" t="n"/>
+      <c r="C80" s="15" t="inlineStr">
         <is>
           <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
         </is>
       </c>
-      <c r="D79" s="37" t="n"/>
-      <c r="E79" s="37" t="n"/>
-      <c r="F79" s="37" t="n"/>
-      <c r="G79" s="37" t="n"/>
-      <c r="H79" s="37" t="n"/>
-      <c r="I79" s="37" t="n"/>
-      <c r="J79" s="37" t="n"/>
-    </row>
-    <row r="80" ht="28" customHeight="1" s="6">
-      <c r="A80" s="39" t="inlineStr">
+      <c r="D80" s="37" t="n"/>
+      <c r="E80" s="37" t="n"/>
+      <c r="F80" s="37" t="n"/>
+      <c r="G80" s="37" t="n"/>
+      <c r="H80" s="37" t="n"/>
+      <c r="I80" s="37" t="n"/>
+      <c r="J80" s="37" t="n"/>
+    </row>
+    <row r="81" ht="6" customHeight="1" s="6">
+      <c r="A81" s="39" t="inlineStr">
         <is>
           <t>עלות החלופה ל-4: האגם וההליכה חינם; חניה כ־€12 לרכב לפי דיווח מטיילים. רכבל Solisko רק אם מחליטים במקום – מחיר Gopass דינמי.</t>
         </is>
       </c>
-      <c r="B80" s="18" t="n"/>
-      <c r="C80" s="18" t="n"/>
-      <c r="D80" s="18" t="n"/>
-      <c r="E80" s="18" t="n"/>
-      <c r="F80" s="18" t="n"/>
-      <c r="G80" s="18" t="n"/>
-      <c r="H80" s="18" t="n"/>
-      <c r="I80" s="18" t="n"/>
-      <c r="J80" s="19" t="n"/>
-    </row>
-    <row r="81" ht="6" customHeight="1" s="6"/>
-    <row r="82" ht="32" customHeight="1" s="6">
-      <c r="A82" s="32" t="inlineStr">
+      <c r="B81" s="18" t="n"/>
+      <c r="C81" s="18" t="n"/>
+      <c r="D81" s="18" t="n"/>
+      <c r="E81" s="18" t="n"/>
+      <c r="F81" s="18" t="n"/>
+      <c r="G81" s="18" t="n"/>
+      <c r="H81" s="18" t="n"/>
+      <c r="I81" s="18" t="n"/>
+      <c r="J81" s="19" t="n"/>
+    </row>
+    <row r="82" ht="32" customHeight="1" s="6"/>
+    <row r="83" ht="58" customHeight="1" s="6">
+      <c r="A83" s="32" t="inlineStr">
         <is>
           <t>חלופה | 25.9 חלופת גשם | חלופת גשם/עננות כבדה: Levoča, Spiš Castle ו־Kežmarok</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="58" customHeight="1" s="6">
-      <c r="A83" s="34" t="inlineStr">
-        <is>
-          <t>25.9.2026 – חלופה</t>
-        </is>
-      </c>
-      <c r="B83" s="35" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C83" s="34" t="inlineStr"/>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Levoča – העיר העתיקה</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Košická brána, Levoča</t>
-        </is>
-      </c>
-      <c r="F83" s="35" t="inlineStr">
-        <is>
-          <t>30–35 דק׳</t>
-        </is>
-      </c>
-      <c r="G83" s="35" t="inlineStr">
-        <is>
-          <t>1:30 ש׳</t>
-        </is>
-      </c>
-      <c r="H83" s="35" t="inlineStr">
-        <is>
-          <t>העיר העתיקה חינם</t>
-        </is>
-      </c>
-      <c r="I83" s="34" t="inlineStr">
-        <is>
-          <t>כיכר Majstra Pavla, חומות, רחובות עתיקים וקפה.</t>
-        </is>
-      </c>
-      <c r="J83" s="34" t="inlineStr">
-        <is>
-          <t>עדיפות לחניוני P+R החינמיים ליד Košická brána.</t>
         </is>
       </c>
     </row>
@@ -3569,47 +3573,43 @@
       </c>
       <c r="B84" s="35" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="C84" s="34" t="inlineStr">
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C84" s="34" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
         <is>
           <t>Levoča – העיר העתיקה</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Spiš Castle</t>
-        </is>
-      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Spišský hrad</t>
+          <t>Košická brána, Levoča</t>
         </is>
       </c>
       <c r="F84" s="35" t="inlineStr">
         <is>
-          <t>20–25 דק׳</t>
+          <t>30–35 דק׳</t>
         </is>
       </c>
       <c r="G84" s="35" t="inlineStr">
         <is>
-          <t>1:30–2:00 ש׳</t>
+          <t>1:30 ש׳</t>
         </is>
       </c>
       <c r="H84" s="35" t="inlineStr">
         <is>
-          <t>€32 ל־4 (8€ למבוגר)</t>
+          <t>העיר העתיקה חינם</t>
         </is>
       </c>
       <c r="I84" s="34" t="inlineStr">
         <is>
-          <t>אחד ממתחמי הטירות הגדולים במרכז אירופה.</t>
+          <t>כיכר Majstra Pavla, חומות, רחובות עתיקים וקפה.</t>
         </is>
       </c>
       <c r="J84" s="34" t="inlineStr">
         <is>
-          <t>בגשם חזק לא אידיאלי; לבדוק שעות פתיחה יום לפני.</t>
+          <t>עדיפות לחניוני P+R החינמיים ליד Košická brána.</t>
         </is>
       </c>
     </row>
@@ -3621,47 +3621,47 @@
       </c>
       <c r="B85" s="35" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C85" s="34" t="inlineStr">
         <is>
+          <t>Levoča – העיר העתיקה</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>Spiš Castle</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Kežmarok</t>
-        </is>
-      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hradné námestie, Kežmarok</t>
+          <t>Spišský hrad</t>
         </is>
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>35–45 דק׳</t>
+          <t>20–25 דק׳</t>
         </is>
       </c>
       <c r="G85" s="35" t="inlineStr">
         <is>
-          <t>1:30 ש׳</t>
+          <t>1:30–2:00 ש׳</t>
         </is>
       </c>
       <c r="H85" s="35" t="inlineStr">
         <is>
-          <t>המרכז חינם; כניסה לטירה רק אם בוחרים</t>
+          <t>€32 ל־4 (8€ למבוגר)</t>
         </is>
       </c>
       <c r="I85" s="34" t="inlineStr">
         <is>
-          <t>טירה, מרכז עתיק, קפה וארוחת צהריים.</t>
+          <t>אחד ממתחמי הטירות הגדולים במרכז אירופה.</t>
         </is>
       </c>
       <c r="J85" s="34" t="inlineStr">
         <is>
-          <t>חניה מרכזית בתשלום ב־Hradné námestie.</t>
+          <t>בגשם חזק לא אידיאלי; לבדוק שעות פתיחה יום לפני.</t>
         </is>
       </c>
     </row>
@@ -3673,139 +3673,143 @@
       </c>
       <c r="B86" s="35" t="inlineStr">
         <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C86" s="34" t="inlineStr">
+        <is>
+          <t>Spiš Castle</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Kežmarok</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Hradné námestie, Kežmarok</t>
+        </is>
+      </c>
+      <c r="F86" s="35" t="inlineStr">
+        <is>
+          <t>35–45 דק׳</t>
+        </is>
+      </c>
+      <c r="G86" s="35" t="inlineStr">
+        <is>
+          <t>1:30 ש׳</t>
+        </is>
+      </c>
+      <c r="H86" s="35" t="inlineStr">
+        <is>
+          <t>המרכז חינם; כניסה לטירה רק אם בוחרים</t>
+        </is>
+      </c>
+      <c r="I86" s="34" t="inlineStr">
+        <is>
+          <t>טירה, מרכז עתיק, קפה וארוחת צהריים.</t>
+        </is>
+      </c>
+      <c r="J86" s="34" t="inlineStr">
+        <is>
+          <t>חניה מרכזית בתשלום ב־Hradné námestie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1" s="6">
+      <c r="A87" s="34" t="inlineStr">
+        <is>
+          <t>25.9.2026 – חלופה</t>
+        </is>
+      </c>
+      <c r="B87" s="35" t="inlineStr">
+        <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="C86" s="34" t="inlineStr">
+      <c r="C87" s="34" t="inlineStr">
         <is>
           <t>Kežmarok</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Hotel International</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
-      <c r="F86" s="35" t="inlineStr">
+      <c r="F87" s="35" t="inlineStr">
         <is>
           <t>10–15 דק׳</t>
         </is>
       </c>
-      <c r="G86" s="35" t="inlineStr">
+      <c r="G87" s="35" t="inlineStr">
         <is>
           <t>אחה״צ/ערב</t>
         </is>
       </c>
-      <c r="H86" s="35" t="inlineStr">
+      <c r="H87" s="35" t="inlineStr">
         <is>
           <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
-      <c r="I86" s="34" t="inlineStr">
+      <c r="I87" s="34" t="inlineStr">
         <is>
           <t>ספא, בריכה וארוחת ערב.</t>
         </is>
       </c>
-      <c r="J86" s="34" t="inlineStr">
+      <c r="J87" s="34" t="inlineStr">
         <is>
           <t>יום רגוע יותר אם מזג האוויר גרוע.</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1" s="6">
-      <c r="A87" s="36" t="inlineStr">
+    <row r="88" ht="28" customHeight="1" s="6">
+      <c r="A88" s="36" t="inlineStr">
         <is>
           <t>Google Maps לחלופה</t>
         </is>
       </c>
-      <c r="B87" s="37" t="n"/>
-      <c r="C87" s="15" t="inlineStr">
+      <c r="B88" s="37" t="n"/>
+      <c r="C88" s="15" t="inlineStr">
         <is>
           <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
         </is>
       </c>
-      <c r="D87" s="37" t="n"/>
-      <c r="E87" s="37" t="n"/>
-      <c r="F87" s="37" t="n"/>
-      <c r="G87" s="37" t="n"/>
-      <c r="H87" s="37" t="n"/>
-      <c r="I87" s="37" t="n"/>
-      <c r="J87" s="37" t="n"/>
-    </row>
-    <row r="88" ht="28" customHeight="1" s="6">
-      <c r="A88" s="39" t="inlineStr">
+      <c r="D88" s="37" t="n"/>
+      <c r="E88" s="37" t="n"/>
+      <c r="F88" s="37" t="n"/>
+      <c r="G88" s="37" t="n"/>
+      <c r="H88" s="37" t="n"/>
+      <c r="I88" s="37" t="n"/>
+      <c r="J88" s="37" t="n"/>
+    </row>
+    <row r="89" ht="8" customHeight="1" s="6">
+      <c r="A89" s="39" t="inlineStr">
         <is>
           <t>עלות החלופה ל-4: Spiš Castle: €32 ל־4; Levoča/Kežmarok מרכזים חינם.</t>
         </is>
       </c>
-      <c r="B88" s="18" t="n"/>
-      <c r="C88" s="18" t="n"/>
-      <c r="D88" s="18" t="n"/>
-      <c r="E88" s="18" t="n"/>
-      <c r="F88" s="18" t="n"/>
-      <c r="G88" s="18" t="n"/>
-      <c r="H88" s="18" t="n"/>
-      <c r="I88" s="18" t="n"/>
-      <c r="J88" s="19" t="n"/>
-    </row>
-    <row r="89" ht="8" customHeight="1" s="6"/>
-    <row r="90" ht="28" customHeight="1" s="6">
-      <c r="A90" s="10" t="inlineStr">
+      <c r="B89" s="18" t="n"/>
+      <c r="C89" s="18" t="n"/>
+      <c r="D89" s="18" t="n"/>
+      <c r="E89" s="18" t="n"/>
+      <c r="F89" s="18" t="n"/>
+      <c r="G89" s="18" t="n"/>
+      <c r="H89" s="18" t="n"/>
+      <c r="I89" s="18" t="n"/>
+      <c r="J89" s="19" t="n"/>
+    </row>
+    <row r="90" ht="28" customHeight="1" s="6"/>
+    <row r="91" ht="58" customHeight="1" s="6">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>שבת | 26.9.2026 | הטטרה הנמוכים: Jasná, Vrbické pleso, Slide Park Priehyba, Chopok, מערת החירות, Liptovská Mara ו־Hrabovo כאפשרות</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="58" customHeight="1" s="6">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>26.9.2026 – שבת</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Hotel International – יציאה</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Hotel International, Veľká Lomnica</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>יציאה</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>כלול לפי חבילת המלון</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>יציאה מהמלון לאחר ארוחת הבוקר לכיוון הטטרה הנמוכים.</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>לבדוק בבוקר רוח, ראות ופעילות רכבלים ב־Jasná.</t>
         </is>
       </c>
     </row>
@@ -3817,47 +3821,43 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
         <is>
           <t>Hotel International – יציאה</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Jasná – Biela Púť</t>
-        </is>
-      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jasná Biela Púť</t>
+          <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>1:00–1:20 ש׳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>20 דק׳</t>
+          <t>יציאה</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>חניה/רכבל לפי Gopass</t>
+          <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>הגעה למרכז הרכבלים, חניה והתארגנות.</t>
+          <t>יציאה מהמלון לאחר ארוחת הבוקר לכיוון הטטרה הנמוכים.</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>לצאת מוקדם ולבדוק בבוקר רוח, ראות ופעילות רכבלים.</t>
+          <t>לבדוק בבוקר רוח, ראות ופעילות רכבלים ב־Jasná.</t>
         </is>
       </c>
     </row>
@@ -3869,47 +3869,47 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
+          <t>Hotel International – יציאה</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
           <t>Jasná – Biela Púť</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Vrbické pleso</t>
-        </is>
-      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Vrbické pleso, Jasná</t>
+          <t>Jasná Biela Púť</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>5–10 דק׳ / הליכה</t>
+          <t>1:00–1:20 ש׳</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>30–40 דק׳</t>
+          <t>20 דק׳</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>חניה/רכבל לפי Gopass</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>סיבוב קצר סביב אגם הררי בתוך היער, תצפיות וצילומים.</t>
+          <t>הגעה למרכז הרכבלים, חניה והתארגנות.</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>האגם ממש ליד Jasná ולכן זו תוספת יפה בלי נסיעה מיותרת.</t>
+          <t>לצאת מוקדם ולבדוק בבוקר רוח, ראות ופעילות רכבלים.</t>
         </is>
       </c>
     </row>
@@ -3921,47 +3921,47 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
+          <t>Jasná – Biela Púť</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
           <t>Vrbické pleso</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Slide Park Jasná – Priehyba</t>
-        </is>
-      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Priehyba, Jasná</t>
+          <t>Vrbické pleso, Jasná</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>רכבל A6</t>
+          <t>5–10 דק׳ / הליכה</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>30–45 דק׳</t>
+          <t>30–40 דק׳</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>חינם; נדרש להגיע עם הרכבל</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>פארק המגלשות החדש ב־Priehyba עם 7 מגלשות יבשות; עצירה בדרך ל־Chopok.</t>
+          <t>אגם הררי ליד Jasná, למטה ליד החניה. הולכים 10–15 דק׳, מקיפים כ־20 דק׳ וחוזרים. אין צורך ברכבל.</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>הכניסה לפארק חינם; הרכבל לפי הכרטיס. לבדוק סמוך לנסיעה שהפעילות פתוחה.</t>
+          <t>GPS: 48.970831, 19.576958. עושים ברגל מאזור Biela Púť/Grand Jasná וחוזרים לרכבלים בלי להזיז את הרכב.</t>
         </is>
       </c>
     </row>
@@ -3973,47 +3973,47 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="inlineStr">
+        <is>
+          <t>Vrbické pleso</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
         <is>
           <t>Slide Park Jasná – Priehyba</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Chopok</t>
-        </is>
-      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chopok</t>
+          <t>48.970831,19.576958</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>רכבלים</t>
+          <t>🚶 10–15 דק׳</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2:00–2:30 ש׳</t>
+          <t>35–45 דק׳</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>מחיר Gopass דינמי – לבדוק 1–3 ימים לפני</t>
+          <t>חינם; נדרש להגיע עם הרכבל</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>המשך ברכבל לפסגה בגובה כ־2,024 מ׳, תצפית פנורמית וקפה בפסגה.</t>
+          <t>פארק המגלשות החדש ב־Priehyba עם 7 מגלשות יבשות; עצירה בדרך ל־Chopok.</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>להצטייד במעיל; לשים לב לזמן כדי להספיק למערה.</t>
+          <t>הכניסה לפארק חינם; הרכבל לפי הכרטיס. לבדוק סמוך לנסיעה שהפעילות פתוחה.</t>
         </is>
       </c>
     </row>
@@ -4025,47 +4025,47 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
+          <t>Slide Park Jasná – Priehyba</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
           <t>Chopok</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Demänovská Cave of Liberty</t>
-        </is>
-      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Demänovská jaskyňa slobody</t>
+          <t>Chopok</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>15–20 דק׳</t>
+          <t>רכבלים</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>1:30–2:00 ש׳</t>
+          <t>2:00–2:30 ש׳</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>€60 ל־4 – סיור מסורתי (15€ לאדם)</t>
+          <t>מחיר Gopass דינמי – לבדוק 1–3 ימים לפני</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>מערת נטיפים גדולה עם אולמות, נהר תת־קרקעי וסיור מודרך.</t>
+          <t>המשך ברכבל לפסגה בגובה כ־2,024 מ׳, תצפית פנורמית וקפה בפסגה.</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>להגיע לפני שעת הסיור; יש מדרגות והטמפרטורה נמוכה.</t>
+          <t>להצטייד במעיל; לשים לב לזמן כדי להספיק למערה.</t>
         </is>
       </c>
     </row>
@@ -4077,47 +4077,47 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
+          <t>Chopok</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
           <t>Demänovská Cave of Liberty</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Liptovská Mara</t>
-        </is>
-      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Liptovská Mara – Liptovský Trnovec</t>
+          <t>Demänovská jaskyňa slobody</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>25–35 דק׳</t>
+          <t>15–20 דק׳</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>45–60 דק׳</t>
+          <t>1:45–2:00 ש׳</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>€59 ל־4: 3×€15 + Senior 60+ אחד €14</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>אגם גדול, מרינה, תצפיות וקפה לקראת אחר הצהריים.</t>
+          <t>מערת נטיפים מרשימה עם נטיפים, זקיפים, אולמות גדולים ונהר תת־קרקעי. סיור מסורתי מודרך.</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>כאן מחליטים לפי השעה אם ממשיכים ל־Hrabovo.</t>
+          <t>לא להתעכב: צריך להגיע לפני סיור 14:00 במערת החירות.</t>
         </is>
       </c>
     </row>
@@ -4129,147 +4129,143 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>Demänovská Cave of Liberty</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
           <t>Liptovská Mara</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Hrabovo / Malinô Brdo – אופציונלי</t>
-        </is>
-      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hrabovo, Ružomberok</t>
+          <t>Liptovská Mara – Liptovský Trnovec</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>35–45 דק׳</t>
+          <t>🚗 15–20 דק׳ אחרי הירידה מהרכבל</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>1:00–1:30 ש׳</t>
+          <t>כ־60 דק׳ + כניסה/יציאה</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>האגם חינם; רכבל/קארטינג/Tarzania בתשלום לפי בחירה</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>אגם נופש יפה; אם הזמן והפעילות מאפשרים: רכבל ל־Malinô Brdo, Mountain Carts או Tarzania.</t>
+          <t>אגם גדול, מרינה, תצפיות וקפה לקראת אחר הצהריים.</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>אופציונלי בלבד. בסוף ספטמבר לבדוק שעות פעילות מראש; אם אין זמן או שהמתקנים סגורים חוזרים למלון.</t>
+          <t>בספטמבר סיורים: 09:30, 11:00, 12:30, 14:00. ניסים בן 64 זכאי ל־Senior 60+.</t>
         </is>
       </c>
     </row>
     <row r="99" ht="58" customHeight="1" s="6">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>26.9.2026 – שבת</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Hrabovo / Malinô Brdo – אופציונלי</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Hotel International</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Hotel International, Veľká Lomnica</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>1:00–1:25 ש׳</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>ערב</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>כלול לפי חבילת המלון</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>חזרה למלון, ספא וארוחת ערב.</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>אם מוותרים על Hrabovo חוזרים מוקדם יותר מ־Liptovská Mara.</t>
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Google Maps ליום</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
         </is>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1" s="6">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Google Maps ליום</t>
+          <t>לינה בסוף היום</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
+          <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1" s="6">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>לינה בסוף היום</t>
-        </is>
-      </c>
-      <c r="C101" s="15" t="inlineStr">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>עלות משוערת ליום ל-4: מערת החירות €59 ל־4 + Chopok במחיר Gopass דינמי; Vrbické/Slide Park חינם.</t>
+        </is>
+      </c>
+      <c r="B101" s="18" t="n"/>
+      <c r="C101" s="18" t="n"/>
+      <c r="D101" s="18" t="n"/>
+      <c r="E101" s="18" t="n"/>
+      <c r="F101" s="18" t="n"/>
+      <c r="G101" s="18" t="n"/>
+      <c r="H101" s="18" t="n"/>
+      <c r="I101" s="18" t="n"/>
+      <c r="J101" s="19" t="n"/>
+    </row>
+    <row r="102" ht="28" customHeight="1" s="6"/>
+    <row r="103" ht="6" customHeight="1" s="6">
+      <c r="A103" s="32" t="inlineStr">
+        <is>
+          <t>חלופה | 26.9 חלופת גשם | חלופת גשם לטטרה הנמוכים: מערת החירות, Liptovský Mikuláš, Liptovská Mara ו־Hrabovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1" s="6">
+      <c r="A104" s="34" t="inlineStr">
+        <is>
+          <t>26.9.2026 – חלופה</t>
+        </is>
+      </c>
+      <c r="B104" s="35" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C104" s="34" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Hotel International – יציאה</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
         <is>
           <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
-    </row>
-    <row r="102" ht="28" customHeight="1" s="6">
-      <c r="A102" s="16" t="inlineStr">
-        <is>
-          <t>עלות משוערת ליום ל-4: מערת החירות €60 ל־4 + Chopok במחיר Gopass דינמי; Vrbické/Slide Park/Mara חינם. Hrabovo אופציונלי.</t>
-        </is>
-      </c>
-      <c r="B102" s="18" t="n"/>
-      <c r="C102" s="18" t="n"/>
-      <c r="D102" s="18" t="n"/>
-      <c r="E102" s="18" t="n"/>
-      <c r="F102" s="18" t="n"/>
-      <c r="G102" s="18" t="n"/>
-      <c r="H102" s="18" t="n"/>
-      <c r="I102" s="18" t="n"/>
-      <c r="J102" s="19" t="n"/>
-    </row>
-    <row r="103" ht="6" customHeight="1" s="6"/>
-    <row r="104" ht="32" customHeight="1" s="6">
-      <c r="A104" s="32" t="inlineStr">
-        <is>
-          <t>חלופה | 26.9 חלופת גשם | חלופת גשם לטטרה הנמוכים: מערת החירות, Liptovský Mikuláš, Liptovská Mara ו־Hrabovo</t>
+      <c r="F104" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H104" s="35" t="inlineStr">
+        <is>
+          <t>כלול לפי חבילת המלון</t>
+        </is>
+      </c>
+      <c r="I104" s="34" t="inlineStr">
+        <is>
+          <t>יוצאים ישר למערה.</t>
+        </is>
+      </c>
+      <c r="J104" s="34" t="inlineStr">
+        <is>
+          <t>להתאים את היציאה לשעת הסיור.</t>
         </is>
       </c>
     </row>
@@ -4281,43 +4277,47 @@
       </c>
       <c r="B105" s="35" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="C105" s="34" t="inlineStr"/>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C105" s="34" t="inlineStr">
+        <is>
+          <t>Hotel International – יציאה</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Hotel International – יציאה</t>
+          <t>Demänovská Cave of Liberty</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hotel International, Veľká Lomnica</t>
+          <t>Demänovská jaskyňa slobody</t>
         </is>
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1:10–1:25 ש׳</t>
         </is>
       </c>
       <c r="G105" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1:30–2:00 ש׳</t>
         </is>
       </c>
       <c r="H105" s="35" t="inlineStr">
         <is>
-          <t>כלול לפי חבילת המלון</t>
+          <t>€59 ל־4: 3×€15 + Senior 60+ אחד €14</t>
         </is>
       </c>
       <c r="I105" s="34" t="inlineStr">
         <is>
-          <t>יוצאים ישר למערה.</t>
+          <t>סיור במערת נטיפים ונהר תת־קרקעי.</t>
         </is>
       </c>
       <c r="J105" s="34" t="inlineStr">
         <is>
-          <t>להתאים את היציאה לשעת הסיור.</t>
+          <t>בספטמבר קיימות כניסות בשעות קבועות; להגיע מוקדם.</t>
         </is>
       </c>
     </row>
@@ -4329,47 +4329,47 @@
       </c>
       <c r="B106" s="35" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C106" s="34" t="inlineStr">
         <is>
-          <t>Hotel International – יציאה</t>
+          <t>Demänovská Cave of Liberty</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Demänovská Cave of Liberty</t>
+          <t>Liptovský Mikuláš</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Demänovská jaskyňa slobody</t>
+          <t>Liptovský Mikuláš centrum</t>
         </is>
       </c>
       <c r="F106" s="35" t="inlineStr">
         <is>
-          <t>1:10–1:25 ש׳</t>
+          <t>15–20 דק׳</t>
         </is>
       </c>
       <c r="G106" s="35" t="inlineStr">
         <is>
-          <t>1:30–2:00 ש׳</t>
+          <t>1:15 ש׳</t>
         </is>
       </c>
       <c r="H106" s="35" t="inlineStr">
         <is>
-          <t>€60 ל־4 – סיור מסורתי (15€ לאדם)</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I106" s="34" t="inlineStr">
         <is>
-          <t>סיור במערת נטיפים ונהר תת־קרקעי.</t>
+          <t>מרכז העיר, ארוחת צהריים וקפה.</t>
         </is>
       </c>
       <c r="J106" s="34" t="inlineStr">
         <is>
-          <t>בספטמבר קיימות כניסות בשעות קבועות; להגיע מוקדם.</t>
+          <t>חניה לפי שילוט מקומי.</t>
         </is>
       </c>
     </row>
@@ -4381,22 +4381,22 @@
       </c>
       <c r="B107" s="35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C107" s="34" t="inlineStr">
         <is>
-          <t>Demänovská Cave of Liberty</t>
+          <t>Liptovský Mikuláš</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Liptovský Mikuláš</t>
+          <t>Liptovská Mara</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Liptovský Mikuláš centrum</t>
+          <t>Liptovská Mara – Liptovský Trnovec</t>
         </is>
       </c>
       <c r="F107" s="35" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G107" s="35" t="inlineStr">
         <is>
-          <t>1:15 ש׳</t>
+          <t>30–45 דק׳</t>
         </is>
       </c>
       <c r="H107" s="35" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="I107" s="34" t="inlineStr">
         <is>
-          <t>מרכז העיר, ארוחת צהריים וקפה.</t>
+          <t>תצפית/מרינה אם הגשם נחלש.</t>
         </is>
       </c>
       <c r="J107" s="34" t="inlineStr">
         <is>
-          <t>חניה לפי שילוט מקומי.</t>
+          <t>אם מזג האוויר לא משתפר – מדלגים.</t>
         </is>
       </c>
     </row>
@@ -4433,47 +4433,47 @@
       </c>
       <c r="B108" s="35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C108" s="34" t="inlineStr">
         <is>
-          <t>Liptovský Mikuláš</t>
+          <t>Liptovská Mara</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Liptovská Mara</t>
+          <t>Hrabovo – אופציונלי</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Liptovská Mara – Liptovský Trnovec</t>
+          <t>Hrabovo, Ružomberok</t>
         </is>
       </c>
       <c r="F108" s="35" t="inlineStr">
         <is>
-          <t>15–20 דק׳</t>
+          <t>35–45 דק׳</t>
         </is>
       </c>
       <c r="G108" s="35" t="inlineStr">
         <is>
-          <t>30–45 דק׳</t>
+          <t>1:00 ש׳</t>
         </is>
       </c>
       <c r="H108" s="35" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>האגם חינם; רכבל/קארטינג/Tarzania בתשלום לפי בחירה</t>
         </is>
       </c>
       <c r="I108" s="34" t="inlineStr">
         <is>
-          <t>תצפית/מרינה אם הגשם נחלש.</t>
+          <t>אגם ובית קפה; פעילויות רק אם מזג האוויר מאפשר.</t>
         </is>
       </c>
       <c r="J108" s="34" t="inlineStr">
         <is>
-          <t>אם מזג האוויר לא משתפר – מדלגים.</t>
+          <t>לא לבנות על רכבל/קארטינג בגשם.</t>
         </is>
       </c>
     </row>
@@ -4485,143 +4485,139 @@
       </c>
       <c r="B109" s="35" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C109" s="34" t="inlineStr">
         <is>
+          <t>Hrabovo – אופציונלי</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Hotel International</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Hotel International, Veľká Lomnica</t>
+        </is>
+      </c>
+      <c r="F109" s="35" t="inlineStr">
+        <is>
+          <t>1:00–1:25 ש׳</t>
+        </is>
+      </c>
+      <c r="G109" s="35" t="inlineStr">
+        <is>
+          <t>ערב</t>
+        </is>
+      </c>
+      <c r="H109" s="35" t="inlineStr">
+        <is>
+          <t>כלול לפי חבילת המלון</t>
+        </is>
+      </c>
+      <c r="I109" s="34" t="inlineStr">
+        <is>
+          <t>חזרה לספא וארוחת ערב.</t>
+        </is>
+      </c>
+      <c r="J109" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="58" customHeight="1" s="6">
+      <c r="A110" s="36" t="inlineStr">
+        <is>
+          <t>Google Maps לחלופה</t>
+        </is>
+      </c>
+      <c r="B110" s="37" t="n"/>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
+        </is>
+      </c>
+      <c r="D110" s="37" t="n"/>
+      <c r="E110" s="37" t="n"/>
+      <c r="F110" s="37" t="n"/>
+      <c r="G110" s="37" t="n"/>
+      <c r="H110" s="37" t="n"/>
+      <c r="I110" s="37" t="n"/>
+      <c r="J110" s="37" t="n"/>
+    </row>
+    <row r="111" ht="20" customHeight="1" s="6">
+      <c r="A111" s="39" t="inlineStr">
+        <is>
+          <t>עלות החלופה ל-4: מערת החירות: €60 ל־4; יתר העצירות חינם, פעילויות Hrabovo אופציונליות.</t>
+        </is>
+      </c>
+      <c r="B111" s="18" t="n"/>
+      <c r="C111" s="18" t="n"/>
+      <c r="D111" s="18" t="n"/>
+      <c r="E111" s="18" t="n"/>
+      <c r="F111" s="18" t="n"/>
+      <c r="G111" s="18" t="n"/>
+      <c r="H111" s="18" t="n"/>
+      <c r="I111" s="18" t="n"/>
+      <c r="J111" s="19" t="n"/>
+    </row>
+    <row r="112" ht="28" customHeight="1" s="6"/>
+    <row r="113" ht="8" customHeight="1" s="6">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>יום א׳ | 27.9.2026 | הטטרה הנמוכים, בנסקה ביסטריצה, תצפית עיקול הדנובה ואאוטלט בדרך לבודפשט</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="28" customHeight="1" s="6">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>27.9.2026 – יום א׳</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
           <t>Liptovská Mara</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Hrabovo – אופציונלי</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Hrabovo, Ružomberok</t>
-        </is>
-      </c>
-      <c r="F109" s="35" t="inlineStr">
-        <is>
-          <t>35–45 דק׳</t>
-        </is>
-      </c>
-      <c r="G109" s="35" t="inlineStr">
-        <is>
-          <t>1:00 ש׳</t>
-        </is>
-      </c>
-      <c r="H109" s="35" t="inlineStr">
-        <is>
-          <t>האגם חינם; רכבל/קארטינג/Tarzania בתשלום לפי בחירה</t>
-        </is>
-      </c>
-      <c r="I109" s="34" t="inlineStr">
-        <is>
-          <t>אגם ובית קפה; פעילויות רק אם מזג האוויר מאפשר.</t>
-        </is>
-      </c>
-      <c r="J109" s="34" t="inlineStr">
-        <is>
-          <t>לא לבנות על רכבל/קארטינג בגשם.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="58" customHeight="1" s="6">
-      <c r="A110" s="34" t="inlineStr">
-        <is>
-          <t>26.9.2026 – חלופה</t>
-        </is>
-      </c>
-      <c r="B110" s="35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C110" s="34" t="inlineStr">
-        <is>
-          <t>Hrabovo – אופציונלי</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Hotel International</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Hotel International, Veľká Lomnica</t>
-        </is>
-      </c>
-      <c r="F110" s="35" t="inlineStr">
-        <is>
-          <t>1:00–1:25 ש׳</t>
-        </is>
-      </c>
-      <c r="G110" s="35" t="inlineStr">
-        <is>
-          <t>ערב</t>
-        </is>
-      </c>
-      <c r="H110" s="35" t="inlineStr">
-        <is>
-          <t>כלול לפי חבילת המלון</t>
-        </is>
-      </c>
-      <c r="I110" s="34" t="inlineStr">
-        <is>
-          <t>חזרה לספא וארוחת ערב.</t>
-        </is>
-      </c>
-      <c r="J110" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1" s="6">
-      <c r="A111" s="36" t="inlineStr">
-        <is>
-          <t>Google Maps לחלופה</t>
-        </is>
-      </c>
-      <c r="B111" s="37" t="n"/>
-      <c r="C111" s="15" t="inlineStr">
-        <is>
-          <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
-        </is>
-      </c>
-      <c r="D111" s="37" t="n"/>
-      <c r="E111" s="37" t="n"/>
-      <c r="F111" s="37" t="n"/>
-      <c r="G111" s="37" t="n"/>
-      <c r="H111" s="37" t="n"/>
-      <c r="I111" s="37" t="n"/>
-      <c r="J111" s="37" t="n"/>
-    </row>
-    <row r="112" ht="28" customHeight="1" s="6">
-      <c r="A112" s="39" t="inlineStr">
-        <is>
-          <t>עלות החלופה ל-4: מערת החירות: €60 ל־4; יתר העצירות חינם, פעילויות Hrabovo אופציונליות.</t>
-        </is>
-      </c>
-      <c r="B112" s="18" t="n"/>
-      <c r="C112" s="18" t="n"/>
-      <c r="D112" s="18" t="n"/>
-      <c r="E112" s="18" t="n"/>
-      <c r="F112" s="18" t="n"/>
-      <c r="G112" s="18" t="n"/>
-      <c r="H112" s="18" t="n"/>
-      <c r="I112" s="18" t="n"/>
-      <c r="J112" s="19" t="n"/>
-    </row>
-    <row r="113" ht="8" customHeight="1" s="6"/>
-    <row r="114" ht="28" customHeight="1" s="6">
-      <c r="A114" s="11" t="inlineStr">
-        <is>
-          <t>יום א׳ | 27.9.2026 | הטטרה הנמוכים, בנסקה ביסטריצה, תצפית עיקול הדנובה ואאוטלט בדרך לבודפשט</t>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Liptovská Mara – Liptovský Trnovec</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>1:00–1:15 ש׳</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>20–30 דק׳</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>חינם</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>אגם גדול בטטרה הנמוכים, מרינה ותצפיות יפות.</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>עצירת בוקר קצרה לצילומים וקפה.</t>
         </is>
       </c>
     </row>
@@ -4633,23 +4629,27 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr"/>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Liptovská Mara</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Liptovská Mara</t>
+          <t>Donovaly</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Liptovská Mara – Liptovský Trnovec</t>
+          <t>Donovaly, Slovakia</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>1:00–1:15 ש׳</t>
+          <t>45–55 דק׳</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -4659,17 +4659,17 @@
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>חינם לעצירת נוף</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>אגם גדול בטטרה הנמוכים, מרינה ותצפיות יפות.</t>
+          <t>מעבר הרים ועיירת נופש עם תצפיות ונוף אלפיני.</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>עצירת בוקר קצרה לצילומים וקפה.</t>
+          <t>עצירת התרעננות בלבד.</t>
         </is>
       </c>
     </row>
@@ -4681,47 +4681,47 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Liptovská Mara</t>
+          <t>Donovaly</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Donovaly</t>
+          <t>Bobová dráha FunAréna Donovaly – אופציונלי</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Donovaly, Slovakia</t>
+          <t>FunAréna Donovaly</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>45–55 דק׳</t>
+          <t>🚗 3–5 דק׳</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>20–30 דק׳</t>
+          <t>35–50 דק׳</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>חינם לעצירת נוף</t>
+          <t>€24 / €46 / €64 ל־4 (1 / 2 / 3 סיבובים)</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>מעבר הרים ועיירת נופש עם תצפיות ונוף אלפיני.</t>
+          <t>מגלשת הרים מהירה וקצרה – עצירה כיפית בדרך בלי להפוך אותה ליום אטרקציות.</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>עצירת התרעננות בלבד.</t>
+          <t>מחיר רשמי 2026: €6 לסיבוב, €11.50 לשני סיבובים, €16 לשלושה – לאדם.</t>
         </is>
       </c>
     </row>
@@ -4733,47 +4733,47 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Donovaly</t>
+          <t>Bobová dráha FunAréna Donovaly – אופציונלי</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Bobová dráha FunAréna Donovaly – אופציונלי</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FunAréna Donovaly</t>
+          <t>Námestie SNP, Banská Bystrica</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>🚗 3–5 דק׳</t>
+          <t>30–35 דק׳</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>35–50 דק׳</t>
+          <t>1:00–1:15 ש׳</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>€24 / €46 / €64 ל־4 (1 / 2 / 3 סיבובים)</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>מגלשת הרים מהירה וקצרה – עצירה כיפית בדרך בלי להפוך אותה ליום אטרקציות.</t>
+          <t>כיכר היסטורית צבעונית, מדרחוב וארוחת צהריים קלה.</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>מחיר רשמי 2026: €6 לסיבוב, €11.50 לשני סיבובים, €16 לשלושה – לאדם.</t>
+          <t>לא להיכנס למוזיאונים כדי לשמור זמן.</t>
         </is>
       </c>
     </row>
@@ -4785,47 +4785,47 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Bobová dráha FunAréna Donovaly – אופציונלי</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Visegrád – תצפית עיקול הדנובה</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Námestie SNP, Banská Bystrica</t>
+          <t>Zsitvay-kilátó, Visegrád</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>30–35 דק׳</t>
+          <t>2:30–2:50 ש׳</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>1:00–1:15 ש׳</t>
+          <t>25–35 דק׳</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>3,400 HUF ל־4 (850 HUF לאדם)</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>כיכר היסטורית צבעונית, מדרחוב וארוחת צהריים קלה.</t>
+          <t>תצפית פנורמית מרשימה על עיקול הדנובה והגבעות.</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>לא להיכנס למוזיאונים כדי לשמור זמן.</t>
+          <t>עצירת הוואו של הדרך; ללא סיור ארוך.</t>
         </is>
       </c>
     </row>
@@ -4837,47 +4837,47 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Visegrád – תצפית עיקול הדנובה</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Visegrád – תצפית עיקול הדנובה</t>
+          <t>Premier Outlet Budapest</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Zsitvay-kilátó, Visegrád</t>
+          <t>Premier Outlet Budapest</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2:30–2:50 ש׳</t>
+          <t>1:10–1:25 ש׳</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>25–35 דק׳</t>
+          <t>1:15–1:45 ש׳</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>3,400 HUF ל־4 (850 HUF לאדם)</t>
+          <t>כניסה חינם</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>תצפית פנורמית מרשימה על עיקול הדנובה והגבעות.</t>
+          <t>קניות מרוכזות לפני הכניסה לבודפשט.</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>עצירת הוואו של הדרך; ללא סיור ארוך.</t>
+          <t>לבדוק שעות פתיחה ביום א׳.</t>
         </is>
       </c>
     </row>
@@ -4889,147 +4889,143 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Visegrád – תצפית עיקול הדנובה</t>
+          <t>Premier Outlet Budapest</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Premier Outlet Budapest</t>
+          <t>La Prima Hotel Budapest</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Premier Outlet Budapest</t>
+          <t>La Prima Hotel Budapest</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>1:10–1:25 ש׳</t>
+          <t>25–40 דק׳</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>1:15–1:45 ש׳</t>
+          <t>ערב</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>כניסה חינם</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>קניות מרוכזות לפני הכניסה לבודפשט.</t>
+          <t>צ׳ק־אין, ארוחת ערב ומנוחה במרכז העיר.</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>לבדוק שעות פתיחה ביום א׳.</t>
+          <t>אם מתעכבים, מקצרים קודם את Donovaly.</t>
         </is>
       </c>
     </row>
     <row r="121" ht="58" customHeight="1" s="6">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>27.9.2026 – יום א׳</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Premier Outlet Budapest</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>La Prima Hotel Budapest</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>La Prima Hotel Budapest</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>25–40 דק׳</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>ערב</t>
-        </is>
-      </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>צ׳ק־אין, ארוחת ערב ומנוחה במרכז העיר.</t>
-        </is>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>אם מתעכבים, מקצרים קודם את Donovaly.</t>
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>Google Maps ליום</t>
+        </is>
+      </c>
+      <c r="C121" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
         </is>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1" s="6">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>Google Maps ליום</t>
+          <t>לינה בסוף היום</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
+          <t>La Prima Hotel Budapest</t>
         </is>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1" s="6">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>לינה בסוף היום</t>
-        </is>
-      </c>
-      <c r="C123" s="15" t="inlineStr">
-        <is>
-          <t>La Prima Hotel Budapest</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="28" customHeight="1" s="6">
-      <c r="A124" s="16" t="inlineStr">
+      <c r="A123" s="16" t="inlineStr">
         <is>
           <t>עלות משוערת ליום ל-4: Donovaly Bob: €24 / €46 / €64 ל־4 (1/2/3 סיבובים) + Zsitvay lookout: 3,400 HUF ל־4; שאר העצירות ללא כניסה.</t>
         </is>
       </c>
-      <c r="B124" s="18" t="n"/>
-      <c r="C124" s="18" t="n"/>
-      <c r="D124" s="18" t="n"/>
-      <c r="E124" s="18" t="n"/>
-      <c r="F124" s="18" t="n"/>
-      <c r="G124" s="18" t="n"/>
-      <c r="H124" s="18" t="n"/>
-      <c r="I124" s="18" t="n"/>
-      <c r="J124" s="19" t="n"/>
-    </row>
-    <row r="125" ht="6" customHeight="1" s="6"/>
+      <c r="B123" s="18" t="n"/>
+      <c r="C123" s="18" t="n"/>
+      <c r="D123" s="18" t="n"/>
+      <c r="E123" s="18" t="n"/>
+      <c r="F123" s="18" t="n"/>
+      <c r="G123" s="18" t="n"/>
+      <c r="H123" s="18" t="n"/>
+      <c r="I123" s="18" t="n"/>
+      <c r="J123" s="19" t="n"/>
+    </row>
+    <row r="124" ht="28" customHeight="1" s="6"/>
+    <row r="125" ht="6" customHeight="1" s="6">
+      <c r="A125" s="32" t="inlineStr">
+        <is>
+          <t>חלופה | 27.9 חלופת גשם | חלופת גשם בדרך לבודפשט: Banská Bystrica → Premier Outlet → Budapest</t>
+        </is>
+      </c>
+    </row>
     <row r="126" ht="32" customHeight="1" s="6">
-      <c r="A126" s="32" t="inlineStr">
-        <is>
-          <t>חלופה | 27.9 חלופת גשם | חלופת גשם בדרך לבודפשט: Banská Bystrica → Premier Outlet → Budapest</t>
+      <c r="A126" s="34" t="inlineStr">
+        <is>
+          <t>27.9.2026 – חלופה</t>
+        </is>
+      </c>
+      <c r="B126" s="35" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C126" s="34" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Hotel International – יציאה</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Hotel International, Veľká Lomnica</t>
+        </is>
+      </c>
+      <c r="F126" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G126" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H126" s="35" t="inlineStr">
+        <is>
+          <t>כלול לפי חבילת המלון</t>
+        </is>
+      </c>
+      <c r="I126" s="34" t="inlineStr">
+        <is>
+          <t>יציאה רגועה לבודפשט.</t>
+        </is>
+      </c>
+      <c r="J126" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5041,43 +5037,47 @@
       </c>
       <c r="B127" s="35" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C127" s="34" t="inlineStr"/>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C127" s="34" t="inlineStr">
+        <is>
+          <t>Hotel International – יציאה</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Hotel International – יציאה</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hotel International, Veľká Lomnica</t>
+          <t>Námestie SNP, Banská Bystrica</t>
         </is>
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1:30–1:45 ש׳</t>
         </is>
       </c>
       <c r="G127" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1:15 ש׳</t>
         </is>
       </c>
       <c r="H127" s="35" t="inlineStr">
         <is>
-          <t>כלול לפי חבילת המלון</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I127" s="34" t="inlineStr">
         <is>
-          <t>יציאה רגועה לבודפשט.</t>
+          <t>כיכר מרכזית, קפה/ארוחת צהריים קצרה.</t>
         </is>
       </c>
       <c r="J127" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ביום א׳ החניה העירונית במרכז חינם.</t>
         </is>
       </c>
     </row>
@@ -5089,47 +5089,47 @@
       </c>
       <c r="B128" s="35" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C128" s="34" t="inlineStr">
         <is>
-          <t>Hotel International – יציאה</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Premier Outlet Budapest</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Námestie SNP, Banská Bystrica</t>
+          <t>Premier Outlet Budapest</t>
         </is>
       </c>
       <c r="F128" s="35" t="inlineStr">
         <is>
-          <t>1:30–1:45 ש׳</t>
+          <t>2:30–2:50 ש׳</t>
         </is>
       </c>
       <c r="G128" s="35" t="inlineStr">
         <is>
-          <t>1:15 ש׳</t>
+          <t>1:30–2:00 ש׳</t>
         </is>
       </c>
       <c r="H128" s="35" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>כניסה חינם</t>
         </is>
       </c>
       <c r="I128" s="34" t="inlineStr">
         <is>
-          <t>כיכר מרכזית, קפה/ארוחת צהריים קצרה.</t>
+          <t>קניות במקום מקורה/חצי מקורה.</t>
         </is>
       </c>
       <c r="J128" s="34" t="inlineStr">
         <is>
-          <t>ביום א׳ החניה העירונית במרכז חינם.</t>
+          <t>בדוק שעות פתיחה ביום א׳ סמוך לנסיעה.</t>
         </is>
       </c>
     </row>
@@ -5141,143 +5141,139 @@
       </c>
       <c r="B129" s="35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C129" s="34" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Premier Outlet Budapest</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Premier Outlet Budapest</t>
+          <t>La Prima Hotel Budapest</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Premier Outlet Budapest</t>
+          <t>La Prima Hotel Budapest</t>
         </is>
       </c>
       <c r="F129" s="35" t="inlineStr">
         <is>
-          <t>2:30–2:50 ש׳</t>
+          <t>25–40 דק׳</t>
         </is>
       </c>
       <c r="G129" s="35" t="inlineStr">
         <is>
-          <t>1:30–2:00 ש׳</t>
+          <t>ערב</t>
         </is>
       </c>
       <c r="H129" s="35" t="inlineStr">
         <is>
-          <t>כניסה חינם</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I129" s="34" t="inlineStr">
         <is>
-          <t>קניות במקום מקורה/חצי מקורה.</t>
+          <t>צ׳ק־אין וערב בעיר.</t>
         </is>
       </c>
       <c r="J129" s="34" t="inlineStr">
         <is>
-          <t>בדוק שעות פתיחה ביום א׳ סמוך לנסיעה.</t>
+          <t>חניה: Franklin Parkolóház הוא חלופה זולה יחסית ליד המלון.</t>
         </is>
       </c>
     </row>
     <row r="130" ht="58" customHeight="1" s="6">
-      <c r="A130" s="34" t="inlineStr">
-        <is>
-          <t>27.9.2026 – חלופה</t>
-        </is>
-      </c>
-      <c r="B130" s="35" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C130" s="34" t="inlineStr">
-        <is>
-          <t>Premier Outlet Budapest</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>La Prima Hotel Budapest</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>La Prima Hotel Budapest</t>
-        </is>
-      </c>
-      <c r="F130" s="35" t="inlineStr">
-        <is>
-          <t>25–40 דק׳</t>
-        </is>
-      </c>
-      <c r="G130" s="35" t="inlineStr">
-        <is>
-          <t>ערב</t>
-        </is>
-      </c>
-      <c r="H130" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I130" s="34" t="inlineStr">
-        <is>
-          <t>צ׳ק־אין וערב בעיר.</t>
-        </is>
-      </c>
-      <c r="J130" s="34" t="inlineStr">
-        <is>
-          <t>חניה: Franklin Parkolóház הוא חלופה זולה יחסית ליד המלון.</t>
-        </is>
-      </c>
+      <c r="A130" s="36" t="inlineStr">
+        <is>
+          <t>Google Maps לחלופה</t>
+        </is>
+      </c>
+      <c r="B130" s="37" t="n"/>
+      <c r="C130" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
+        </is>
+      </c>
+      <c r="D130" s="37" t="n"/>
+      <c r="E130" s="37" t="n"/>
+      <c r="F130" s="37" t="n"/>
+      <c r="G130" s="37" t="n"/>
+      <c r="H130" s="37" t="n"/>
+      <c r="I130" s="37" t="n"/>
+      <c r="J130" s="37" t="n"/>
     </row>
     <row r="131" ht="20" customHeight="1" s="6">
-      <c r="A131" s="36" t="inlineStr">
-        <is>
-          <t>Google Maps לחלופה</t>
-        </is>
-      </c>
-      <c r="B131" s="37" t="n"/>
-      <c r="C131" s="15" t="inlineStr">
-        <is>
-          <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
-        </is>
-      </c>
-      <c r="D131" s="37" t="n"/>
-      <c r="E131" s="37" t="n"/>
-      <c r="F131" s="37" t="n"/>
-      <c r="G131" s="37" t="n"/>
-      <c r="H131" s="37" t="n"/>
-      <c r="I131" s="37" t="n"/>
-      <c r="J131" s="37" t="n"/>
-    </row>
-    <row r="132" ht="28" customHeight="1" s="6">
-      <c r="A132" s="39" t="inlineStr">
+      <c r="A131" s="39" t="inlineStr">
         <is>
           <t>עלות החלופה ל-4: 0 € כניסות חובה (לא כולל קניות/חניה)</t>
         </is>
       </c>
-      <c r="B132" s="18" t="n"/>
-      <c r="C132" s="18" t="n"/>
-      <c r="D132" s="18" t="n"/>
-      <c r="E132" s="18" t="n"/>
-      <c r="F132" s="18" t="n"/>
-      <c r="G132" s="18" t="n"/>
-      <c r="H132" s="18" t="n"/>
-      <c r="I132" s="18" t="n"/>
-      <c r="J132" s="19" t="n"/>
-    </row>
-    <row r="133" ht="8" customHeight="1" s="6"/>
+      <c r="B131" s="18" t="n"/>
+      <c r="C131" s="18" t="n"/>
+      <c r="D131" s="18" t="n"/>
+      <c r="E131" s="18" t="n"/>
+      <c r="F131" s="18" t="n"/>
+      <c r="G131" s="18" t="n"/>
+      <c r="H131" s="18" t="n"/>
+      <c r="I131" s="18" t="n"/>
+      <c r="J131" s="19" t="n"/>
+    </row>
+    <row r="132" ht="28" customHeight="1" s="6"/>
+    <row r="133" ht="8" customHeight="1" s="6">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>יום ב׳ | 28.9.2026 | בודפשט בבוקר, החזרת הרכב וטיסת קרן ומאי</t>
+        </is>
+      </c>
+    </row>
     <row r="134" ht="28" customHeight="1" s="6">
-      <c r="A134" s="10" t="inlineStr">
-        <is>
-          <t>יום ב׳ | 28.9.2026 | בודפשט בבוקר, החזרת הרכב וטיסת קרן ומאי</t>
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>28.9.2026 – יום ב׳</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>הפרלמנט ונעלי הברזל</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Shoes on the Danube Bank</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>הליכה/תחבורה</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>1:15–1:30 ש׳</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>חינם מבחוץ</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>טיילת הדנובה, אנדרטת הנעליים ותצפית לפרלמנט.</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>אין צורך בסיור פנימי ביום טיסה.</t>
         </is>
       </c>
     </row>
@@ -5289,43 +5285,47 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr"/>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>הפרלמנט ונעלי הברזל</t>
+        </is>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>הפרלמנט ונעלי הברזל</t>
+          <t>בזיליקת סנט אישטוון</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shoes on the Danube Bank</t>
+          <t>Szent István Bazilika</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>הליכה/תחבורה</t>
+          <t>15–20 דק׳</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>1:15–1:30 ש׳</t>
+          <t>45–60 דק׳</t>
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>חינם מבחוץ</t>
+          <t>ל־4: 10,400 HUF כנסייה / 20,000 HUF תצפית+אוצר / 27,200 HUF משולב</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>טיילת הדנובה, אנדרטת הנעליים ותצפית לפרלמנט.</t>
+          <t>כיכר הבזיליקה, קפה ותצפית אם אין תור.</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>אין צורך בסיור פנימי ביום טיסה.</t>
+          <t>לשמור זמן לחזרה למלון.</t>
         </is>
       </c>
     </row>
@@ -5337,47 +5337,47 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>הפרלמנט ונעלי הברזל</t>
+          <t>בזיליקת סנט אישטוון</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>בזיליקת סנט אישטוון</t>
+          <t>La Prima Hotel – איסוף מזוודות</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Szent István Bazilika</t>
+          <t>La Prima Hotel Budapest</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>15–20 דק׳</t>
+          <t>15–25 דק׳</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>45–60 דק׳</t>
+          <t>20–25 דק׳</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>ל־4: 10,400 HUF כנסייה / 20,000 HUF תצפית+אוצר / 27,200 HUF משולב</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>כיכר הבזיליקה, קפה ותצפית אם אין תור.</t>
+          <t>איסוף מזוודות ויציאה להחזרת הרכב.</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>לשמור זמן לחזרה למלון.</t>
+          <t>לא להתעכב – ההחזרה מוזמנת ל־13:00.</t>
         </is>
       </c>
     </row>
@@ -5389,47 +5389,47 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>בזיליקת סנט אישטוון</t>
+          <t>La Prima Hotel – איסוף מזוודות</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>La Prima Hotel – איסוף מזוודות</t>
+          <t>Klass Wagen – החזרת הרכב</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>La Prima Hotel Budapest</t>
+          <t>Klass Wagen, Új Ecseri út 2, 2220 Vecsés, Hungary</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>15–25 דק׳</t>
+          <t>30–45 דק׳</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>20–25 דק׳</t>
+          <t>45–60 דק׳</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>כלול בהשכרה</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>איסוף מזוודות ויציאה להחזרת הרכב.</t>
+          <t>תדלוק לפני ההגעה, החזרת הרכב ובדיקת החשבון.</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>לא להתעכב – ההחזרה מוזמנת ל־13:00.</t>
+          <t>כתובת מהואוצ׳ר: Új Ecseri út 2, 2220 Vecsés. לצלם רכב, דלק וקילומטראז׳ לפני המסירה.</t>
         </is>
       </c>
     </row>
@@ -5441,47 +5441,47 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>La Prima Hotel – איסוף מזוודות</t>
+          <t>Klass Wagen – החזרת הרכב</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Klass Wagen – החזרת הרכב</t>
+          <t>Budapest Airport Terminal 2</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Klass Wagen, Új Ecseri út 2, 2220 Vecsés, Hungary</t>
+          <t>Budapest Airport Terminal 2</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>30–45 דק׳</t>
+          <t>שאטל Klass Wagen</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>45–60 דק׳</t>
+          <t>עד הטיסה</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>כלול בהשכרה</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>תדלוק לפני ההגעה, החזרת הרכב ובדיקת החשבון.</t>
+          <t>שאטל של חברת ההשכרה לטרמינל. קרן ומאי לטיסה 15:30.</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>כתובת מהואוצ׳ר: Új Ecseri út 2, 2220 Vecsés. לצלם רכב, דלק וקילומטראז׳ לפני המסירה.</t>
+          <t>ניסים ואלעד חוזרים לבודפשט לאחר הפרידה.</t>
         </is>
       </c>
     </row>
@@ -5493,32 +5493,32 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Klass Wagen – החזרת הרכב</t>
+          <t>Budapest Airport Terminal 2</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Budapest Airport Terminal 2</t>
+          <t>חזרה לבודפשט – ניסים ואלעד</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Budapest Airport Terminal 2</t>
+          <t>La Prima Hotel Budapest</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>שאטל Klass Wagen</t>
+          <t>תחבורה ציבורית/מונית</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>עד הטיסה</t>
+          <t>אחה״צ וערב</t>
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr">
@@ -5528,112 +5528,108 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>שאטל של חברת ההשכרה לטרמינל. קרן ומאי לטיסה 15:30.</t>
+          <t>חזרה למרכז העיר, ואצי/דנובה/ארוחה לפי הכוח.</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>ניסים ואלעד חוזרים לבודפשט לאחר הפרידה.</t>
+          <t>אין יותר רכב שכור.</t>
         </is>
       </c>
     </row>
     <row r="140" ht="58" customHeight="1" s="6">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>28.9.2026 – יום ב׳</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Budapest Airport Terminal 2</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>חזרה לבודפשט – ניסים ואלעד</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>La Prima Hotel Budapest</t>
-        </is>
-      </c>
-      <c r="F140" s="3" t="inlineStr">
-        <is>
-          <t>תחבורה ציבורית/מונית</t>
-        </is>
-      </c>
-      <c r="G140" s="3" t="inlineStr">
-        <is>
-          <t>אחה״צ וערב</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>חזרה למרכז העיר, ואצי/דנובה/ארוחה לפי הכוח.</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>אין יותר רכב שכור.</t>
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>Google Maps ליום</t>
+        </is>
+      </c>
+      <c r="C140" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
         </is>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1" s="6">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>Google Maps ליום</t>
+          <t>לינה בסוף היום</t>
         </is>
       </c>
       <c r="C141" s="15" t="inlineStr">
         <is>
-          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
+          <t>בודפשט – ניסים ואלעד</t>
         </is>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1" s="6">
-      <c r="A142" s="4" t="inlineStr">
-        <is>
-          <t>לינה בסוף היום</t>
-        </is>
-      </c>
-      <c r="C142" s="15" t="inlineStr">
-        <is>
-          <t>בודפשט – ניסים ואלעד</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="28" customHeight="1" s="6">
-      <c r="A143" s="16" t="inlineStr">
+      <c r="A142" s="16" t="inlineStr">
         <is>
           <t>עלות משוערת ליום ל-4: האתרים בחוץ חינם; בזיליקה אם נכנסים: 10,400–27,200 HUF ל־4 לפי סוג הכרטיס.</t>
         </is>
       </c>
-      <c r="B143" s="18" t="n"/>
-      <c r="C143" s="18" t="n"/>
-      <c r="D143" s="18" t="n"/>
-      <c r="E143" s="18" t="n"/>
-      <c r="F143" s="18" t="n"/>
-      <c r="G143" s="18" t="n"/>
-      <c r="H143" s="18" t="n"/>
-      <c r="I143" s="18" t="n"/>
-      <c r="J143" s="19" t="n"/>
-    </row>
-    <row r="144" ht="8" customHeight="1" s="6"/>
+      <c r="B142" s="18" t="n"/>
+      <c r="C142" s="18" t="n"/>
+      <c r="D142" s="18" t="n"/>
+      <c r="E142" s="18" t="n"/>
+      <c r="F142" s="18" t="n"/>
+      <c r="G142" s="18" t="n"/>
+      <c r="H142" s="18" t="n"/>
+      <c r="I142" s="18" t="n"/>
+      <c r="J142" s="19" t="n"/>
+    </row>
+    <row r="143" ht="28" customHeight="1" s="6"/>
+    <row r="144" ht="8" customHeight="1" s="6">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>יום ג׳ | 29.9.2026 | בוקר רגוע וטיסה של ניסים ואלעד</t>
+        </is>
+      </c>
+    </row>
     <row r="145" ht="28" customHeight="1" s="6">
-      <c r="A145" s="11" t="inlineStr">
-        <is>
-          <t>יום ג׳ | 29.9.2026 | בוקר רגוע וטיסה של ניסים ואלעד</t>
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>29.9.2026 – יום ג׳</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ארוחת בוקר וצ׳ק־אאוט</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>La Prima Hotel Budapest</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>60–75 דק׳</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>כלול/לפי המלון</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>ארוחת בוקר, אריזה ובדיקת החדר.</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>לא לתכנן אתר מרוחק ביום הטיסה.</t>
         </is>
       </c>
     </row>
@@ -5645,43 +5641,47 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr"/>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>ארוחת בוקר וצ׳ק־אאוט</t>
+        </is>
+      </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ארוחת בוקר וצ׳ק־אאוט</t>
+          <t>יציאה לשדה התעופה</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>La Prima Hotel Budapest</t>
+          <t>Budapest Airport Terminal 2</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
+          <t>35–50 דק׳</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G146" s="3" t="inlineStr">
-        <is>
-          <t>60–75 דק׳</t>
-        </is>
-      </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>כלול/לפי המלון</t>
+          <t>תחבורה לפי אמצעי</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>ארוחת בוקר, אריזה ובדיקת החדר.</t>
+          <t>מונית/תחבורה ציבורית לשדה.</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>לא לתכנן אתר מרוחק ביום הטיסה.</t>
+          <t>אין רכב שכור ביום זה.</t>
         </is>
       </c>
     </row>
@@ -5693,17 +5693,17 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>ארוחת בוקר וצ׳ק־אאוט</t>
+          <t>יציאה לשדה התעופה</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>יציאה לשדה התעופה</t>
+          <t>Budapest Airport Terminal 2</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5713,27 +5713,27 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>35–50 דק׳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
+          <t>עד הטיסה</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr">
-        <is>
-          <t>תחבורה לפי אמצעי</t>
-        </is>
-      </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>מונית/תחבורה ציבורית לשדה.</t>
+          <t>צ׳ק־אין, בידוק וביקורת גבולות.</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>אין רכב שכור ביום זה.</t>
+          <t>לבדוק טרמינל ושעת טיסה ערב קודם.</t>
         </is>
       </c>
     </row>
@@ -5745,24 +5745,24 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>יציאה לשדה התעופה</t>
+          <t>Budapest Airport Terminal 2</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>טיסה הביתה</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>Budapest Airport Terminal 2</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Budapest Airport Terminal 2</t>
-        </is>
-      </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
           <t>—</t>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>עד הטיסה</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
@@ -5780,107 +5780,56 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>צ׳ק־אין, בידוק וביקורת גבולות.</t>
+          <t>טיסת ניסים ואלעד.</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>לבדוק טרמינל ושעת טיסה ערב קודם.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="149" ht="58" customHeight="1" s="6">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>29.9.2026 – יום ג׳</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Budapest Airport Terminal 2</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>טיסה הביתה</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Budapest Airport Terminal 2</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G149" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H149" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>טיסת ניסים ואלעד.</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>Google Maps ליום</t>
+        </is>
+      </c>
+      <c r="C149" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
         </is>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1" s="6">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>Google Maps ליום</t>
+          <t>לינה בסוף היום</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
+          <t>טיסה חזרה</t>
         </is>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1" s="6">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t>לינה בסוף היום</t>
-        </is>
-      </c>
-      <c r="C151" s="15" t="inlineStr">
-        <is>
-          <t>טיסה חזרה</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="28" customHeight="1" s="6">
-      <c r="A152" s="16" t="inlineStr">
+      <c r="A151" s="16" t="inlineStr">
         <is>
           <t>עלות משוערת ליום ל-4: 0 € (לא כולל תחבורה לשדה)</t>
         </is>
       </c>
-      <c r="B152" s="18" t="n"/>
-      <c r="C152" s="18" t="n"/>
-      <c r="D152" s="18" t="n"/>
-      <c r="E152" s="18" t="n"/>
-      <c r="F152" s="18" t="n"/>
-      <c r="G152" s="18" t="n"/>
-      <c r="H152" s="18" t="n"/>
-      <c r="I152" s="18" t="n"/>
-      <c r="J152" s="19" t="n"/>
-    </row>
+      <c r="B151" s="18" t="n"/>
+      <c r="C151" s="18" t="n"/>
+      <c r="D151" s="18" t="n"/>
+      <c r="E151" s="18" t="n"/>
+      <c r="F151" s="18" t="n"/>
+      <c r="G151" s="18" t="n"/>
+      <c r="H151" s="18" t="n"/>
+      <c r="I151" s="18" t="n"/>
+      <c r="J151" s="19" t="n"/>
+    </row>
+    <row r="152" ht="28" customHeight="1" s="6"/>
     <row r="153" ht="8" customHeight="1" s="6"/>
   </sheetData>
   <mergeCells count="29">
@@ -5955,152 +5904,150 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId184"/>
   </hyperlinks>
   <pageMargins left="0.2" right="0.2" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>

--- a/SLOVAKIA_2026_FINAL_LINKS_FIXED.xlsx
+++ b/SLOVAKIA_2026_FINAL_LINKS_FIXED.xlsx
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="18" customWidth="1" style="6" min="1" max="1"/>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>ביקור אחד ממוקד: חניה ליד Ždiarsky Dom, הליכה בין בתי העץ הגוראליים, צילומים מול ההרים וקפה/עוגה אם רוצים.</t>
+          <t>כפר הררי ציורי, בתי עץ, קפה וצילומים.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>לא חוזרים ל־Ždiar פעם נוספת. לא משוטטים סתם – ביקור קצר וממוקד בלבד.</t>
+          <t>אין צורך במסלול ארוך בתוך הכפר.</t>
         </is>
       </c>
     </row>
@@ -1905,47 +1905,47 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>Bobová dráha Bachledka – מגלשת ההרים</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Ždiar</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Bachledka Ski &amp; Sun</t>
+          <t>Obria lavička</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bachledka Ski &amp; Sun, Ždiar 702, Slovakia</t>
+          <t>Obria lavička Ždiar</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>🚶 באותו מתחם</t>
+          <t>5–10 דק׳</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>30–45 דק׳</t>
+          <t>20–30 דק׳</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>€44 ל־4 לסיבוב רגיל; €36 ל־4 אם מספיקים למבצע עד 10:30</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>מגלשת הרים חדשה באורך 1,520 מ׳, 20 פניות ועד 40 קמ״ש. שולטים במהירות לבד.</t>
+          <t>ספסל ענק מול הנוף ונקודת צילום מיוחדת.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>באותו מתחם – אין נסיעה נוספת. יש למלא טופס לפני הנסיעה.</t>
+          <t>עצירה קצרה ונוחה.</t>
         </is>
       </c>
     </row>
@@ -1957,22 +1957,22 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Ždiar</t>
+          <t>Obria lavička</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Obria lavička</t>
+          <t>Strednica Viewpoint</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Obria lavička Ždiar</t>
+          <t>Strednica Ždiar</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>20–30 דק׳</t>
+          <t>30–45 דק׳</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>ספסל ענק מול הנוף ונקודת צילום מיוחדת.</t>
+          <t>תצפית פתוחה על רכס Belianske Tatras.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>עצירה קצרה ונוחה.</t>
+          <t>כמעט ללא הליכה.</t>
         </is>
       </c>
     </row>
@@ -2009,22 +2009,22 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Obria lavička</t>
+          <t>Strednica Viewpoint</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Strednica Viewpoint</t>
+          <t>ארוחת צהריים באזור Ždiar</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Strednica Ždiar</t>
+          <t>Ždiar, Slovakia</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>30–45 דק׳</t>
+          <t>60 דק׳</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>תצפית פתוחה על רכס Belianske Tatras.</t>
+          <t>ארוחה רגועה וקפה.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>כמעט ללא הליכה.</t>
+          <t>אפשר להזיז לפי עומס ומזג אוויר.</t>
         </is>
       </c>
     </row>
@@ -2061,147 +2061,143 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Strednica Viewpoint</t>
+          <t>ארוחת צהריים באזור Ždiar</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ארוחת צהריים באזור Ždiar</t>
+          <t>Hotel International</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ždiar, Slovakia</t>
+          <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>5–10 דק׳</t>
+          <t>30–35 דק׳</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>60 דק׳</t>
+          <t>ערב</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>קפה/מאפה/נשנוש קצר בלבד למי שרוצה.</t>
+          <t>חזרה לספא ולארוחת ערב.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>אין ארוחת צהריים מלאה; אוכלים בוקר וערב במלון.</t>
+          <t>Belianska Cave נשארת חלופת גשם בלבד.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" s="6">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>24.9.2026 – יום ה׳</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים באזור Ždiar</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Hotel International</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Hotel International, Veľká Lomnica</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>30–35 דק׳</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>ערב</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>כלול לפי חבילת המלון</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>חזרה לספא ולארוחת ערב.</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Belianska Cave נשארת חלופת גשם בלבד.</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Google Maps ליום</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" s="6">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Google Maps ליום</t>
+          <t>לינה בסוף היום</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
+          <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" s="6">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>לינה בסוף היום</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>עלות משוערת ליום ל-4: Bachledka ל־4: €116 אונליין / €120 בקופה; שאר היום חינם.</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="n"/>
+      <c r="C40" s="18" t="n"/>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="18" t="n"/>
+      <c r="G40" s="18" t="n"/>
+      <c r="H40" s="18" t="n"/>
+      <c r="I40" s="18" t="n"/>
+      <c r="J40" s="19" t="n"/>
+    </row>
+    <row r="41" ht="6" customHeight="1" s="6"/>
+    <row r="42" ht="32" customHeight="1" s="6">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>חלופה | 24.9 חלופת גשם | חלופת גשם: Belianska Cave, Kežmarok ו־Poprad</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1" s="6">
+      <c r="A43" s="34" t="inlineStr">
+        <is>
+          <t>24.9.2026 – חלופה</t>
+        </is>
+      </c>
+      <c r="B43" s="35" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C43" s="34" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Hotel International – יציאה</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="6" customHeight="1" s="6">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>עלות משוערת ליום ל-4: Bachledka €116 אונליין / €120 בקופה + מגלשת Bachledka €44 ל־4 לסיבוב (או €36 במבצע בוקר אם מספיקים).</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="18" t="n"/>
-      <c r="D41" s="18" t="n"/>
-      <c r="E41" s="18" t="n"/>
-      <c r="F41" s="18" t="n"/>
-      <c r="G41" s="18" t="n"/>
-      <c r="H41" s="18" t="n"/>
-      <c r="I41" s="18" t="n"/>
-      <c r="J41" s="19" t="n"/>
-    </row>
-    <row r="42" ht="32" customHeight="1" s="6"/>
-    <row r="43" ht="58" customHeight="1" s="6">
-      <c r="A43" s="32" t="inlineStr">
-        <is>
-          <t>חלופה | 24.9 חלופת גשם | חלופת גשם: Belianska Cave, Kežmarok ו־Poprad</t>
+      <c r="F43" s="35" t="inlineStr">
+        <is>
+          <t>25–30 דק׳</t>
+        </is>
+      </c>
+      <c r="G43" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="35" t="inlineStr">
+        <is>
+          <t>כלול לפי חבילת המלון</t>
+        </is>
+      </c>
+      <c r="I43" s="34" t="inlineStr">
+        <is>
+          <t>יציאה לכיוון מערת Belianska.</t>
+        </is>
+      </c>
+      <c r="J43" s="34" t="inlineStr">
+        <is>
+          <t>להגיע מוקדם כדי לתפוס סיור.</t>
         </is>
       </c>
     </row>
@@ -2213,43 +2209,47 @@
       </c>
       <c r="B44" s="35" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C44" s="34" t="inlineStr"/>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C44" s="34" t="inlineStr">
+        <is>
+          <t>Hotel International – יציאה</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Hotel International – יציאה</t>
+          <t>Belianska Cave</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hotel International, Veľká Lomnica</t>
+          <t>Belianska jaskyňa</t>
         </is>
       </c>
       <c r="F44" s="35" t="inlineStr">
         <is>
-          <t>25–30 דק׳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G44" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1:30–2:00 ש׳</t>
         </is>
       </c>
       <c r="H44" s="35" t="inlineStr">
         <is>
-          <t>כלול לפי חבילת המלון</t>
+          <t>€60 ל־4 (15€ לאדם)</t>
         </is>
       </c>
       <c r="I44" s="34" t="inlineStr">
         <is>
-          <t>יציאה לכיוון מערת Belianska.</t>
+          <t>מערת נטיפים מרשימה – חלופה מצוינת למזג אוויר גשום.</t>
         </is>
       </c>
       <c r="J44" s="34" t="inlineStr">
         <is>
-          <t>להגיע מוקדם כדי לתפוס סיור.</t>
+          <t>יש עלייה רגלית לכניסה; קר בפנים.</t>
         </is>
       </c>
     </row>
@@ -2261,47 +2261,47 @@
       </c>
       <c r="B45" s="35" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>Hotel International – יציאה</t>
+          <t>Belianska Cave</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Belianska Cave</t>
+          <t>Kežmarok – מרכז עתיק</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Belianska jaskyňa</t>
+          <t>Hradné námestie, Kežmarok</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20–25 דק׳</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
         <is>
-          <t>1:30–2:00 ש׳</t>
+          <t>1:15 ש׳</t>
         </is>
       </c>
       <c r="H45" s="35" t="inlineStr">
         <is>
-          <t>€60 ל־4 (15€ לאדם)</t>
+          <t>המרכז חינם; כניסה לטירה רק אם בוחרים</t>
         </is>
       </c>
       <c r="I45" s="34" t="inlineStr">
         <is>
-          <t>מערת נטיפים מרשימה – חלופה מצוינת למזג אוויר גשום.</t>
+          <t>טירה, כיכר עתיקה, קפה וארוחת צהריים.</t>
         </is>
       </c>
       <c r="J45" s="34" t="inlineStr">
         <is>
-          <t>יש עלייה רגלית לכניסה; קר בפנים.</t>
+          <t>חניה בתשלום במרכז; לא נמצא חניון חינם ציבורי מאומת.</t>
         </is>
       </c>
     </row>
@@ -2313,22 +2313,22 @@
       </c>
       <c r="B46" s="35" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>Belianska Cave</t>
+          <t>Kežmarok – מרכז עתיק</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Kežmarok – מרכז עתיק</t>
+          <t>Poprad – Forum / מרכז</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hradné námestie, Kežmarok</t>
+          <t>Forum Poprad</t>
         </is>
       </c>
       <c r="F46" s="35" t="inlineStr">
@@ -2338,22 +2338,22 @@
       </c>
       <c r="G46" s="35" t="inlineStr">
         <is>
-          <t>1:15 ש׳</t>
+          <t>1:30–2:00 ש׳</t>
         </is>
       </c>
       <c r="H46" s="35" t="inlineStr">
         <is>
-          <t>המרכז חינם; כניסה לטירה רק אם בוחרים</t>
+          <t>חינם; קניות/אוכל לפי בחירה</t>
         </is>
       </c>
       <c r="I46" s="34" t="inlineStr">
         <is>
-          <t>טירה, כיכר עתיקה, קפה וארוחת צהריים.</t>
+          <t>קניות קלות, קפה וגלידה במקום מקורה.</t>
         </is>
       </c>
       <c r="J46" s="34" t="inlineStr">
         <is>
-          <t>חניה בתשלום במרכז; לא נמצא חניון חינם ציבורי מאומת.</t>
+          <t>Forum: 2 שעות ראשונות חינם ביום חול.</t>
         </is>
       </c>
     </row>
@@ -2365,143 +2365,139 @@
       </c>
       <c r="B47" s="35" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>Kežmarok – מרכז עתיק</t>
+          <t>Poprad – Forum / מרכז</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Poprad – Forum / מרכז</t>
+          <t>Hotel International</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Forum Poprad</t>
+          <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>20–25 דק׳</t>
+          <t>15–20 דק׳</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
         <is>
-          <t>1:30–2:00 ש׳</t>
+          <t>ערב</t>
         </is>
       </c>
       <c r="H47" s="35" t="inlineStr">
         <is>
-          <t>חינם; קניות/אוכל לפי בחירה</t>
+          <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
       <c r="I47" s="34" t="inlineStr">
         <is>
-          <t>קניות קלות, קפה וגלידה במקום מקורה.</t>
+          <t>חזרה לספא וארוחת ערב.</t>
         </is>
       </c>
       <c r="J47" s="34" t="inlineStr">
         <is>
-          <t>Forum: 2 שעות ראשונות חינם ביום חול.</t>
+          <t>אם מזג האוויר משתפר אפשר להוסיף עצירה קצרה בתצפית.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1" s="6">
-      <c r="A48" s="34" t="inlineStr">
-        <is>
-          <t>24.9.2026 – חלופה</t>
-        </is>
-      </c>
-      <c r="B48" s="35" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C48" s="34" t="inlineStr">
-        <is>
-          <t>Poprad – Forum / מרכז</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Hotel International</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Hotel International, Veľká Lomnica</t>
-        </is>
-      </c>
-      <c r="F48" s="35" t="inlineStr">
-        <is>
-          <t>15–20 דק׳</t>
-        </is>
-      </c>
-      <c r="G48" s="35" t="inlineStr">
-        <is>
-          <t>ערב</t>
-        </is>
-      </c>
-      <c r="H48" s="35" t="inlineStr">
-        <is>
-          <t>כלול לפי חבילת המלון</t>
-        </is>
-      </c>
-      <c r="I48" s="34" t="inlineStr">
-        <is>
-          <t>חזרה לספא וארוחת ערב.</t>
-        </is>
-      </c>
-      <c r="J48" s="34" t="inlineStr">
-        <is>
-          <t>אם מזג האוויר משתפר אפשר להוסיף עצירה קצרה בתצפית.</t>
-        </is>
-      </c>
+      <c r="A48" s="36" t="inlineStr">
+        <is>
+          <t>Google Maps לחלופה</t>
+        </is>
+      </c>
+      <c r="B48" s="37" t="n"/>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
+        </is>
+      </c>
+      <c r="D48" s="37" t="n"/>
+      <c r="E48" s="37" t="n"/>
+      <c r="F48" s="37" t="n"/>
+      <c r="G48" s="37" t="n"/>
+      <c r="H48" s="37" t="n"/>
+      <c r="I48" s="37" t="n"/>
+      <c r="J48" s="37" t="n"/>
     </row>
     <row r="49" ht="28" customHeight="1" s="6">
-      <c r="A49" s="36" t="inlineStr">
-        <is>
-          <t>Google Maps לחלופה</t>
-        </is>
-      </c>
-      <c r="B49" s="37" t="n"/>
-      <c r="C49" s="15" t="inlineStr">
-        <is>
-          <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
-        </is>
-      </c>
-      <c r="D49" s="37" t="n"/>
-      <c r="E49" s="37" t="n"/>
-      <c r="F49" s="37" t="n"/>
-      <c r="G49" s="37" t="n"/>
-      <c r="H49" s="37" t="n"/>
-      <c r="I49" s="37" t="n"/>
-      <c r="J49" s="37" t="n"/>
-    </row>
-    <row r="50" ht="8" customHeight="1" s="6">
-      <c r="A50" s="39" t="inlineStr">
+      <c r="A49" s="39" t="inlineStr">
         <is>
           <t>עלות החלופה ל-4: Belianska Cave: €60 ל־4; Kežmarok/Poprad ללא כניסה חובה.</t>
         </is>
       </c>
-      <c r="B50" s="18" t="n"/>
-      <c r="C50" s="18" t="n"/>
-      <c r="D50" s="18" t="n"/>
-      <c r="E50" s="18" t="n"/>
-      <c r="F50" s="18" t="n"/>
-      <c r="G50" s="18" t="n"/>
-      <c r="H50" s="18" t="n"/>
-      <c r="I50" s="18" t="n"/>
-      <c r="J50" s="19" t="n"/>
-    </row>
-    <row r="51" ht="28" customHeight="1" s="6"/>
+      <c r="B49" s="18" t="n"/>
+      <c r="C49" s="18" t="n"/>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="18" t="n"/>
+      <c r="G49" s="18" t="n"/>
+      <c r="H49" s="18" t="n"/>
+      <c r="I49" s="18" t="n"/>
+      <c r="J49" s="19" t="n"/>
+    </row>
+    <row r="50" ht="8" customHeight="1" s="6"/>
+    <row r="51" ht="28" customHeight="1" s="6">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>יום ו׳ | 25.9.2026 | Suchá Belá – נקיק הסולמות, ולאחריו Tatrabob</t>
+        </is>
+      </c>
+    </row>
     <row r="52" ht="58" customHeight="1" s="6">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>יום ו׳ | 25.9.2026 | Suchá Belá – נקיק הסולמות, ולאחריו Tatrabob</t>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>25.9.2026 – יום ו׳</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Podlesok – Suchá Belá</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Podlesok, Slovenský raj</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>45–60 דק׳</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>20–30 דק׳</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>€16 ל־4 כניסת Suchá Belá + חניה בנפרד</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>נסיעה לנקודת ההתחלה וחניה.</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>להגיע מוקדם לפני העומס על הסולמות.</t>
         </is>
       </c>
     </row>
@@ -2513,43 +2509,47 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr"/>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Podlesok – Suchá Belá</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Podlesok – Suchá Belá</t>
+          <t>Suchá Belá Gorge</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Podlesok, Slovenský raj</t>
+          <t>Suchá Belá, Podlesok</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>45–60 דק׳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>20–30 דק׳</t>
+          <t>4:00–5:00 ש׳</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>€16 ל־4 כניסת Suchá Belá + חניה בנפרד</t>
+          <t>€16 ל־4 (4€ לאדם)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Podlesok הוא החניון ונקודת היציאה ל־Suchá Belá. מחנים ומתארגנים ומכאן יוצאים ברגל לערוץ.</t>
+          <t>נקיק צר עם מפלים, גשרי עץ וסולמות מתכת גבוהים.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>להגיע מוקדם לפני העומס על הסולמות.</t>
+          <t>מסלול חד־כיווני; נעלי הליכה חובה ולא בגשם חזק.</t>
         </is>
       </c>
     </row>
@@ -2561,22 +2561,22 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Podlesok – Suchá Belá</t>
+          <t>Suchá Belá Gorge</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Suchá Belá Gorge</t>
+          <t>ארוחת צהריים ב־Podlesok</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Suchá Belá, Podlesok</t>
+          <t>Podlesok</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2586,22 +2586,22 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>4:00–5:00 ש׳</t>
+          <t>45–60 דק׳</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>€16 ל־4 (4€ לאדם)</t>
+          <t>€16 ל־4 כניסת Suchá Belá + חניה בנפרד</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>נקיק צר עם מפלים, גשרי עץ וסולמות מתכת גבוהים.</t>
+          <t>ארוחה ומנוחה לאחר המסלול.</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>מסלול חד־כיווני; נעלי הליכה חובה ולא בגשם חזק.</t>
+          <t>לא להתעכב כדי להספיק את המגלשה.</t>
         </is>
       </c>
     </row>
@@ -2613,27 +2613,27 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Suchá Belá Gorge</t>
+          <t>ארוחת צהריים ב־Podlesok</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ארוחת צהריים ב־Podlesok</t>
+          <t>Tatrabob – Tatranská Lomnica</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Podlesok</t>
+          <t>Tatrabob Tatranská Lomnica</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45–55 דק׳</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -2643,17 +2643,17 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>€16 ל־4 כניסת Suchá Belá + חניה בנפרד</t>
+          <t>€36 ל־4 לסיבוב אחד (9€ לאדם)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>מנוחה קצרה, שתייה, קפה/מאפה או נשנוש אחרי המסלול.</t>
+          <t>מגלשת הרים על מסילה עם שליטה אישית במהירות.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>לא ארוחת צהריים מלאה – שומרים זמן ל־Tatrabob ולחזרה למלון סביב 17:00.</t>
+          <t>לבדוק שעות פעילות ומזג אוויר סמוך ליום.</t>
         </is>
       </c>
     </row>
@@ -2665,147 +2665,143 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>ארוחת צהריים ב־Podlesok</t>
+          <t>Tatrabob – Tatranská Lomnica</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tatrabob – Tatranská Lomnica</t>
+          <t>Hotel International</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tatrabob Tatranská Lomnica</t>
+          <t>Hotel International</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>45–55 דק׳</t>
+          <t>10–15 דק׳</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>45–60 דק׳</t>
+          <t>ערב</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>€36 ל־4 לסיבוב אחד (9€ לאדם)</t>
+          <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>מגלשת הרים על מסילה עם שליטה אישית במהירות.</t>
+          <t>חזרה למלון, ספא וארוחת ערב.</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>לבדוק שעות פעילות ומזג אוויר סמוך ליום.</t>
+          <t>המגלשה קרובה למלון ולכן משתלבת היטב.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1" s="6">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>25.9.2026 – יום ו׳</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Tatrabob – Tatranská Lomnica</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Hotel International</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Hotel International</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>10–15 דק׳</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>ערב</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>כלול לפי חבילת המלון</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>חזרה למלון, ספא וארוחת ערב.</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>המגלשה קרובה למלון ולכן משתלבת היטב.</t>
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Google Maps ליום</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" s="6">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Google Maps ליום</t>
+          <t>לינה בסוף היום</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
+          <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1" s="6">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>לינה בסוף היום</t>
-        </is>
-      </c>
-      <c r="C59" s="15" t="inlineStr">
-        <is>
-          <t>Hotel International, Veľká Lomnica</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="6" customHeight="1" s="6">
-      <c r="A60" s="16" t="inlineStr">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>עלות משוערת ליום ל-4: Suchá Belá €16 ל־4 + Tatrabob €36 ל־4 לסיבוב אחד = כ־€52 + חניה.</t>
         </is>
       </c>
-      <c r="B60" s="18" t="n"/>
-      <c r="C60" s="18" t="n"/>
-      <c r="D60" s="18" t="n"/>
-      <c r="E60" s="18" t="n"/>
-      <c r="F60" s="18" t="n"/>
-      <c r="G60" s="18" t="n"/>
-      <c r="H60" s="18" t="n"/>
-      <c r="I60" s="18" t="n"/>
-      <c r="J60" s="19" t="n"/>
-    </row>
-    <row r="61" ht="32" customHeight="1" s="6"/>
+      <c r="B59" s="18" t="n"/>
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="18" t="n"/>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n"/>
+      <c r="G59" s="18" t="n"/>
+      <c r="H59" s="18" t="n"/>
+      <c r="I59" s="18" t="n"/>
+      <c r="J59" s="19" t="n"/>
+    </row>
+    <row r="60" ht="6" customHeight="1" s="6"/>
+    <row r="61" ht="32" customHeight="1" s="6">
+      <c r="A61" s="32" t="inlineStr">
+        <is>
+          <t>חלופה | 25.9 חלופה – פסגות | חלופה ל־Suchá Belá: יום פסגות – Skalnaté Pleso, Lomnický štít / Lomnické sedlo, Veľká Svišťovka ו־Mountain Carts</t>
+        </is>
+      </c>
+    </row>
     <row r="62" ht="58" customHeight="1" s="6">
-      <c r="A62" s="32" t="inlineStr">
-        <is>
-          <t>חלופה | 25.9 חלופה – פסגות | חלופה ל־Suchá Belá: יום פסגות – Skalnaté Pleso, Lomnický štít / Lomnické sedlo, Veľká Svišťovka ו־Mountain Carts</t>
+      <c r="A62" s="34" t="inlineStr">
+        <is>
+          <t>25.9.2026 – חלופה</t>
+        </is>
+      </c>
+      <c r="B62" s="35" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C62" s="34" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Tatranská Lomnica – חניה ורכבל</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Tatranská Lomnica Cable Car</t>
+        </is>
+      </c>
+      <c r="F62" s="35" t="inlineStr">
+        <is>
+          <t>10–15 דק׳</t>
+        </is>
+      </c>
+      <c r="G62" s="35" t="inlineStr">
+        <is>
+          <t>20–30 דק׳</t>
+        </is>
+      </c>
+      <c r="H62" s="35" t="inlineStr">
+        <is>
+          <t>חניה חינם ב־Eurocamp או כ־€10 ליום ליד הרכבל</t>
+        </is>
+      </c>
+      <c r="I62" s="34" t="inlineStr">
+        <is>
+          <t>חניה והתארגנות לרכבלים.</t>
+        </is>
+      </c>
+      <c r="J62" s="34" t="inlineStr">
+        <is>
+          <t>אפשר חניה חינם ב־Eurocamp או חניה בתשלום ליד הרכבל.</t>
         </is>
       </c>
     </row>
@@ -2817,43 +2813,47 @@
       </c>
       <c r="B63" s="35" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="C63" s="34" t="inlineStr"/>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="C63" s="34" t="inlineStr">
+        <is>
+          <t>Tatranská Lomnica – חניה ורכבל</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tatranská Lomnica – חניה ורכבל</t>
+          <t>Skalnaté Pleso</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tatranská Lomnica Cable Car</t>
+          <t>Skalnaté Pleso</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>10–15 דק׳</t>
+          <t>רכבל</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
         <is>
-          <t>20–30 דק׳</t>
+          <t>45–60 דק׳</t>
         </is>
       </c>
       <c r="H63" s="35" t="inlineStr">
         <is>
-          <t>חניה חינם ב־Eurocamp או כ־€10 ליום ליד הרכבל</t>
+          <t>מחיר Gopass דינמי</t>
         </is>
       </c>
       <c r="I63" s="34" t="inlineStr">
         <is>
-          <t>חניה והתארגנות לרכבלים.</t>
+          <t>עלייה לאגם האלפיני בגובה כ־1,751 מ׳.</t>
         </is>
       </c>
       <c r="J63" s="34" t="inlineStr">
         <is>
-          <t>אפשר חניה חינם ב־Eurocamp או חניה בתשלום ליד הרכבל.</t>
+          <t>להזמין Gopass מראש אם אפשר.</t>
         </is>
       </c>
     </row>
@@ -2865,47 +2865,47 @@
       </c>
       <c r="B64" s="35" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>Tatranská Lomnica – חניה ורכבל</t>
+          <t>Skalnaté Pleso</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Skalnaté Pleso</t>
+          <t>Lomnický štít – אם יש כרטיס</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Skalnaté Pleso</t>
+          <t>Lomnický štít</t>
         </is>
       </c>
       <c r="F64" s="35" t="inlineStr">
         <is>
-          <t>רכבל</t>
+          <t>רכבל מיוחד</t>
         </is>
       </c>
       <c r="G64" s="35" t="inlineStr">
         <is>
-          <t>45–60 דק׳</t>
+          <t>60–90 דק׳</t>
         </is>
       </c>
       <c r="H64" s="35" t="inlineStr">
         <is>
-          <t>מחיר Gopass דינמי</t>
+          <t>מחיר Gopass דינמי – חובה לבדוק/להזמין מראש</t>
         </is>
       </c>
       <c r="I64" s="34" t="inlineStr">
         <is>
-          <t>עלייה לאגם האלפיני בגובה כ־1,751 מ׳.</t>
+          <t>פסגת לומניצקי בגובה 2,634 מ׳ – תצפית ה־WOW של היום.</t>
         </is>
       </c>
       <c r="J64" s="34" t="inlineStr">
         <is>
-          <t>להזמין Gopass מראש אם אפשר.</t>
+          <t>השעה בכרטיס היא היציאה מ־Skalnaté Pleso; קיבולת מוגבלת.</t>
         </is>
       </c>
     </row>
@@ -2917,47 +2917,47 @@
       </c>
       <c r="B65" s="35" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C65" s="34" t="inlineStr">
         <is>
-          <t>Skalnaté Pleso</t>
+          <t>Lomnický štít – אם יש כרטיס</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Lomnický štít – אם יש כרטיס</t>
+          <t>Lomnické sedlo</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lomnický štít</t>
+          <t>Lomnické sedlo</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>רכבל מיוחד</t>
+          <t>רכבל כיסאות</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
         <is>
-          <t>60–90 דק׳</t>
+          <t>60–75 דק׳</t>
         </is>
       </c>
       <c r="H65" s="35" t="inlineStr">
         <is>
-          <t>מחיר Gopass דינמי – חובה לבדוק/להזמין מראש</t>
+          <t>מחיר Gopass דינמי</t>
         </is>
       </c>
       <c r="I65" s="34" t="inlineStr">
         <is>
-          <t>פסגת לומניצקי בגובה 2,634 מ׳ – תצפית ה־WOW של היום.</t>
+          <t>אוכף הרים בגובה כ־2,190 מ׳ עם נוף חד לפסגות.</t>
         </is>
       </c>
       <c r="J65" s="34" t="inlineStr">
         <is>
-          <t>השעה בכרטיס היא היציאה מ־Skalnaté Pleso; קיבולת מוגבלת.</t>
+          <t>אם עלינו ל־Lomnický štít והזמן קצר – אפשר לקצר כאן.</t>
         </is>
       </c>
     </row>
@@ -2969,47 +2969,47 @@
       </c>
       <c r="B66" s="35" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
-          <t>Lomnický štít – אם יש כרטיס</t>
+          <t>Lomnické sedlo</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Lomnické sedlo</t>
+          <t>Veľká Svišťovka – אופציונלי</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lomnické sedlo</t>
+          <t>Veľká Svišťovka</t>
         </is>
       </c>
       <c r="F66" s="35" t="inlineStr">
         <is>
-          <t>רכבל כיסאות</t>
+          <t>הליכה</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
         <is>
-          <t>60–75 דק׳</t>
+          <t>2:30–3:00 ש׳</t>
         </is>
       </c>
       <c r="H66" s="35" t="inlineStr">
         <is>
-          <t>מחיר Gopass דינמי</t>
+          <t>חינם – מסלול הליכה</t>
         </is>
       </c>
       <c r="I66" s="34" t="inlineStr">
         <is>
-          <t>אוכף הרים בגובה כ־2,190 מ׳ עם נוף חד לפסגות.</t>
+          <t>מסלול הררי ותצפיות גבוהות; לבצע רק בתנאים יבשים.</t>
         </is>
       </c>
       <c r="J66" s="34" t="inlineStr">
         <is>
-          <t>אם עלינו ל־Lomnický štít והזמן קצר – אפשר לקצר כאן.</t>
+          <t>לא לבצע בערפל/גשם/סלע רטוב. אם יש פסגה + עומס, לוותר.</t>
         </is>
       </c>
     </row>
@@ -3021,47 +3021,47 @@
       </c>
       <c r="B67" s="35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C67" s="34" t="inlineStr">
         <is>
-          <t>Lomnické sedlo</t>
+          <t>Veľká Svišťovka – אופציונלי</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Veľká Svišťovka – אופציונלי</t>
+          <t>Štart / Mountain Carts</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Veľká Svišťovka</t>
+          <t>Mountain Carts Tatranská Lomnica</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>הליכה</t>
+          <t>רכבל</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
         <is>
-          <t>2:30–3:00 ש׳</t>
+          <t>30–45 דק׳</t>
         </is>
       </c>
       <c r="H67" s="35" t="inlineStr">
         <is>
-          <t>חינם – מסלול הליכה</t>
+          <t>מחיר משתנה – לבדוק ב־Gopass/באתר ביום הקנייה</t>
         </is>
       </c>
       <c r="I67" s="34" t="inlineStr">
         <is>
-          <t>מסלול הררי ותצפיות גבוהות; לבצע רק בתנאים יבשים.</t>
+          <t>ירידה חווייתית במסלול אספלט של כ־3 ק״מ.</t>
         </is>
       </c>
       <c r="J67" s="34" t="inlineStr">
         <is>
-          <t>לא לבצע בערפל/גשם/סלע רטוב. אם יש פסגה + עומס, לוותר.</t>
+          <t>אופציונלי ובכפוף לפעילות ומזג אוויר.</t>
         </is>
       </c>
     </row>
@@ -3073,27 +3073,27 @@
       </c>
       <c r="B68" s="35" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C68" s="34" t="inlineStr">
         <is>
-          <t>Veľká Svišťovka – אופציונלי</t>
+          <t>Štart / Mountain Carts</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Štart / Mountain Carts</t>
+          <t>Starý Smokovec – רק אם נשאר זמן</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mountain Carts Tatranská Lomnica</t>
+          <t>Starý Smokovec</t>
         </is>
       </c>
       <c r="F68" s="35" t="inlineStr">
         <is>
-          <t>רכבל</t>
+          <t>15–20 דק׳</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="H68" s="35" t="inlineStr">
         <is>
-          <t>מחיר משתנה – לבדוק ב־Gopass/באתר ביום הקנייה</t>
+          <t>חינם לסיבוב בעיירה</t>
         </is>
       </c>
       <c r="I68" s="34" t="inlineStr">
         <is>
-          <t>ירידה חווייתית במסלול אספלט של כ־3 ק״מ.</t>
+          <t>קפה/גלידה וסיבוב קצר בעיירה.</t>
         </is>
       </c>
       <c r="J68" s="34" t="inlineStr">
         <is>
-          <t>אופציונלי ובכפוף לפעילות ומזג אוויר.</t>
+          <t>אם היום בהר התארך – חוזרים ישר למלון.</t>
         </is>
       </c>
     </row>
@@ -3125,143 +3125,139 @@
       </c>
       <c r="B69" s="35" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C69" s="34" t="inlineStr">
         <is>
-          <t>Štart / Mountain Carts</t>
+          <t>Starý Smokovec – רק אם נשאר זמן</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Starý Smokovec – רק אם נשאר זמן</t>
+          <t>Hotel International</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Starý Smokovec</t>
+          <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>15–20 דק׳</t>
+          <t>20–25 דק׳</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
         <is>
-          <t>30–45 דק׳</t>
+          <t>ערב</t>
         </is>
       </c>
       <c r="H69" s="35" t="inlineStr">
         <is>
-          <t>חינם לסיבוב בעיירה</t>
+          <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
       <c r="I69" s="34" t="inlineStr">
         <is>
-          <t>קפה/גלידה וסיבוב קצר בעיירה.</t>
+          <t>חזרה למלון, ספא וארוחת ערב.</t>
         </is>
       </c>
       <c r="J69" s="34" t="inlineStr">
         <is>
-          <t>אם היום בהר התארך – חוזרים ישר למלון.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1" s="6">
-      <c r="A70" s="34" t="inlineStr">
+      <c r="A70" s="36" t="inlineStr">
+        <is>
+          <t>Google Maps לחלופה</t>
+        </is>
+      </c>
+      <c r="B70" s="37" t="n"/>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
+        </is>
+      </c>
+      <c r="D70" s="37" t="n"/>
+      <c r="E70" s="37" t="n"/>
+      <c r="F70" s="37" t="n"/>
+      <c r="G70" s="37" t="n"/>
+      <c r="H70" s="37" t="n"/>
+      <c r="I70" s="37" t="n"/>
+      <c r="J70" s="37" t="n"/>
+    </row>
+    <row r="71" ht="28" customHeight="1" s="6">
+      <c r="A71" s="39" t="inlineStr">
+        <is>
+          <t>עלות החלופה ל-4: כ־€220–360 ל־4 לפי כרטיסי הרכבל והאם עולים ל־Lomnický štít</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="n"/>
+      <c r="C71" s="18" t="n"/>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="18" t="n"/>
+      <c r="F71" s="18" t="n"/>
+      <c r="G71" s="18" t="n"/>
+      <c r="H71" s="18" t="n"/>
+      <c r="I71" s="18" t="n"/>
+      <c r="J71" s="19" t="n"/>
+    </row>
+    <row r="72" ht="6" customHeight="1" s="6"/>
+    <row r="73" ht="32" customHeight="1" s="6">
+      <c r="A73" s="32" t="inlineStr">
+        <is>
+          <t>חלופה | 25.9 חלופה רגועה – Štrbské Pleso | חלופה רגועה / ראות בינונית: Štrbské Pleso – אגם, הליכה וקפה</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="58" customHeight="1" s="6">
+      <c r="A74" s="34" t="inlineStr">
         <is>
           <t>25.9.2026 – חלופה</t>
         </is>
       </c>
-      <c r="B70" s="35" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C70" s="34" t="inlineStr">
-        <is>
-          <t>Starý Smokovec – רק אם נשאר זמן</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Hotel International</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Hotel International, Veľká Lomnica</t>
-        </is>
-      </c>
-      <c r="F70" s="35" t="inlineStr">
-        <is>
-          <t>20–25 דק׳</t>
-        </is>
-      </c>
-      <c r="G70" s="35" t="inlineStr">
-        <is>
-          <t>ערב</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>כלול לפי חבילת המלון</t>
-        </is>
-      </c>
-      <c r="I70" s="34" t="inlineStr">
-        <is>
-          <t>חזרה למלון, ספא וארוחת ערב.</t>
-        </is>
-      </c>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="28" customHeight="1" s="6">
-      <c r="A71" s="36" t="inlineStr">
-        <is>
-          <t>Google Maps לחלופה</t>
-        </is>
-      </c>
-      <c r="B71" s="37" t="n"/>
-      <c r="C71" s="15" t="inlineStr">
-        <is>
-          <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
-        </is>
-      </c>
-      <c r="D71" s="37" t="n"/>
-      <c r="E71" s="37" t="n"/>
-      <c r="F71" s="37" t="n"/>
-      <c r="G71" s="37" t="n"/>
-      <c r="H71" s="37" t="n"/>
-      <c r="I71" s="37" t="n"/>
-      <c r="J71" s="37" t="n"/>
-    </row>
-    <row r="72" ht="6" customHeight="1" s="6">
-      <c r="A72" s="39" t="inlineStr">
-        <is>
-          <t>עלות החלופה ל-4: כ־€220–360 ל־4 לפי כרטיסי הרכבל והאם עולים ל־Lomnický štít</t>
-        </is>
-      </c>
-      <c r="B72" s="18" t="n"/>
-      <c r="C72" s="18" t="n"/>
-      <c r="D72" s="18" t="n"/>
-      <c r="E72" s="18" t="n"/>
-      <c r="F72" s="18" t="n"/>
-      <c r="G72" s="18" t="n"/>
-      <c r="H72" s="18" t="n"/>
-      <c r="I72" s="18" t="n"/>
-      <c r="J72" s="19" t="n"/>
-    </row>
-    <row r="73" ht="32" customHeight="1" s="6"/>
-    <row r="74" ht="58" customHeight="1" s="6">
-      <c r="A74" s="32" t="inlineStr">
-        <is>
-          <t>חלופה | 25.9 חלופה רגועה – Štrbské Pleso | חלופה רגועה / ראות בינונית: Štrbské Pleso – אגם, הליכה וקפה</t>
+      <c r="B74" s="35" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C74" s="34" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Štrbské Pleso – חניה</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Central parking Štrbské Pleso</t>
+        </is>
+      </c>
+      <c r="F74" s="35" t="inlineStr">
+        <is>
+          <t>🚗 35–45 דק׳</t>
+        </is>
+      </c>
+      <c r="G74" s="35" t="inlineStr">
+        <is>
+          <t>10–15 דק׳</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>כ־€12 לרכב (חניה; לבדוק במקום)</t>
+        </is>
+      </c>
+      <c r="I74" s="34" t="inlineStr">
+        <is>
+          <t>מחנים ליד מרכז העיירה ויוצאים ברגל לאגם.</t>
+        </is>
+      </c>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>החניה שדווחה ע״י מטיילים הייתה כ־€12 ליום; לבדוק תעריף במקום.</t>
         </is>
       </c>
     </row>
@@ -3273,43 +3269,47 @@
       </c>
       <c r="B75" s="35" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C75" s="34" t="inlineStr"/>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C75" s="34" t="inlineStr">
+        <is>
+          <t>Štrbské Pleso – חניה</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Štrbské Pleso – חניה</t>
+          <t>Štrbské Pleso – סיבוב סביב האגם</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Central parking Štrbské Pleso</t>
+          <t>Štrbské Pleso</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>🚗 35–45 דק׳</t>
+          <t>🚶 5–10 דק׳</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
         <is>
-          <t>10–15 דק׳</t>
+          <t>1:15–1:45 ש׳</t>
         </is>
       </c>
       <c r="H75" s="35" t="inlineStr">
         <is>
-          <t>כ־€12 לרכב (חניה; לבדוק במקום)</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I75" s="34" t="inlineStr">
         <is>
-          <t>מחנים ליד מרכז העיירה ויוצאים ברגל לאגם.</t>
+          <t>הליכה קלה סביב האגם האלפיני, תצפיות לפסגות, צילום וקפה.</t>
         </is>
       </c>
       <c r="J75" s="34" t="inlineStr">
         <is>
-          <t>החניה שדווחה ע״י מטיילים הייתה כ־€12 ליום; לבדוק תעריף במקום.</t>
+          <t>מסלול נוח וגמיש; אפשר לקצר בכל שלב.</t>
         </is>
       </c>
     </row>
@@ -3321,17 +3321,17 @@
       </c>
       <c r="B76" s="35" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C76" s="34" t="inlineStr">
         <is>
-          <t>Štrbské Pleso – חניה</t>
+          <t>Štrbské Pleso – סיבוב סביב האגם</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Štrbské Pleso – סיבוב סביב האגם</t>
+          <t>קפה / דוכנים ליד האגם</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3341,27 +3341,27 @@
       </c>
       <c r="F76" s="35" t="inlineStr">
         <is>
-          <t>🚶 5–10 דק׳</t>
+          <t>🚶 2–5 דק׳</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
         <is>
-          <t>1:15–1:45 ש׳</t>
+          <t>45–60 דק׳</t>
         </is>
       </c>
       <c r="H76" s="35" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>לפי הזמנה</t>
         </is>
       </c>
       <c r="I76" s="34" t="inlineStr">
         <is>
-          <t>הליכה קלה סביב האגם האלפיני, תצפיות לפסגות, צילום וקפה.</t>
+          <t>קפה, מאפה והפסקה מול הנוף.</t>
         </is>
       </c>
       <c r="J76" s="34" t="inlineStr">
         <is>
-          <t>מסלול נוח וגמיש; אפשר לקצר בכל שלב.</t>
+          <t>ללא התחייבות לאטרקציה נוספת.</t>
         </is>
       </c>
     </row>
@@ -3373,47 +3373,47 @@
       </c>
       <c r="B77" s="35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C77" s="34" t="inlineStr">
         <is>
-          <t>Štrbské Pleso – סיבוב סביב האגם</t>
+          <t>קפה / דוכנים ליד האגם</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>קפה / דוכנים ליד האגם</t>
+          <t>Solisko – אופציונלי רק אם הראות טובה</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Štrbské Pleso</t>
+          <t>Solisko Express Štrbské Pleso</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>🚶 2–5 דק׳</t>
+          <t>🚶 10–15 דק׳</t>
         </is>
       </c>
       <c r="G77" s="35" t="inlineStr">
         <is>
-          <t>45–60 דק׳</t>
+          <t>1:30–2:00 ש׳</t>
         </is>
       </c>
       <c r="H77" s="35" t="inlineStr">
         <is>
-          <t>לפי הזמנה</t>
+          <t>מחיר Gopass דינמי – לבדוק ביום הקנייה</t>
         </is>
       </c>
       <c r="I77" s="34" t="inlineStr">
         <is>
-          <t>קפה, מאפה והפסקה מול הנוף.</t>
+          <t>רכבל כיסאות לתצפיות גבוהות מעל Štrbské Pleso, רק אם העננות נפתחת.</t>
         </is>
       </c>
       <c r="J77" s="34" t="inlineStr">
         <is>
-          <t>ללא התחייבות לאטרקציה נוספת.</t>
+          <t>לא חובה; מחיר הכרטיס דינמי ב־Gopass ולכן מחליטים במקום/יום קודם.</t>
         </is>
       </c>
     </row>
@@ -3425,143 +3425,139 @@
       </c>
       <c r="B78" s="35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C78" s="34" t="inlineStr">
         <is>
-          <t>קפה / דוכנים ליד האגם</t>
+          <t>Solisko – אופציונלי רק אם הראות טובה</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Solisko – אופציונלי רק אם הראות טובה</t>
+          <t>Hotel International</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Solisko Express Štrbské Pleso</t>
+          <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
       <c r="F78" s="35" t="inlineStr">
         <is>
-          <t>🚶 10–15 דק׳</t>
+          <t>🚗 35–45 דק׳</t>
         </is>
       </c>
       <c r="G78" s="35" t="inlineStr">
         <is>
-          <t>1:30–2:00 ש׳</t>
+          <t>אחה״צ/ערב</t>
         </is>
       </c>
       <c r="H78" s="35" t="inlineStr">
         <is>
-          <t>מחיר Gopass דינמי – לבדוק ביום הקנייה</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="34" t="inlineStr">
         <is>
-          <t>רכבל כיסאות לתצפיות גבוהות מעל Štrbské Pleso, רק אם העננות נפתחת.</t>
+          <t>חזרה מוקדמת יחסית לספא, מנוחה וארוחת ערב.</t>
         </is>
       </c>
       <c r="J78" s="34" t="inlineStr">
         <is>
-          <t>לא חובה; מחיר הכרטיס דינמי ב־Gopass ולכן מחליטים במקום/יום קודם.</t>
+          <t>חלופה רגועה בכוונה.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1" s="6">
-      <c r="A79" s="34" t="inlineStr">
+      <c r="A79" s="36" t="inlineStr">
+        <is>
+          <t>Google Maps לחלופה</t>
+        </is>
+      </c>
+      <c r="B79" s="37" t="n"/>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
+        </is>
+      </c>
+      <c r="D79" s="37" t="n"/>
+      <c r="E79" s="37" t="n"/>
+      <c r="F79" s="37" t="n"/>
+      <c r="G79" s="37" t="n"/>
+      <c r="H79" s="37" t="n"/>
+      <c r="I79" s="37" t="n"/>
+      <c r="J79" s="37" t="n"/>
+    </row>
+    <row r="80" ht="28" customHeight="1" s="6">
+      <c r="A80" s="39" t="inlineStr">
+        <is>
+          <t>עלות החלופה ל-4: האגם וההליכה חינם; חניה כ־€12 לרכב לפי דיווח מטיילים. רכבל Solisko רק אם מחליטים במקום – מחיר Gopass דינמי.</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="n"/>
+      <c r="C80" s="18" t="n"/>
+      <c r="D80" s="18" t="n"/>
+      <c r="E80" s="18" t="n"/>
+      <c r="F80" s="18" t="n"/>
+      <c r="G80" s="18" t="n"/>
+      <c r="H80" s="18" t="n"/>
+      <c r="I80" s="18" t="n"/>
+      <c r="J80" s="19" t="n"/>
+    </row>
+    <row r="81" ht="6" customHeight="1" s="6"/>
+    <row r="82" ht="32" customHeight="1" s="6">
+      <c r="A82" s="32" t="inlineStr">
+        <is>
+          <t>חלופה | 25.9 חלופת גשם | חלופת גשם/עננות כבדה: Levoča, Spiš Castle ו־Kežmarok</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="58" customHeight="1" s="6">
+      <c r="A83" s="34" t="inlineStr">
         <is>
           <t>25.9.2026 – חלופה</t>
         </is>
       </c>
-      <c r="B79" s="35" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C79" s="34" t="inlineStr">
-        <is>
-          <t>Solisko – אופציונלי רק אם הראות טובה</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Hotel International</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Hotel International, Veľká Lomnica</t>
-        </is>
-      </c>
-      <c r="F79" s="35" t="inlineStr">
-        <is>
-          <t>🚗 35–45 דק׳</t>
-        </is>
-      </c>
-      <c r="G79" s="35" t="inlineStr">
-        <is>
-          <t>אחה״צ/ערב</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="34" t="inlineStr">
-        <is>
-          <t>חזרה מוקדמת יחסית לספא, מנוחה וארוחת ערב.</t>
-        </is>
-      </c>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>חלופה רגועה בכוונה.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="28" customHeight="1" s="6">
-      <c r="A80" s="36" t="inlineStr">
-        <is>
-          <t>Google Maps לחלופה</t>
-        </is>
-      </c>
-      <c r="B80" s="37" t="n"/>
-      <c r="C80" s="15" t="inlineStr">
-        <is>
-          <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
-        </is>
-      </c>
-      <c r="D80" s="37" t="n"/>
-      <c r="E80" s="37" t="n"/>
-      <c r="F80" s="37" t="n"/>
-      <c r="G80" s="37" t="n"/>
-      <c r="H80" s="37" t="n"/>
-      <c r="I80" s="37" t="n"/>
-      <c r="J80" s="37" t="n"/>
-    </row>
-    <row r="81" ht="6" customHeight="1" s="6">
-      <c r="A81" s="39" t="inlineStr">
-        <is>
-          <t>עלות החלופה ל-4: האגם וההליכה חינם; חניה כ־€12 לרכב לפי דיווח מטיילים. רכבל Solisko רק אם מחליטים במקום – מחיר Gopass דינמי.</t>
-        </is>
-      </c>
-      <c r="B81" s="18" t="n"/>
-      <c r="C81" s="18" t="n"/>
-      <c r="D81" s="18" t="n"/>
-      <c r="E81" s="18" t="n"/>
-      <c r="F81" s="18" t="n"/>
-      <c r="G81" s="18" t="n"/>
-      <c r="H81" s="18" t="n"/>
-      <c r="I81" s="18" t="n"/>
-      <c r="J81" s="19" t="n"/>
-    </row>
-    <row r="82" ht="32" customHeight="1" s="6"/>
-    <row r="83" ht="58" customHeight="1" s="6">
-      <c r="A83" s="32" t="inlineStr">
-        <is>
-          <t>חלופה | 25.9 חלופת גשם | חלופת גשם/עננות כבדה: Levoča, Spiš Castle ו־Kežmarok</t>
+      <c r="B83" s="35" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C83" s="34" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Levoča – העיר העתיקה</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Košická brána, Levoča</t>
+        </is>
+      </c>
+      <c r="F83" s="35" t="inlineStr">
+        <is>
+          <t>30–35 דק׳</t>
+        </is>
+      </c>
+      <c r="G83" s="35" t="inlineStr">
+        <is>
+          <t>1:30 ש׳</t>
+        </is>
+      </c>
+      <c r="H83" s="35" t="inlineStr">
+        <is>
+          <t>העיר העתיקה חינם</t>
+        </is>
+      </c>
+      <c r="I83" s="34" t="inlineStr">
+        <is>
+          <t>כיכר Majstra Pavla, חומות, רחובות עתיקים וקפה.</t>
+        </is>
+      </c>
+      <c r="J83" s="34" t="inlineStr">
+        <is>
+          <t>עדיפות לחניוני P+R החינמיים ליד Košická brána.</t>
         </is>
       </c>
     </row>
@@ -3573,43 +3569,47 @@
       </c>
       <c r="B84" s="35" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C84" s="34" t="inlineStr"/>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C84" s="34" t="inlineStr">
+        <is>
+          <t>Levoča – העיר העתיקה</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Levoča – העיר העתיקה</t>
+          <t>Spiš Castle</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Košická brána, Levoča</t>
+          <t>Spišský hrad</t>
         </is>
       </c>
       <c r="F84" s="35" t="inlineStr">
         <is>
-          <t>30–35 דק׳</t>
+          <t>20–25 דק׳</t>
         </is>
       </c>
       <c r="G84" s="35" t="inlineStr">
         <is>
-          <t>1:30 ש׳</t>
+          <t>1:30–2:00 ש׳</t>
         </is>
       </c>
       <c r="H84" s="35" t="inlineStr">
         <is>
-          <t>העיר העתיקה חינם</t>
+          <t>€32 ל־4 (8€ למבוגר)</t>
         </is>
       </c>
       <c r="I84" s="34" t="inlineStr">
         <is>
-          <t>כיכר Majstra Pavla, חומות, רחובות עתיקים וקפה.</t>
+          <t>אחד ממתחמי הטירות הגדולים במרכז אירופה.</t>
         </is>
       </c>
       <c r="J84" s="34" t="inlineStr">
         <is>
-          <t>עדיפות לחניוני P+R החינמיים ליד Košická brána.</t>
+          <t>בגשם חזק לא אידיאלי; לבדוק שעות פתיחה יום לפני.</t>
         </is>
       </c>
     </row>
@@ -3621,47 +3621,47 @@
       </c>
       <c r="B85" s="35" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C85" s="34" t="inlineStr">
         <is>
-          <t>Levoča – העיר העתיקה</t>
+          <t>Spiš Castle</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Spiš Castle</t>
+          <t>Kežmarok</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Spišský hrad</t>
+          <t>Hradné námestie, Kežmarok</t>
         </is>
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>20–25 דק׳</t>
+          <t>35–45 דק׳</t>
         </is>
       </c>
       <c r="G85" s="35" t="inlineStr">
         <is>
-          <t>1:30–2:00 ש׳</t>
+          <t>1:30 ש׳</t>
         </is>
       </c>
       <c r="H85" s="35" t="inlineStr">
         <is>
-          <t>€32 ל־4 (8€ למבוגר)</t>
+          <t>המרכז חינם; כניסה לטירה רק אם בוחרים</t>
         </is>
       </c>
       <c r="I85" s="34" t="inlineStr">
         <is>
-          <t>אחד ממתחמי הטירות הגדולים במרכז אירופה.</t>
+          <t>טירה, מרכז עתיק, קפה וארוחת צהריים.</t>
         </is>
       </c>
       <c r="J85" s="34" t="inlineStr">
         <is>
-          <t>בגשם חזק לא אידיאלי; לבדוק שעות פתיחה יום לפני.</t>
+          <t>חניה מרכזית בתשלום ב־Hradné námestie.</t>
         </is>
       </c>
     </row>
@@ -3673,143 +3673,139 @@
       </c>
       <c r="B86" s="35" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C86" s="34" t="inlineStr">
         <is>
-          <t>Spiš Castle</t>
+          <t>Kežmarok</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Kežmarok</t>
+          <t>Hotel International</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hradné námestie, Kežmarok</t>
+          <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
       <c r="F86" s="35" t="inlineStr">
         <is>
-          <t>35–45 דק׳</t>
+          <t>10–15 דק׳</t>
         </is>
       </c>
       <c r="G86" s="35" t="inlineStr">
         <is>
-          <t>1:30 ש׳</t>
+          <t>אחה״צ/ערב</t>
         </is>
       </c>
       <c r="H86" s="35" t="inlineStr">
         <is>
-          <t>המרכז חינם; כניסה לטירה רק אם בוחרים</t>
+          <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
       <c r="I86" s="34" t="inlineStr">
         <is>
-          <t>טירה, מרכז עתיק, קפה וארוחת צהריים.</t>
+          <t>ספא, בריכה וארוחת ערב.</t>
         </is>
       </c>
       <c r="J86" s="34" t="inlineStr">
         <is>
-          <t>חניה מרכזית בתשלום ב־Hradné námestie.</t>
+          <t>יום רגוע יותר אם מזג האוויר גרוע.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1" s="6">
-      <c r="A87" s="34" t="inlineStr">
-        <is>
-          <t>25.9.2026 – חלופה</t>
-        </is>
-      </c>
-      <c r="B87" s="35" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="C87" s="34" t="inlineStr">
-        <is>
-          <t>Kežmarok</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Hotel International</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
+      <c r="A87" s="36" t="inlineStr">
+        <is>
+          <t>Google Maps לחלופה</t>
+        </is>
+      </c>
+      <c r="B87" s="37" t="n"/>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
+        </is>
+      </c>
+      <c r="D87" s="37" t="n"/>
+      <c r="E87" s="37" t="n"/>
+      <c r="F87" s="37" t="n"/>
+      <c r="G87" s="37" t="n"/>
+      <c r="H87" s="37" t="n"/>
+      <c r="I87" s="37" t="n"/>
+      <c r="J87" s="37" t="n"/>
+    </row>
+    <row r="88" ht="28" customHeight="1" s="6">
+      <c r="A88" s="39" t="inlineStr">
+        <is>
+          <t>עלות החלופה ל-4: Spiš Castle: €32 ל־4; Levoča/Kežmarok מרכזים חינם.</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="n"/>
+      <c r="C88" s="18" t="n"/>
+      <c r="D88" s="18" t="n"/>
+      <c r="E88" s="18" t="n"/>
+      <c r="F88" s="18" t="n"/>
+      <c r="G88" s="18" t="n"/>
+      <c r="H88" s="18" t="n"/>
+      <c r="I88" s="18" t="n"/>
+      <c r="J88" s="19" t="n"/>
+    </row>
+    <row r="89" ht="8" customHeight="1" s="6"/>
+    <row r="90" ht="28" customHeight="1" s="6">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>שבת | 26.9.2026 | הטטרה הנמוכים: Jasná, Vrbické pleso, Slide Park Priehyba, Chopok, מערת החירות, Liptovská Mara ו־Hrabovo כאפשרות</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="58" customHeight="1" s="6">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>26.9.2026 – שבת</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Hotel International – יציאה</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
         <is>
           <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
-      <c r="F87" s="35" t="inlineStr">
-        <is>
-          <t>10–15 דק׳</t>
-        </is>
-      </c>
-      <c r="G87" s="35" t="inlineStr">
-        <is>
-          <t>אחה״צ/ערב</t>
-        </is>
-      </c>
-      <c r="H87" s="35" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>יציאה</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
         <is>
           <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
-      <c r="I87" s="34" t="inlineStr">
-        <is>
-          <t>ספא, בריכה וארוחת ערב.</t>
-        </is>
-      </c>
-      <c r="J87" s="34" t="inlineStr">
-        <is>
-          <t>יום רגוע יותר אם מזג האוויר גרוע.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="28" customHeight="1" s="6">
-      <c r="A88" s="36" t="inlineStr">
-        <is>
-          <t>Google Maps לחלופה</t>
-        </is>
-      </c>
-      <c r="B88" s="37" t="n"/>
-      <c r="C88" s="15" t="inlineStr">
-        <is>
-          <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
-        </is>
-      </c>
-      <c r="D88" s="37" t="n"/>
-      <c r="E88" s="37" t="n"/>
-      <c r="F88" s="37" t="n"/>
-      <c r="G88" s="37" t="n"/>
-      <c r="H88" s="37" t="n"/>
-      <c r="I88" s="37" t="n"/>
-      <c r="J88" s="37" t="n"/>
-    </row>
-    <row r="89" ht="8" customHeight="1" s="6">
-      <c r="A89" s="39" t="inlineStr">
-        <is>
-          <t>עלות החלופה ל-4: Spiš Castle: €32 ל־4; Levoča/Kežmarok מרכזים חינם.</t>
-        </is>
-      </c>
-      <c r="B89" s="18" t="n"/>
-      <c r="C89" s="18" t="n"/>
-      <c r="D89" s="18" t="n"/>
-      <c r="E89" s="18" t="n"/>
-      <c r="F89" s="18" t="n"/>
-      <c r="G89" s="18" t="n"/>
-      <c r="H89" s="18" t="n"/>
-      <c r="I89" s="18" t="n"/>
-      <c r="J89" s="19" t="n"/>
-    </row>
-    <row r="90" ht="28" customHeight="1" s="6"/>
-    <row r="91" ht="58" customHeight="1" s="6">
-      <c r="A91" s="10" t="inlineStr">
-        <is>
-          <t>שבת | 26.9.2026 | הטטרה הנמוכים: Jasná, Vrbické pleso, Slide Park Priehyba, Chopok, מערת החירות, Liptovská Mara ו־Hrabovo כאפשרות</t>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>יציאה מהמלון לאחר ארוחת הבוקר לכיוון הטטרה הנמוכים.</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>לבדוק בבוקר רוח, ראות ופעילות רכבלים ב־Jasná.</t>
         </is>
       </c>
     </row>
@@ -3821,43 +3817,47 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr"/>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Hotel International – יציאה</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Hotel International – יציאה</t>
+          <t>Jasná – Biela Púť</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hotel International, Veľká Lomnica</t>
+          <t>Jasná Biela Púť</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1:00–1:20 ש׳</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>יציאה</t>
+          <t>20 דק׳</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>כלול לפי חבילת המלון</t>
+          <t>חניה/רכבל לפי Gopass</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>יציאה מהמלון לאחר ארוחת הבוקר לכיוון הטטרה הנמוכים.</t>
+          <t>הגעה למרכז הרכבלים, חניה והתארגנות.</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>לבדוק בבוקר רוח, ראות ופעילות רכבלים ב־Jasná.</t>
+          <t>לצאת מוקדם ולבדוק בבוקר רוח, ראות ופעילות רכבלים.</t>
         </is>
       </c>
     </row>
@@ -3869,47 +3869,47 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Hotel International – יציאה</t>
+          <t>Jasná – Biela Púť</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Jasná – Biela Púť</t>
+          <t>Vrbické pleso</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jasná Biela Púť</t>
+          <t>Vrbické pleso, Jasná</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>1:00–1:20 ש׳</t>
+          <t>5–10 דק׳ / הליכה</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>20 דק׳</t>
+          <t>30–40 דק׳</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>חניה/רכבל לפי Gopass</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>הגעה למרכז הרכבלים, חניה והתארגנות.</t>
+          <t>סיבוב קצר סביב אגם הררי בתוך היער, תצפיות וצילומים.</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>לצאת מוקדם ולבדוק בבוקר רוח, ראות ופעילות רכבלים.</t>
+          <t>האגם ממש ליד Jasná ולכן זו תוספת יפה בלי נסיעה מיותרת.</t>
         </is>
       </c>
     </row>
@@ -3921,47 +3921,47 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Jasná – Biela Púť</t>
+          <t>Vrbické pleso</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Vrbické pleso</t>
+          <t>Slide Park Jasná – Priehyba</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vrbické pleso, Jasná</t>
+          <t>Priehyba, Jasná</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>5–10 דק׳ / הליכה</t>
+          <t>רכבל A6</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>30–40 דק׳</t>
+          <t>30–45 דק׳</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>חינם; נדרש להגיע עם הרכבל</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>אגם הררי ליד Jasná, למטה ליד החניה. הולכים 10–15 דק׳, מקיפים כ־20 דק׳ וחוזרים. אין צורך ברכבל.</t>
+          <t>פארק המגלשות החדש ב־Priehyba עם 7 מגלשות יבשות; עצירה בדרך ל־Chopok.</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>GPS: 48.970831, 19.576958. עושים ברגל מאזור Biela Púť/Grand Jasná וחוזרים לרכבלים בלי להזיז את הרכב.</t>
+          <t>הכניסה לפארק חינם; הרכבל לפי הכרטיס. לבדוק סמוך לנסיעה שהפעילות פתוחה.</t>
         </is>
       </c>
     </row>
@@ -3973,47 +3973,47 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="C95" s="15" t="inlineStr">
-        <is>
-          <t>Vrbické pleso</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Slide Park Jasná – Priehyba</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Slide Park Jasná – Priehyba</t>
+          <t>Chopok</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>48.970831,19.576958</t>
+          <t>Chopok</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>🚶 10–15 דק׳</t>
+          <t>רכבלים</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>35–45 דק׳</t>
+          <t>2:00–2:30 ש׳</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>חינם; נדרש להגיע עם הרכבל</t>
+          <t>מחיר Gopass דינמי – לבדוק 1–3 ימים לפני</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>פארק המגלשות החדש ב־Priehyba עם 7 מגלשות יבשות; עצירה בדרך ל־Chopok.</t>
+          <t>המשך ברכבל לפסגה בגובה כ־2,024 מ׳, תצפית פנורמית וקפה בפסגה.</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>הכניסה לפארק חינם; הרכבל לפי הכרטיס. לבדוק סמוך לנסיעה שהפעילות פתוחה.</t>
+          <t>להצטייד במעיל; לשים לב לזמן כדי להספיק למערה.</t>
         </is>
       </c>
     </row>
@@ -4025,47 +4025,47 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Slide Park Jasná – Priehyba</t>
+          <t>Chopok</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Chopok</t>
+          <t>Demänovská Cave of Liberty</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chopok</t>
+          <t>Demänovská jaskyňa slobody</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>רכבלים</t>
+          <t>15–20 דק׳</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2:00–2:30 ש׳</t>
+          <t>1:30–2:00 ש׳</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>מחיר Gopass דינמי – לבדוק 1–3 ימים לפני</t>
+          <t>€60 ל־4 – סיור מסורתי (15€ לאדם)</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>המשך ברכבל לפסגה בגובה כ־2,024 מ׳, תצפית פנורמית וקפה בפסגה.</t>
+          <t>מערת נטיפים גדולה עם אולמות, נהר תת־קרקעי וסיור מודרך.</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>להצטייד במעיל; לשים לב לזמן כדי להספיק למערה.</t>
+          <t>להגיע לפני שעת הסיור; יש מדרגות והטמפרטורה נמוכה.</t>
         </is>
       </c>
     </row>
@@ -4077,47 +4077,47 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Chopok</t>
+          <t>Demänovská Cave of Liberty</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Demänovská Cave of Liberty</t>
+          <t>Liptovská Mara</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Demänovská jaskyňa slobody</t>
+          <t>Liptovská Mara – Liptovský Trnovec</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>15–20 דק׳</t>
+          <t>25–35 דק׳</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>1:45–2:00 ש׳</t>
+          <t>45–60 דק׳</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>€59 ל־4: 3×€15 + Senior 60+ אחד €14</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>מערת נטיפים מרשימה עם נטיפים, זקיפים, אולמות גדולים ונהר תת־קרקעי. סיור מסורתי מודרך.</t>
+          <t>אגם גדול, מרינה, תצפיות וקפה לקראת אחר הצהריים.</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>לא להתעכב: צריך להגיע לפני סיור 14:00 במערת החירות.</t>
+          <t>כאן מחליטים לפי השעה אם ממשיכים ל־Hrabovo.</t>
         </is>
       </c>
     </row>
@@ -4129,143 +4129,147 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Demänovská Cave of Liberty</t>
+          <t>Liptovská Mara</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Liptovská Mara</t>
+          <t>Hrabovo / Malinô Brdo – אופציונלי</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Liptovská Mara – Liptovský Trnovec</t>
+          <t>Hrabovo, Ružomberok</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>🚗 15–20 דק׳ אחרי הירידה מהרכבל</t>
+          <t>35–45 דק׳</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>כ־60 דק׳ + כניסה/יציאה</t>
+          <t>1:00–1:30 ש׳</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>האגם חינם; רכבל/קארטינג/Tarzania בתשלום לפי בחירה</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>אגם גדול, מרינה, תצפיות וקפה לקראת אחר הצהריים.</t>
+          <t>אגם נופש יפה; אם הזמן והפעילות מאפשרים: רכבל ל־Malinô Brdo, Mountain Carts או Tarzania.</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>בספטמבר סיורים: 09:30, 11:00, 12:30, 14:00. ניסים בן 64 זכאי ל־Senior 60+.</t>
+          <t>אופציונלי בלבד. בסוף ספטמבר לבדוק שעות פעילות מראש; אם אין זמן או שהמתקנים סגורים חוזרים למלון.</t>
         </is>
       </c>
     </row>
     <row r="99" ht="58" customHeight="1" s="6">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>Google Maps ליום</t>
-        </is>
-      </c>
-      <c r="C99" s="15" t="inlineStr">
-        <is>
-          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>26.9.2026 – שבת</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Hrabovo / Malinô Brdo – אופציונלי</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Hotel International</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Hotel International, Veľká Lomnica</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>1:00–1:25 ש׳</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>ערב</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>כלול לפי חבילת המלון</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>חזרה למלון, ספא וארוחת ערב.</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>אם מוותרים על Hrabovo חוזרים מוקדם יותר מ־Liptovská Mara.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1" s="6">
       <c r="A100" s="4" t="inlineStr">
         <is>
+          <t>Google Maps ליום</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1" s="6">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
           <t>לינה בסוף היום</t>
         </is>
       </c>
-      <c r="C100" s="15" t="inlineStr">
+      <c r="C101" s="15" t="inlineStr">
         <is>
           <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="20" customHeight="1" s="6">
-      <c r="A101" s="16" t="inlineStr">
-        <is>
-          <t>עלות משוערת ליום ל-4: מערת החירות €59 ל־4 + Chopok במחיר Gopass דינמי; Vrbické/Slide Park חינם.</t>
-        </is>
-      </c>
-      <c r="B101" s="18" t="n"/>
-      <c r="C101" s="18" t="n"/>
-      <c r="D101" s="18" t="n"/>
-      <c r="E101" s="18" t="n"/>
-      <c r="F101" s="18" t="n"/>
-      <c r="G101" s="18" t="n"/>
-      <c r="H101" s="18" t="n"/>
-      <c r="I101" s="18" t="n"/>
-      <c r="J101" s="19" t="n"/>
-    </row>
-    <row r="102" ht="28" customHeight="1" s="6"/>
-    <row r="103" ht="6" customHeight="1" s="6">
-      <c r="A103" s="32" t="inlineStr">
+    <row r="102" ht="28" customHeight="1" s="6">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>עלות משוערת ליום ל-4: מערת החירות €60 ל־4 + Chopok במחיר Gopass דינמי; Vrbické/Slide Park/Mara חינם. Hrabovo אופציונלי.</t>
+        </is>
+      </c>
+      <c r="B102" s="18" t="n"/>
+      <c r="C102" s="18" t="n"/>
+      <c r="D102" s="18" t="n"/>
+      <c r="E102" s="18" t="n"/>
+      <c r="F102" s="18" t="n"/>
+      <c r="G102" s="18" t="n"/>
+      <c r="H102" s="18" t="n"/>
+      <c r="I102" s="18" t="n"/>
+      <c r="J102" s="19" t="n"/>
+    </row>
+    <row r="103" ht="6" customHeight="1" s="6"/>
+    <row r="104" ht="32" customHeight="1" s="6">
+      <c r="A104" s="32" t="inlineStr">
         <is>
           <t>חלופה | 26.9 חלופת גשם | חלופת גשם לטטרה הנמוכים: מערת החירות, Liptovský Mikuláš, Liptovská Mara ו־Hrabovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="32" customHeight="1" s="6">
-      <c r="A104" s="34" t="inlineStr">
-        <is>
-          <t>26.9.2026 – חלופה</t>
-        </is>
-      </c>
-      <c r="B104" s="35" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="C104" s="34" t="inlineStr"/>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Hotel International – יציאה</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Hotel International, Veľká Lomnica</t>
-        </is>
-      </c>
-      <c r="F104" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G104" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H104" s="35" t="inlineStr">
-        <is>
-          <t>כלול לפי חבילת המלון</t>
-        </is>
-      </c>
-      <c r="I104" s="34" t="inlineStr">
-        <is>
-          <t>יוצאים ישר למערה.</t>
-        </is>
-      </c>
-      <c r="J104" s="34" t="inlineStr">
-        <is>
-          <t>להתאים את היציאה לשעת הסיור.</t>
         </is>
       </c>
     </row>
@@ -4277,47 +4281,43 @@
       </c>
       <c r="B105" s="35" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="C105" s="34" t="inlineStr">
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C105" s="34" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
         <is>
           <t>Hotel International – יציאה</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Demänovská Cave of Liberty</t>
-        </is>
-      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Demänovská jaskyňa slobody</t>
+          <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>1:10–1:25 ש׳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G105" s="35" t="inlineStr">
         <is>
-          <t>1:30–2:00 ש׳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H105" s="35" t="inlineStr">
         <is>
-          <t>€59 ל־4: 3×€15 + Senior 60+ אחד €14</t>
+          <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
       <c r="I105" s="34" t="inlineStr">
         <is>
-          <t>סיור במערת נטיפים ונהר תת־קרקעי.</t>
+          <t>יוצאים ישר למערה.</t>
         </is>
       </c>
       <c r="J105" s="34" t="inlineStr">
         <is>
-          <t>בספטמבר קיימות כניסות בשעות קבועות; להגיע מוקדם.</t>
+          <t>להתאים את היציאה לשעת הסיור.</t>
         </is>
       </c>
     </row>
@@ -4329,47 +4329,47 @@
       </c>
       <c r="B106" s="35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C106" s="34" t="inlineStr">
         <is>
+          <t>Hotel International – יציאה</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
           <t>Demänovská Cave of Liberty</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Liptovský Mikuláš</t>
-        </is>
-      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Liptovský Mikuláš centrum</t>
+          <t>Demänovská jaskyňa slobody</t>
         </is>
       </c>
       <c r="F106" s="35" t="inlineStr">
         <is>
-          <t>15–20 דק׳</t>
+          <t>1:10–1:25 ש׳</t>
         </is>
       </c>
       <c r="G106" s="35" t="inlineStr">
         <is>
-          <t>1:15 ש׳</t>
+          <t>1:30–2:00 ש׳</t>
         </is>
       </c>
       <c r="H106" s="35" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>€60 ל־4 – סיור מסורתי (15€ לאדם)</t>
         </is>
       </c>
       <c r="I106" s="34" t="inlineStr">
         <is>
-          <t>מרכז העיר, ארוחת צהריים וקפה.</t>
+          <t>סיור במערת נטיפים ונהר תת־קרקעי.</t>
         </is>
       </c>
       <c r="J106" s="34" t="inlineStr">
         <is>
-          <t>חניה לפי שילוט מקומי.</t>
+          <t>בספטמבר קיימות כניסות בשעות קבועות; להגיע מוקדם.</t>
         </is>
       </c>
     </row>
@@ -4381,22 +4381,22 @@
       </c>
       <c r="B107" s="35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C107" s="34" t="inlineStr">
         <is>
+          <t>Demänovská Cave of Liberty</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
           <t>Liptovský Mikuláš</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Liptovská Mara</t>
-        </is>
-      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Liptovská Mara – Liptovský Trnovec</t>
+          <t>Liptovský Mikuláš centrum</t>
         </is>
       </c>
       <c r="F107" s="35" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G107" s="35" t="inlineStr">
         <is>
-          <t>30–45 דק׳</t>
+          <t>1:15 ש׳</t>
         </is>
       </c>
       <c r="H107" s="35" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="I107" s="34" t="inlineStr">
         <is>
-          <t>תצפית/מרינה אם הגשם נחלש.</t>
+          <t>מרכז העיר, ארוחת צהריים וקפה.</t>
         </is>
       </c>
       <c r="J107" s="34" t="inlineStr">
         <is>
-          <t>אם מזג האוויר לא משתפר – מדלגים.</t>
+          <t>חניה לפי שילוט מקומי.</t>
         </is>
       </c>
     </row>
@@ -4433,47 +4433,47 @@
       </c>
       <c r="B108" s="35" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C108" s="34" t="inlineStr">
         <is>
+          <t>Liptovský Mikuláš</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
           <t>Liptovská Mara</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Hrabovo – אופציונלי</t>
-        </is>
-      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hrabovo, Ružomberok</t>
+          <t>Liptovská Mara – Liptovský Trnovec</t>
         </is>
       </c>
       <c r="F108" s="35" t="inlineStr">
         <is>
-          <t>35–45 דק׳</t>
+          <t>15–20 דק׳</t>
         </is>
       </c>
       <c r="G108" s="35" t="inlineStr">
         <is>
-          <t>1:00 ש׳</t>
+          <t>30–45 דק׳</t>
         </is>
       </c>
       <c r="H108" s="35" t="inlineStr">
         <is>
-          <t>האגם חינם; רכבל/קארטינג/Tarzania בתשלום לפי בחירה</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I108" s="34" t="inlineStr">
         <is>
-          <t>אגם ובית קפה; פעילויות רק אם מזג האוויר מאפשר.</t>
+          <t>תצפית/מרינה אם הגשם נחלש.</t>
         </is>
       </c>
       <c r="J108" s="34" t="inlineStr">
         <is>
-          <t>לא לבנות על רכבל/קארטינג בגשם.</t>
+          <t>אם מזג האוויר לא משתפר – מדלגים.</t>
         </is>
       </c>
     </row>
@@ -4485,139 +4485,143 @@
       </c>
       <c r="B109" s="35" t="inlineStr">
         <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="C109" s="34" t="inlineStr">
+        <is>
+          <t>Liptovská Mara</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Hrabovo – אופציונלי</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Hrabovo, Ružomberok</t>
+        </is>
+      </c>
+      <c r="F109" s="35" t="inlineStr">
+        <is>
+          <t>35–45 דק׳</t>
+        </is>
+      </c>
+      <c r="G109" s="35" t="inlineStr">
+        <is>
+          <t>1:00 ש׳</t>
+        </is>
+      </c>
+      <c r="H109" s="35" t="inlineStr">
+        <is>
+          <t>האגם חינם; רכבל/קארטינג/Tarzania בתשלום לפי בחירה</t>
+        </is>
+      </c>
+      <c r="I109" s="34" t="inlineStr">
+        <is>
+          <t>אגם ובית קפה; פעילויות רק אם מזג האוויר מאפשר.</t>
+        </is>
+      </c>
+      <c r="J109" s="34" t="inlineStr">
+        <is>
+          <t>לא לבנות על רכבל/קארטינג בגשם.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="58" customHeight="1" s="6">
+      <c r="A110" s="34" t="inlineStr">
+        <is>
+          <t>26.9.2026 – חלופה</t>
+        </is>
+      </c>
+      <c r="B110" s="35" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C109" s="34" t="inlineStr">
+      <c r="C110" s="34" t="inlineStr">
         <is>
           <t>Hrabovo – אופציונלי</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>Hotel International</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
-      <c r="F109" s="35" t="inlineStr">
+      <c r="F110" s="35" t="inlineStr">
         <is>
           <t>1:00–1:25 ש׳</t>
         </is>
       </c>
-      <c r="G109" s="35" t="inlineStr">
+      <c r="G110" s="35" t="inlineStr">
         <is>
           <t>ערב</t>
         </is>
       </c>
-      <c r="H109" s="35" t="inlineStr">
+      <c r="H110" s="35" t="inlineStr">
         <is>
           <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
-      <c r="I109" s="34" t="inlineStr">
+      <c r="I110" s="34" t="inlineStr">
         <is>
           <t>חזרה לספא וארוחת ערב.</t>
         </is>
       </c>
-      <c r="J109" s="34" t="inlineStr">
+      <c r="J110" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="58" customHeight="1" s="6">
-      <c r="A110" s="36" t="inlineStr">
+    <row r="111" ht="20" customHeight="1" s="6">
+      <c r="A111" s="36" t="inlineStr">
         <is>
           <t>Google Maps לחלופה</t>
         </is>
       </c>
-      <c r="B110" s="37" t="n"/>
-      <c r="C110" s="15" t="inlineStr">
+      <c r="B111" s="37" t="n"/>
+      <c r="C111" s="15" t="inlineStr">
         <is>
           <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
         </is>
       </c>
-      <c r="D110" s="37" t="n"/>
-      <c r="E110" s="37" t="n"/>
-      <c r="F110" s="37" t="n"/>
-      <c r="G110" s="37" t="n"/>
-      <c r="H110" s="37" t="n"/>
-      <c r="I110" s="37" t="n"/>
-      <c r="J110" s="37" t="n"/>
-    </row>
-    <row r="111" ht="20" customHeight="1" s="6">
-      <c r="A111" s="39" t="inlineStr">
+      <c r="D111" s="37" t="n"/>
+      <c r="E111" s="37" t="n"/>
+      <c r="F111" s="37" t="n"/>
+      <c r="G111" s="37" t="n"/>
+      <c r="H111" s="37" t="n"/>
+      <c r="I111" s="37" t="n"/>
+      <c r="J111" s="37" t="n"/>
+    </row>
+    <row r="112" ht="28" customHeight="1" s="6">
+      <c r="A112" s="39" t="inlineStr">
         <is>
           <t>עלות החלופה ל-4: מערת החירות: €60 ל־4; יתר העצירות חינם, פעילויות Hrabovo אופציונליות.</t>
         </is>
       </c>
-      <c r="B111" s="18" t="n"/>
-      <c r="C111" s="18" t="n"/>
-      <c r="D111" s="18" t="n"/>
-      <c r="E111" s="18" t="n"/>
-      <c r="F111" s="18" t="n"/>
-      <c r="G111" s="18" t="n"/>
-      <c r="H111" s="18" t="n"/>
-      <c r="I111" s="18" t="n"/>
-      <c r="J111" s="19" t="n"/>
-    </row>
-    <row r="112" ht="28" customHeight="1" s="6"/>
-    <row r="113" ht="8" customHeight="1" s="6">
-      <c r="A113" s="11" t="inlineStr">
+      <c r="B112" s="18" t="n"/>
+      <c r="C112" s="18" t="n"/>
+      <c r="D112" s="18" t="n"/>
+      <c r="E112" s="18" t="n"/>
+      <c r="F112" s="18" t="n"/>
+      <c r="G112" s="18" t="n"/>
+      <c r="H112" s="18" t="n"/>
+      <c r="I112" s="18" t="n"/>
+      <c r="J112" s="19" t="n"/>
+    </row>
+    <row r="113" ht="8" customHeight="1" s="6"/>
+    <row r="114" ht="28" customHeight="1" s="6">
+      <c r="A114" s="11" t="inlineStr">
         <is>
           <t>יום א׳ | 27.9.2026 | הטטרה הנמוכים, בנסקה ביסטריצה, תצפית עיקול הדנובה ואאוטלט בדרך לבודפשט</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="28" customHeight="1" s="6">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>27.9.2026 – יום א׳</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr"/>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Liptovská Mara</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Liptovská Mara – Liptovský Trnovec</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>1:00–1:15 ש׳</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="inlineStr">
-        <is>
-          <t>20–30 דק׳</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>חינם</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>אגם גדול בטטרה הנמוכים, מרינה ותצפיות יפות.</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>עצירת בוקר קצרה לצילומים וקפה.</t>
         </is>
       </c>
     </row>
@@ -4629,27 +4633,23 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
         <is>
           <t>Liptovská Mara</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Donovaly</t>
-        </is>
-      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Donovaly, Slovakia</t>
+          <t>Liptovská Mara – Liptovský Trnovec</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>45–55 דק׳</t>
+          <t>1:00–1:15 ש׳</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -4659,17 +4659,17 @@
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>חינם לעצירת נוף</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>מעבר הרים ועיירת נופש עם תצפיות ונוף אלפיני.</t>
+          <t>אגם גדול בטטרה הנמוכים, מרינה ותצפיות יפות.</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>עצירת התרעננות בלבד.</t>
+          <t>עצירת בוקר קצרה לצילומים וקפה.</t>
         </is>
       </c>
     </row>
@@ -4681,47 +4681,47 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
+          <t>Liptovská Mara</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
           <t>Donovaly</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Bobová dráha FunAréna Donovaly – אופציונלי</t>
-        </is>
-      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FunAréna Donovaly</t>
+          <t>Donovaly, Slovakia</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>🚗 3–5 דק׳</t>
+          <t>45–55 דק׳</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>35–50 דק׳</t>
+          <t>20–30 דק׳</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>€24 / €46 / €64 ל־4 (1 / 2 / 3 סיבובים)</t>
+          <t>חינם לעצירת נוף</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>מגלשת הרים מהירה וקצרה – עצירה כיפית בדרך בלי להפוך אותה ליום אטרקציות.</t>
+          <t>מעבר הרים ועיירת נופש עם תצפיות ונוף אלפיני.</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>מחיר רשמי 2026: €6 לסיבוב, €11.50 לשני סיבובים, €16 לשלושה – לאדם.</t>
+          <t>עצירת התרעננות בלבד.</t>
         </is>
       </c>
     </row>
@@ -4733,47 +4733,47 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
+          <t>Donovaly</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
           <t>Bobová dráha FunAréna Donovaly – אופציונלי</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Banská Bystrica</t>
-        </is>
-      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Námestie SNP, Banská Bystrica</t>
+          <t>FunAréna Donovaly</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>30–35 דק׳</t>
+          <t>🚗 3–5 דק׳</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>1:00–1:15 ש׳</t>
+          <t>35–50 דק׳</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>€24 / €46 / €64 ל־4 (1 / 2 / 3 סיבובים)</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>כיכר היסטורית צבעונית, מדרחוב וארוחת צהריים קלה.</t>
+          <t>מגלשת הרים מהירה וקצרה – עצירה כיפית בדרך בלי להפוך אותה ליום אטרקציות.</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>לא להיכנס למוזיאונים כדי לשמור זמן.</t>
+          <t>מחיר רשמי 2026: €6 לסיבוב, €11.50 לשני סיבובים, €16 לשלושה – לאדם.</t>
         </is>
       </c>
     </row>
@@ -4785,47 +4785,47 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
+          <t>Bobová dráha FunAréna Donovaly – אופציונלי</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
           <t>Banská Bystrica</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Visegrád – תצפית עיקול הדנובה</t>
-        </is>
-      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zsitvay-kilátó, Visegrád</t>
+          <t>Námestie SNP, Banská Bystrica</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2:30–2:50 ש׳</t>
+          <t>30–35 דק׳</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>25–35 דק׳</t>
+          <t>1:00–1:15 ש׳</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>3,400 HUF ל־4 (850 HUF לאדם)</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>תצפית פנורמית מרשימה על עיקול הדנובה והגבעות.</t>
+          <t>כיכר היסטורית צבעונית, מדרחוב וארוחת צהריים קלה.</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>עצירת הוואו של הדרך; ללא סיור ארוך.</t>
+          <t>לא להיכנס למוזיאונים כדי לשמור זמן.</t>
         </is>
       </c>
     </row>
@@ -4837,47 +4837,47 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
+          <t>Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
           <t>Visegrád – תצפית עיקול הדנובה</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Premier Outlet Budapest</t>
-        </is>
-      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Premier Outlet Budapest</t>
+          <t>Zsitvay-kilátó, Visegrád</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>1:10–1:25 ש׳</t>
+          <t>2:30–2:50 ש׳</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>1:15–1:45 ש׳</t>
+          <t>25–35 דק׳</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>כניסה חינם</t>
+          <t>3,400 HUF ל־4 (850 HUF לאדם)</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>קניות מרוכזות לפני הכניסה לבודפשט.</t>
+          <t>תצפית פנורמית מרשימה על עיקול הדנובה והגבעות.</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>לבדוק שעות פתיחה ביום א׳.</t>
+          <t>עצירת הוואו של הדרך; ללא סיור ארוך.</t>
         </is>
       </c>
     </row>
@@ -4889,143 +4889,147 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Visegrád – תצפית עיקול הדנובה</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Premier Outlet Budapest</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Premier Outlet Budapest</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>1:10–1:25 ש׳</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>1:15–1:45 ש׳</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>כניסה חינם</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>קניות מרוכזות לפני הכניסה לבודפשט.</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>לבדוק שעות פתיחה ביום א׳.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="58" customHeight="1" s="6">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>27.9.2026 – יום א׳</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>Premier Outlet Budapest</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>La Prima Hotel Budapest</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>La Prima Hotel Budapest</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>25–40 דק׳</t>
         </is>
       </c>
-      <c r="G120" s="3" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>ערב</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
+      <c r="H121" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>צ׳ק־אין, ארוחת ערב ומנוחה במרכז העיר.</t>
         </is>
       </c>
-      <c r="J120" s="2" t="inlineStr">
+      <c r="J121" s="2" t="inlineStr">
         <is>
           <t>אם מתעכבים, מקצרים קודם את Donovaly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="58" customHeight="1" s="6">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>Google Maps ליום</t>
-        </is>
-      </c>
-      <c r="C121" s="15" t="inlineStr">
-        <is>
-          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
         </is>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1" s="6">
       <c r="A122" s="4" t="inlineStr">
         <is>
+          <t>Google Maps ליום</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1" s="6">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
           <t>לינה בסוף היום</t>
         </is>
       </c>
-      <c r="C122" s="15" t="inlineStr">
+      <c r="C123" s="15" t="inlineStr">
         <is>
           <t>La Prima Hotel Budapest</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="20" customHeight="1" s="6">
-      <c r="A123" s="16" t="inlineStr">
+    <row r="124" ht="28" customHeight="1" s="6">
+      <c r="A124" s="16" t="inlineStr">
         <is>
           <t>עלות משוערת ליום ל-4: Donovaly Bob: €24 / €46 / €64 ל־4 (1/2/3 סיבובים) + Zsitvay lookout: 3,400 HUF ל־4; שאר העצירות ללא כניסה.</t>
         </is>
       </c>
-      <c r="B123" s="18" t="n"/>
-      <c r="C123" s="18" t="n"/>
-      <c r="D123" s="18" t="n"/>
-      <c r="E123" s="18" t="n"/>
-      <c r="F123" s="18" t="n"/>
-      <c r="G123" s="18" t="n"/>
-      <c r="H123" s="18" t="n"/>
-      <c r="I123" s="18" t="n"/>
-      <c r="J123" s="19" t="n"/>
-    </row>
-    <row r="124" ht="28" customHeight="1" s="6"/>
-    <row r="125" ht="6" customHeight="1" s="6">
-      <c r="A125" s="32" t="inlineStr">
+      <c r="B124" s="18" t="n"/>
+      <c r="C124" s="18" t="n"/>
+      <c r="D124" s="18" t="n"/>
+      <c r="E124" s="18" t="n"/>
+      <c r="F124" s="18" t="n"/>
+      <c r="G124" s="18" t="n"/>
+      <c r="H124" s="18" t="n"/>
+      <c r="I124" s="18" t="n"/>
+      <c r="J124" s="19" t="n"/>
+    </row>
+    <row r="125" ht="6" customHeight="1" s="6"/>
+    <row r="126" ht="32" customHeight="1" s="6">
+      <c r="A126" s="32" t="inlineStr">
         <is>
           <t>חלופה | 27.9 חלופת גשם | חלופת גשם בדרך לבודפשט: Banská Bystrica → Premier Outlet → Budapest</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="32" customHeight="1" s="6">
-      <c r="A126" s="34" t="inlineStr">
-        <is>
-          <t>27.9.2026 – חלופה</t>
-        </is>
-      </c>
-      <c r="B126" s="35" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C126" s="34" t="inlineStr"/>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Hotel International – יציאה</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Hotel International, Veľká Lomnica</t>
-        </is>
-      </c>
-      <c r="F126" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G126" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H126" s="35" t="inlineStr">
-        <is>
-          <t>כלול לפי חבילת המלון</t>
-        </is>
-      </c>
-      <c r="I126" s="34" t="inlineStr">
-        <is>
-          <t>יציאה רגועה לבודפשט.</t>
-        </is>
-      </c>
-      <c r="J126" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -5037,47 +5041,43 @@
       </c>
       <c r="B127" s="35" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="C127" s="34" t="inlineStr">
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C127" s="34" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
         <is>
           <t>Hotel International – יציאה</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Banská Bystrica</t>
-        </is>
-      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Námestie SNP, Banská Bystrica</t>
+          <t>Hotel International, Veľká Lomnica</t>
         </is>
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>1:30–1:45 ש׳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G127" s="35" t="inlineStr">
         <is>
-          <t>1:15 ש׳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H127" s="35" t="inlineStr">
         <is>
-          <t>חינם</t>
+          <t>כלול לפי חבילת המלון</t>
         </is>
       </c>
       <c r="I127" s="34" t="inlineStr">
         <is>
-          <t>כיכר מרכזית, קפה/ארוחת צהריים קצרה.</t>
+          <t>יציאה רגועה לבודפשט.</t>
         </is>
       </c>
       <c r="J127" s="34" t="inlineStr">
         <is>
-          <t>ביום א׳ החניה העירונית במרכז חינם.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5089,47 +5089,47 @@
       </c>
       <c r="B128" s="35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C128" s="34" t="inlineStr">
         <is>
+          <t>Hotel International – יציאה</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
           <t>Banská Bystrica</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Premier Outlet Budapest</t>
-        </is>
-      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Premier Outlet Budapest</t>
+          <t>Námestie SNP, Banská Bystrica</t>
         </is>
       </c>
       <c r="F128" s="35" t="inlineStr">
         <is>
-          <t>2:30–2:50 ש׳</t>
+          <t>1:30–1:45 ש׳</t>
         </is>
       </c>
       <c r="G128" s="35" t="inlineStr">
         <is>
-          <t>1:30–2:00 ש׳</t>
+          <t>1:15 ש׳</t>
         </is>
       </c>
       <c r="H128" s="35" t="inlineStr">
         <is>
-          <t>כניסה חינם</t>
+          <t>חינם</t>
         </is>
       </c>
       <c r="I128" s="34" t="inlineStr">
         <is>
-          <t>קניות במקום מקורה/חצי מקורה.</t>
+          <t>כיכר מרכזית, קפה/ארוחת צהריים קצרה.</t>
         </is>
       </c>
       <c r="J128" s="34" t="inlineStr">
         <is>
-          <t>בדוק שעות פתיחה ביום א׳ סמוך לנסיעה.</t>
+          <t>ביום א׳ החניה העירונית במרכז חינם.</t>
         </is>
       </c>
     </row>
@@ -5141,139 +5141,143 @@
       </c>
       <c r="B129" s="35" t="inlineStr">
         <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C129" s="34" t="inlineStr">
+        <is>
+          <t>Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Premier Outlet Budapest</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Premier Outlet Budapest</t>
+        </is>
+      </c>
+      <c r="F129" s="35" t="inlineStr">
+        <is>
+          <t>2:30–2:50 ש׳</t>
+        </is>
+      </c>
+      <c r="G129" s="35" t="inlineStr">
+        <is>
+          <t>1:30–2:00 ש׳</t>
+        </is>
+      </c>
+      <c r="H129" s="35" t="inlineStr">
+        <is>
+          <t>כניסה חינם</t>
+        </is>
+      </c>
+      <c r="I129" s="34" t="inlineStr">
+        <is>
+          <t>קניות במקום מקורה/חצי מקורה.</t>
+        </is>
+      </c>
+      <c r="J129" s="34" t="inlineStr">
+        <is>
+          <t>בדוק שעות פתיחה ביום א׳ סמוך לנסיעה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="58" customHeight="1" s="6">
+      <c r="A130" s="34" t="inlineStr">
+        <is>
+          <t>27.9.2026 – חלופה</t>
+        </is>
+      </c>
+      <c r="B130" s="35" t="inlineStr">
+        <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="C129" s="34" t="inlineStr">
+      <c r="C130" s="34" t="inlineStr">
         <is>
           <t>Premier Outlet Budapest</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>La Prima Hotel Budapest</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>La Prima Hotel Budapest</t>
         </is>
       </c>
-      <c r="F129" s="35" t="inlineStr">
+      <c r="F130" s="35" t="inlineStr">
         <is>
           <t>25–40 דק׳</t>
         </is>
       </c>
-      <c r="G129" s="35" t="inlineStr">
+      <c r="G130" s="35" t="inlineStr">
         <is>
           <t>ערב</t>
         </is>
       </c>
-      <c r="H129" s="35" t="inlineStr">
+      <c r="H130" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I129" s="34" t="inlineStr">
+      <c r="I130" s="34" t="inlineStr">
         <is>
           <t>צ׳ק־אין וערב בעיר.</t>
         </is>
       </c>
-      <c r="J129" s="34" t="inlineStr">
+      <c r="J130" s="34" t="inlineStr">
         <is>
           <t>חניה: Franklin Parkolóház הוא חלופה זולה יחסית ליד המלון.</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="58" customHeight="1" s="6">
-      <c r="A130" s="36" t="inlineStr">
+    <row r="131" ht="20" customHeight="1" s="6">
+      <c r="A131" s="36" t="inlineStr">
         <is>
           <t>Google Maps לחלופה</t>
         </is>
       </c>
-      <c r="B130" s="37" t="n"/>
-      <c r="C130" s="15" t="inlineStr">
+      <c r="B131" s="37" t="n"/>
+      <c r="C131" s="15" t="inlineStr">
         <is>
           <t>לחץ לפתיחת מסלול החלופה ב-Google Maps</t>
         </is>
       </c>
-      <c r="D130" s="37" t="n"/>
-      <c r="E130" s="37" t="n"/>
-      <c r="F130" s="37" t="n"/>
-      <c r="G130" s="37" t="n"/>
-      <c r="H130" s="37" t="n"/>
-      <c r="I130" s="37" t="n"/>
-      <c r="J130" s="37" t="n"/>
-    </row>
-    <row r="131" ht="20" customHeight="1" s="6">
-      <c r="A131" s="39" t="inlineStr">
+      <c r="D131" s="37" t="n"/>
+      <c r="E131" s="37" t="n"/>
+      <c r="F131" s="37" t="n"/>
+      <c r="G131" s="37" t="n"/>
+      <c r="H131" s="37" t="n"/>
+      <c r="I131" s="37" t="n"/>
+      <c r="J131" s="37" t="n"/>
+    </row>
+    <row r="132" ht="28" customHeight="1" s="6">
+      <c r="A132" s="39" t="inlineStr">
         <is>
           <t>עלות החלופה ל-4: 0 € כניסות חובה (לא כולל קניות/חניה)</t>
         </is>
       </c>
-      <c r="B131" s="18" t="n"/>
-      <c r="C131" s="18" t="n"/>
-      <c r="D131" s="18" t="n"/>
-      <c r="E131" s="18" t="n"/>
-      <c r="F131" s="18" t="n"/>
-      <c r="G131" s="18" t="n"/>
-      <c r="H131" s="18" t="n"/>
-      <c r="I131" s="18" t="n"/>
-      <c r="J131" s="19" t="n"/>
-    </row>
-    <row r="132" ht="28" customHeight="1" s="6"/>
-    <row r="133" ht="8" customHeight="1" s="6">
-      <c r="A133" s="10" t="inlineStr">
+      <c r="B132" s="18" t="n"/>
+      <c r="C132" s="18" t="n"/>
+      <c r="D132" s="18" t="n"/>
+      <c r="E132" s="18" t="n"/>
+      <c r="F132" s="18" t="n"/>
+      <c r="G132" s="18" t="n"/>
+      <c r="H132" s="18" t="n"/>
+      <c r="I132" s="18" t="n"/>
+      <c r="J132" s="19" t="n"/>
+    </row>
+    <row r="133" ht="8" customHeight="1" s="6"/>
+    <row r="134" ht="28" customHeight="1" s="6">
+      <c r="A134" s="10" t="inlineStr">
         <is>
           <t>יום ב׳ | 28.9.2026 | בודפשט בבוקר, החזרת הרכב וטיסת קרן ומאי</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="28" customHeight="1" s="6">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>28.9.2026 – יום ב׳</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr"/>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>הפרלמנט ונעלי הברזל</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Shoes on the Danube Bank</t>
-        </is>
-      </c>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t>הליכה/תחבורה</t>
-        </is>
-      </c>
-      <c r="G134" s="3" t="inlineStr">
-        <is>
-          <t>1:15–1:30 ש׳</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>חינם מבחוץ</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>טיילת הדנובה, אנדרטת הנעליים ותצפית לפרלמנט.</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>אין צורך בסיור פנימי ביום טיסה.</t>
         </is>
       </c>
     </row>
@@ -5285,47 +5289,43 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
         <is>
           <t>הפרלמנט ונעלי הברזל</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>בזיליקת סנט אישטוון</t>
-        </is>
-      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Szent István Bazilika</t>
+          <t>Shoes on the Danube Bank</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>15–20 דק׳</t>
+          <t>הליכה/תחבורה</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>45–60 דק׳</t>
+          <t>1:15–1:30 ש׳</t>
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>ל־4: 10,400 HUF כנסייה / 20,000 HUF תצפית+אוצר / 27,200 HUF משולב</t>
+          <t>חינם מבחוץ</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>כיכר הבזיליקה, קפה ותצפית אם אין תור.</t>
+          <t>טיילת הדנובה, אנדרטת הנעליים ותצפית לפרלמנט.</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>לשמור זמן לחזרה למלון.</t>
+          <t>אין צורך בסיור פנימי ביום טיסה.</t>
         </is>
       </c>
     </row>
@@ -5337,47 +5337,47 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
+          <t>הפרלמנט ונעלי הברזל</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
           <t>בזיליקת סנט אישטוון</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>La Prima Hotel – איסוף מזוודות</t>
-        </is>
-      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>La Prima Hotel Budapest</t>
+          <t>Szent István Bazilika</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>15–25 דק׳</t>
+          <t>15–20 דק׳</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>20–25 דק׳</t>
+          <t>45–60 דק׳</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ל־4: 10,400 HUF כנסייה / 20,000 HUF תצפית+אוצר / 27,200 HUF משולב</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>איסוף מזוודות ויציאה להחזרת הרכב.</t>
+          <t>כיכר הבזיליקה, קפה ותצפית אם אין תור.</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>לא להתעכב – ההחזרה מוזמנת ל־13:00.</t>
+          <t>לשמור זמן לחזרה למלון.</t>
         </is>
       </c>
     </row>
@@ -5389,47 +5389,47 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
+          <t>בזיליקת סנט אישטוון</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
           <t>La Prima Hotel – איסוף מזוודות</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Klass Wagen – החזרת הרכב</t>
-        </is>
-      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Klass Wagen, Új Ecseri út 2, 2220 Vecsés, Hungary</t>
+          <t>La Prima Hotel Budapest</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>30–45 דק׳</t>
+          <t>15–25 דק׳</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>45–60 דק׳</t>
+          <t>20–25 דק׳</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>כלול בהשכרה</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>תדלוק לפני ההגעה, החזרת הרכב ובדיקת החשבון.</t>
+          <t>איסוף מזוודות ויציאה להחזרת הרכב.</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>כתובת מהואוצ׳ר: Új Ecseri út 2, 2220 Vecsés. לצלם רכב, דלק וקילומטראז׳ לפני המסירה.</t>
+          <t>לא להתעכב – ההחזרה מוזמנת ל־13:00.</t>
         </is>
       </c>
     </row>
@@ -5441,47 +5441,47 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
+          <t>La Prima Hotel – איסוף מזוודות</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
           <t>Klass Wagen – החזרת הרכב</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Budapest Airport Terminal 2</t>
-        </is>
-      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Budapest Airport Terminal 2</t>
+          <t>Klass Wagen, Új Ecseri út 2, 2220 Vecsés, Hungary</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>שאטל Klass Wagen</t>
+          <t>30–45 דק׳</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>עד הטיסה</t>
+          <t>45–60 דק׳</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>כלול בהשכרה</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>שאטל של חברת ההשכרה לטרמינל. קרן ומאי לטיסה 15:30.</t>
+          <t>תדלוק לפני ההגעה, החזרת הרכב ובדיקת החשבון.</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>ניסים ואלעד חוזרים לבודפשט לאחר הפרידה.</t>
+          <t>כתובת מהואוצ׳ר: Új Ecseri út 2, 2220 Vecsés. לצלם רכב, דלק וקילומטראז׳ לפני המסירה.</t>
         </is>
       </c>
     </row>
@@ -5493,143 +5493,147 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Klass Wagen – החזרת הרכב</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Budapest Airport Terminal 2</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Budapest Airport Terminal 2</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>שאטל Klass Wagen</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>עד הטיסה</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>שאטל של חברת ההשכרה לטרמינל. קרן ומאי לטיסה 15:30.</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>ניסים ואלעד חוזרים לבודפשט לאחר הפרידה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="58" customHeight="1" s="6">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>28.9.2026 – יום ב׳</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>Budapest Airport Terminal 2</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>חזרה לבודפשט – ניסים ואלעד</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>La Prima Hotel Budapest</t>
         </is>
       </c>
-      <c r="F139" s="3" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr">
         <is>
           <t>תחבורה ציבורית/מונית</t>
         </is>
       </c>
-      <c r="G139" s="3" t="inlineStr">
+      <c r="G140" s="3" t="inlineStr">
         <is>
           <t>אחה״צ וערב</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr">
+      <c r="H140" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>חזרה למרכז העיר, ואצי/דנובה/ארוחה לפי הכוח.</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr">
+      <c r="J140" s="2" t="inlineStr">
         <is>
           <t>אין יותר רכב שכור.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="58" customHeight="1" s="6">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>Google Maps ליום</t>
-        </is>
-      </c>
-      <c r="C140" s="15" t="inlineStr">
-        <is>
-          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
         </is>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1" s="6">
       <c r="A141" s="4" t="inlineStr">
         <is>
+          <t>Google Maps ליום</t>
+        </is>
+      </c>
+      <c r="C141" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1" s="6">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
           <t>לינה בסוף היום</t>
         </is>
       </c>
-      <c r="C141" s="15" t="inlineStr">
+      <c r="C142" s="15" t="inlineStr">
         <is>
           <t>בודפשט – ניסים ואלעד</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="20" customHeight="1" s="6">
-      <c r="A142" s="16" t="inlineStr">
+    <row r="143" ht="28" customHeight="1" s="6">
+      <c r="A143" s="16" t="inlineStr">
         <is>
           <t>עלות משוערת ליום ל-4: האתרים בחוץ חינם; בזיליקה אם נכנסים: 10,400–27,200 HUF ל־4 לפי סוג הכרטיס.</t>
         </is>
       </c>
-      <c r="B142" s="18" t="n"/>
-      <c r="C142" s="18" t="n"/>
-      <c r="D142" s="18" t="n"/>
-      <c r="E142" s="18" t="n"/>
-      <c r="F142" s="18" t="n"/>
-      <c r="G142" s="18" t="n"/>
-      <c r="H142" s="18" t="n"/>
-      <c r="I142" s="18" t="n"/>
-      <c r="J142" s="19" t="n"/>
-    </row>
-    <row r="143" ht="28" customHeight="1" s="6"/>
-    <row r="144" ht="8" customHeight="1" s="6">
-      <c r="A144" s="11" t="inlineStr">
+      <c r="B143" s="18" t="n"/>
+      <c r="C143" s="18" t="n"/>
+      <c r="D143" s="18" t="n"/>
+      <c r="E143" s="18" t="n"/>
+      <c r="F143" s="18" t="n"/>
+      <c r="G143" s="18" t="n"/>
+      <c r="H143" s="18" t="n"/>
+      <c r="I143" s="18" t="n"/>
+      <c r="J143" s="19" t="n"/>
+    </row>
+    <row r="144" ht="8" customHeight="1" s="6"/>
+    <row r="145" ht="28" customHeight="1" s="6">
+      <c r="A145" s="11" t="inlineStr">
         <is>
           <t>יום ג׳ | 29.9.2026 | בוקר רגוע וטיסה של ניסים ואלעד</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="28" customHeight="1" s="6">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>29.9.2026 – יום ג׳</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr"/>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>ארוחת בוקר וצ׳ק־אאוט</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>La Prima Hotel Budapest</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G145" s="3" t="inlineStr">
-        <is>
-          <t>60–75 דק׳</t>
-        </is>
-      </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>כלול/לפי המלון</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>ארוחת בוקר, אריזה ובדיקת החדר.</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>לא לתכנן אתר מרוחק ביום הטיסה.</t>
         </is>
       </c>
     </row>
@@ -5641,47 +5645,43 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
         <is>
           <t>ארוחת בוקר וצ׳ק־אאוט</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>יציאה לשדה התעופה</t>
-        </is>
-      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Budapest Airport Terminal 2</t>
+          <t>La Prima Hotel Budapest</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>35–50 דק׳</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60–75 דק׳</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>תחבורה לפי אמצעי</t>
+          <t>כלול/לפי המלון</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>מונית/תחבורה ציבורית לשדה.</t>
+          <t>ארוחת בוקר, אריזה ובדיקת החדר.</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>אין רכב שכור ביום זה.</t>
+          <t>לא לתכנן אתר מרוחק ביום הטיסה.</t>
         </is>
       </c>
     </row>
@@ -5693,47 +5693,47 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
+          <t>ארוחת בוקר וצ׳ק־אאוט</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
           <t>יציאה לשדה התעופה</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>Budapest Airport Terminal 2</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Budapest Airport Terminal 2</t>
-        </is>
-      </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
+          <t>35–50 דק׳</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G147" s="3" t="inlineStr">
-        <is>
-          <t>עד הטיסה</t>
-        </is>
-      </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>תחבורה לפי אמצעי</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>צ׳ק־אין, בידוק וביקורת גבולות.</t>
+          <t>מונית/תחבורה ציבורית לשדה.</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>לבדוק טרמינל ושעת טיסה ערב קודם.</t>
+          <t>אין רכב שכור ביום זה.</t>
         </is>
       </c>
     </row>
@@ -5745,91 +5745,142 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>יציאה לשדה התעופה</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Budapest Airport Terminal 2</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Budapest Airport Terminal 2</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>עד הטיסה</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>צ׳ק־אין, בידוק וביקורת גבולות.</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>לבדוק טרמינל ושעת טיסה ערב קודם.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="58" customHeight="1" s="6">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>29.9.2026 – יום ג׳</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>Budapest Airport Terminal 2</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>טיסה הביתה</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E149" t="inlineStr">
         <is>
           <t>Budapest Airport Terminal 2</t>
         </is>
       </c>
-      <c r="F148" s="3" t="inlineStr">
+      <c r="F149" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G148" s="3" t="inlineStr">
+      <c r="G149" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
+      <c r="H149" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>טיסת ניסים ואלעד.</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="58" customHeight="1" s="6">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>Google Maps ליום</t>
-        </is>
-      </c>
-      <c r="C149" s="15" t="inlineStr">
-        <is>
-          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
         </is>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1" s="6">
       <c r="A150" s="4" t="inlineStr">
         <is>
+          <t>Google Maps ליום</t>
+        </is>
+      </c>
+      <c r="C150" s="15" t="inlineStr">
+        <is>
+          <t>לחץ לפתיחת המסלול היומי המלא ב-Google Maps</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1" s="6">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
           <t>לינה בסוף היום</t>
         </is>
       </c>
-      <c r="C150" s="15" t="inlineStr">
+      <c r="C151" s="15" t="inlineStr">
         <is>
           <t>טיסה חזרה</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="20" customHeight="1" s="6">
-      <c r="A151" s="16" t="inlineStr">
+    <row r="152" ht="28" customHeight="1" s="6">
+      <c r="A152" s="16" t="inlineStr">
         <is>
           <t>עלות משוערת ליום ל-4: 0 € (לא כולל תחבורה לשדה)</t>
         </is>
       </c>
-      <c r="B151" s="18" t="n"/>
-      <c r="C151" s="18" t="n"/>
-      <c r="D151" s="18" t="n"/>
-      <c r="E151" s="18" t="n"/>
-      <c r="F151" s="18" t="n"/>
-      <c r="G151" s="18" t="n"/>
-      <c r="H151" s="18" t="n"/>
-      <c r="I151" s="18" t="n"/>
-      <c r="J151" s="19" t="n"/>
-    </row>
-    <row r="152" ht="28" customHeight="1" s="6"/>
+      <c r="B152" s="18" t="n"/>
+      <c r="C152" s="18" t="n"/>
+      <c r="D152" s="18" t="n"/>
+      <c r="E152" s="18" t="n"/>
+      <c r="F152" s="18" t="n"/>
+      <c r="G152" s="18" t="n"/>
+      <c r="H152" s="18" t="n"/>
+      <c r="I152" s="18" t="n"/>
+      <c r="J152" s="19" t="n"/>
+    </row>
     <row r="153" ht="8" customHeight="1" s="6"/>
   </sheetData>
   <mergeCells count="29">
@@ -5904,150 +5955,152 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId186"/>
   </hyperlinks>
   <pageMargins left="0.2" right="0.2" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
